--- a/GourmetProject/outputs/019febb6-949b-73e2-9ecb-7ccaca223606/dish.xlsx
+++ b/GourmetProject/outputs/019febb6-949b-73e2-9ecb-7ccaca223606/dish.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_base" sheetId="1" r:id="R1ac9c19333b745c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_variant" sheetId="2" r:id="R8c3711a6b4704606"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill" sheetId="3" r:id="Rb1a8e3ebae254eb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="flavor" sheetId="4" r:id="R11a1a4fb4f754e90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cake_layer_buff" sheetId="5" r:id="Ra01794a61b6a44a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sub_skill" sheetId="6" r:id="R56972f6da0a642c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="食物设计新" sheetId="9" r:id="R9874a73c4a364553"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="位置" sheetId="8" r:id="R9b288f1ac58a4c3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_base" sheetId="1" r:id="R8eba09af5c0e487f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_variant" sheetId="2" r:id="R02e1f55aed2f4f5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill" sheetId="3" r:id="Rf88d20c53d8b458f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="flavor" sheetId="4" r:id="Rfed65e6323134d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cake_layer_buff" sheetId="5" r:id="Rf9e2b4cff8e94586"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sub_skill" sheetId="6" r:id="Rf636764f7d3b46fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="食物设计新" sheetId="9" r:id="R4d9c9a4f4fcd408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="位置" sheetId="8" r:id="R42cf0881a32a4c8b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -179,409 +179,88 @@
     <x:t xml:space="preserve">本技能独占的有序子技能ID列表（| 分隔，命名为 skillId_序号）</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_arrow_cookie_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">arrow_cookie_1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">箭头饼干1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_arrow_cookie_2_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">arrow_cookie_2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">箭头饼干2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_arrow_cookie_3_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">arrow_cookie_3</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">箭头饼干3</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_arrow_cookie_4_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">arrow_cookie_4</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">箭头饼干4</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_jelly_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">jelly</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">果冻</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_cupcake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cupcake</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">糖霜蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_eggtart_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">eggtart</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">蛋挞</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_sugarbean_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_sugarbean_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sugarbean</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">糖豆</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_cheesecake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cheesecake_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cheesecake</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">芝士蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_mousse_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">mousse</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">慕斯蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_fruit_candy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_fruit_candy_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">fruit_candy</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">水果糖</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_choco_bar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_choco_bar_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">choco_bar</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">巧克力棒</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_mochi_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">mochi</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">麻薯</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_cup_cake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cup_cake_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cup_cake</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">杯子蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_cream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cream</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">奶油</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_eggroll_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">eggroll</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">蛋卷</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_baguette_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">baguette</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">法棍</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_tanghulu_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_tanghulu_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tanghulu</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">糖葫芦</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_cake_slice_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cake_slice_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cake_slice</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">蛋糕切角</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_long_cake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_long_cake_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">long_cake</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">长条蛋糕</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_eclair_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">eclair</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">闪电泡芙</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_gummy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">gummy</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">软糖</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_chocolate_strip_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_chocolate_strip_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">chocolate_strip</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">巧克力条</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cake_roll_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cake_roll_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cake_roll</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">蛋糕卷</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_palmier_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">palmier</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">蝴蝶酥</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_chiffion_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">chiffion</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">戚风蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_maple_sugar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">maple_sugar</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">枫糖</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_taosu_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">taosu</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">桃酥</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_waffle_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">waffle</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">华夫饼</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cream_cake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cream_cake_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cream_cake</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">奶油蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_candycane_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_candycane_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">candycane</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">拐杖糖</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_black_forest_cake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_black_forest_cake_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">black_forest_cake</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">黑森林蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_chocolate_sauce_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_chocolate_sauce_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">chocolate_sauce</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">巧克力酱</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_mango_sago_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">mango_sago</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">杨枝甘露</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_fruit_cake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_fruit_cake_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">fruit_cake</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">水果蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_parfait_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">parfait</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">芭菲</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_marshmallow_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">marshmallow</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">棉花糖</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_big_lollipop_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_big_lollipop_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">big_lollipop</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">大棒棒糖</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_apple_pie_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">apple_pie</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">苹果派</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_double_cake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">double_cake</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">双层蛋糕</x:t>
@@ -914,16 +593,49 @@
     <x:t xml:space="preserve">ColumnAndSelf</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">奶油</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">All</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">RowAndSelf</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">法棍</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">蛋糕切角</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Category</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">长条蛋糕</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">闪电泡芙</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">巧克力条</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">枫糖</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">华夫饼</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">巧克力酱</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">芭菲</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Down</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">苹果派</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">食物</x:t>
@@ -1060,9 +772,6 @@
     <x:t xml:space="preserve">份数+蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用01</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">首个结算时
 所有食物分数+20</x:t>
   </x:si>
@@ -1103,9 +812,6 @@
     <x:t xml:space="preserve">所有</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用02</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">处于边缘时
 边缘食物分数+30</x:t>
   </x:si>
@@ -1141,56 +847,32 @@
 欢乐蛋糕 +10 层</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">蛋糕01</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">每有1个空格
 欢乐蛋糕+5层</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">传递01</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">左侧及自身倍率+1
 甜蜜传递至1个食物</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">份数01</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">每有1个占2格的食物
 此类食物分数+8</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用03</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">每次结算
 分数永久-20</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用04</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">将本行食物中最高分数的1/4
 加至本行其他食物上</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用05</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">每有1个装饰品
 本列分数+10</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用06</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">本列倍率+2
 营业结束后1/10概率移除食物</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">传递02</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">结算后
@@ -1201,9 +883,6 @@
     <x:t xml:space="preserve">风味强化</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">蛋糕02</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">本列每有1个蛋糕
 欢乐蛋糕+10层</x:t>
   </x:si>
@@ -1215,9 +894,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">空主动道具槽加分</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">份数02</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">周围及自身
@@ -1281,29 +957,14 @@
     <x:t xml:space="preserve">营业结束概率获得格子</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">蛋糕03</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">蛋糕04</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">欢乐蛋糕+20～80层</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">份数03</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">空格视为2份食物</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">份数04</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">本列每个食物
 将技能数计入份数</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">传递03</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">结算后
@@ -1311,9 +972,6 @@
 额外选择1个目标</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">传递04</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">本行
 每有1份食物，倍率+0.1
 甜蜜传递至5个食物</x:t>
@@ -1388,14 +1046,8 @@
     <x:t xml:space="preserve">.X</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用07</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">本行
 每有1个风味，倍率+0.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">通用08</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">处于非边缘时
@@ -1630,7 +1282,7 @@
       <x:name val="宋体"/>
     </x:font>
   </x:fonts>
-  <x:fills count="41">
+  <x:fills count="42">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -1832,8 +1484,13 @@
         <x:fgColor theme="9" tint="0.39998"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF8C6A43"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="12">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -1926,6 +1583,34 @@
       </x:top>
       <x:bottom style="double">
         <x:color theme="4"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9C8B4"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9C8B4"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9C8B4"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9C8B4"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6DDD3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE6DDD3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE6DDD3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6DDD3"/>
       </x:bottom>
     </x:border>
   </x:borders>
@@ -2076,7 +1761,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="46">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -2176,6 +1861,34 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="41" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="41" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="41" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="41" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -2629,11 +2342,11 @@
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.799999237060547"/>
   <x:cols>
     <x:col min="1" max="1" width="13.076923370361328" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="18.384614944458008" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="220" style="1" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="10.307692527770996" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="13.461538314819336" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="20" style="1" customWidth="1"/>
-    <x:col min="6" max="6" width="21.153846740722656" style="1" customWidth="1"/>
+    <x:col min="6" max="6" width="250" style="1" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="25.538461685180664" style="1" customWidth="1"/>
     <x:col min="8" max="8" width="20.076923370361328" style="1" customWidth="1"/>
     <x:col min="9" max="9" width="17.615385055541992" style="1" customWidth="1"/>
@@ -3614,10 +3327,10 @@
     <x:row r="16">
       <x:c r="A16" s="26"/>
       <x:c r="B16" s="1" t="str">
-        <x:v>codename_general_01</x:v>
+        <x:v>caramel_pudding</x:v>
       </x:c>
       <x:c r="C16" s="1" t="str">
-        <x:v>通用01</x:v>
+        <x:v>焦糖布丁</x:v>
       </x:c>
       <x:c r="D16" s="1" t="n">
         <x:v>20</x:v>
@@ -3626,7 +3339,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F16" s="1" t="str">
-        <x:v>sk_codename_general_01</x:v>
+        <x:v>sk_caramel_pudding</x:v>
       </x:c>
       <x:c r="G16" s="26"/>
       <x:c r="H16" s="1" t="n">
@@ -4067,10 +3780,10 @@
     <x:row r="25">
       <x:c r="A25" s="26"/>
       <x:c r="B25" s="26" t="str">
-        <x:v>cream</x:v>
+        <x:v>cream_puff</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
-        <x:v>奶油</x:v>
+        <x:v>奶油泡芙</x:v>
       </x:c>
       <x:c r="D25" s="26" t="n">
         <x:v>20</x:v>
@@ -4079,7 +3792,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F25" s="26" t="str">
-        <x:v>sk_cream</x:v>
+        <x:v>sk_cream_puff</x:v>
       </x:c>
       <x:c r="G25" s="26"/>
       <x:c r="H25" s="26" t="n">
@@ -4163,10 +3876,10 @@
     <x:row r="27">
       <x:c r="A27" s="26"/>
       <x:c r="B27" s="1" t="str">
-        <x:v>codename_general_02</x:v>
+        <x:v>ice_cream</x:v>
       </x:c>
       <x:c r="C27" s="1" t="str">
-        <x:v>通用02</x:v>
+        <x:v>冰淇淋</x:v>
       </x:c>
       <x:c r="D27" s="1" t="n">
         <x:v>100</x:v>
@@ -4175,7 +3888,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F27" s="1" t="str">
-        <x:v>sk_codename_general_02</x:v>
+        <x:v>sk_ice_cream</x:v>
       </x:c>
       <x:c r="G27" s="26"/>
       <x:c r="H27" s="1" t="n">
@@ -4351,10 +4064,10 @@
     <x:row r="30">
       <x:c r="A30" s="26"/>
       <x:c r="B30" s="1" t="str">
-        <x:v>baguette</x:v>
+        <x:v>osmanthus_cake</x:v>
       </x:c>
       <x:c r="C30" s="1" t="str">
-        <x:v>法棍</x:v>
+        <x:v>桂花糕</x:v>
       </x:c>
       <x:c r="D30" s="1" t="n">
         <x:v>30</x:v>
@@ -4363,7 +4076,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F30" s="1" t="str">
-        <x:v>sk_baguette</x:v>
+        <x:v>sk_osmanthus_cake</x:v>
       </x:c>
       <x:c r="G30" s="1"/>
       <x:c r="H30" s="1" t="n">
@@ -4487,10 +4200,10 @@
     <x:row r="32">
       <x:c r="A32" s="26"/>
       <x:c r="B32" s="26" t="str">
-        <x:v>cake_slice</x:v>
+        <x:v>napoleon_cake</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>蛋糕切角</x:v>
+        <x:v>拿破仑蛋糕</x:v>
       </x:c>
       <x:c r="D32" s="26" t="n">
         <x:v>30</x:v>
@@ -4499,7 +4212,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F32" s="26" t="str">
-        <x:v>sk_cake_slice</x:v>
+        <x:v>sk_napoleon_cake</x:v>
       </x:c>
       <x:c r="G32" s="26" t="str">
         <x:v>cake</x:v>
@@ -4535,10 +4248,10 @@
     <x:row r="33">
       <x:c r="A33" s="26"/>
       <x:c r="B33" s="26" t="str">
-        <x:v>long_cake</x:v>
+        <x:v>honey_cake</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>长条蛋糕</x:v>
+        <x:v>蜂蜜蛋糕</x:v>
       </x:c>
       <x:c r="D33" s="26" t="n">
         <x:v>30</x:v>
@@ -4547,7 +4260,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F33" s="26" t="str">
-        <x:v>sk_long_cake</x:v>
+        <x:v>sk_honey_cake</x:v>
       </x:c>
       <x:c r="G33" s="26" t="str">
         <x:v>cake</x:v>
@@ -4583,10 +4296,10 @@
     <x:row r="34">
       <x:c r="A34" s="26"/>
       <x:c r="B34" s="1" t="str">
-        <x:v>codename_cake_01</x:v>
+        <x:v>tree_ring_cake</x:v>
       </x:c>
       <x:c r="C34" s="1" t="str">
-        <x:v>蛋糕01</x:v>
+        <x:v>年轮蛋糕</x:v>
       </x:c>
       <x:c r="D34" s="1" t="n">
         <x:v>30</x:v>
@@ -4595,7 +4308,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F34" s="1" t="str">
-        <x:v>sk_codename_cake_01</x:v>
+        <x:v>sk_tree_ring_cake</x:v>
       </x:c>
       <x:c r="G34" s="26" t="str">
         <x:v>cake</x:v>
@@ -4653,10 +4366,10 @@
     <x:row r="35">
       <x:c r="A35" s="26"/>
       <x:c r="B35" s="26" t="str">
-        <x:v>codename_transfer_01</x:v>
+        <x:v>nougat</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>传递01</x:v>
+        <x:v>牛轧糖</x:v>
       </x:c>
       <x:c r="D35" s="26" t="n">
         <x:v>30</x:v>
@@ -4665,7 +4378,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F35" s="26" t="str">
-        <x:v>sk_codename_transfer_01</x:v>
+        <x:v>sk_nougat</x:v>
       </x:c>
       <x:c r="G35" s="26"/>
       <x:c r="H35" s="26" t="n">
@@ -4699,10 +4412,10 @@
     <x:row r="36">
       <x:c r="A36" s="26"/>
       <x:c r="B36" s="26" t="str">
-        <x:v>codename_serving_01</x:v>
+        <x:v>hawthorn_cake</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>份数01</x:v>
+        <x:v>山楂糕</x:v>
       </x:c>
       <x:c r="D36" s="26" t="n">
         <x:v>30</x:v>
@@ -4711,7 +4424,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F36" s="26" t="str">
-        <x:v>sk_codename_serving_01</x:v>
+        <x:v>sk_hawthorn_cake</x:v>
       </x:c>
       <x:c r="G36" s="26"/>
       <x:c r="H36" s="26" t="n">
@@ -4745,10 +4458,10 @@
     <x:row r="37">
       <x:c r="A37" s="26"/>
       <x:c r="B37" s="1" t="str">
-        <x:v>codename_general_03</x:v>
+        <x:v>souffle</x:v>
       </x:c>
       <x:c r="C37" s="1" t="str">
-        <x:v>通用03</x:v>
+        <x:v>舒芙蕾</x:v>
       </x:c>
       <x:c r="D37" s="1" t="n">
         <x:v>300</x:v>
@@ -4757,7 +4470,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F37" s="1" t="str">
-        <x:v>sk_codename_general_03</x:v>
+        <x:v>sk_souffle</x:v>
       </x:c>
       <x:c r="G37" s="26"/>
       <x:c r="H37" s="1" t="n">
@@ -4813,10 +4526,10 @@
     <x:row r="38">
       <x:c r="A38" s="26"/>
       <x:c r="B38" s="26" t="str">
-        <x:v>codename_general_04</x:v>
+        <x:v>fruit_tart</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>通用04</x:v>
+        <x:v>水果挞</x:v>
       </x:c>
       <x:c r="D38" s="26" t="n">
         <x:v>30</x:v>
@@ -4825,7 +4538,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F38" s="26" t="str">
-        <x:v>sk_codename_general_04</x:v>
+        <x:v>sk_fruit_tart</x:v>
       </x:c>
       <x:c r="G38" s="26"/>
       <x:c r="H38" s="26" t="n">
@@ -4859,10 +4572,10 @@
     <x:row r="39">
       <x:c r="A39" s="26"/>
       <x:c r="B39" s="26" t="str">
-        <x:v>codename_general_05</x:v>
+        <x:v>strawberry_sundae</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>通用05</x:v>
+        <x:v>草莓圣代</x:v>
       </x:c>
       <x:c r="D39" s="26" t="n">
         <x:v>30</x:v>
@@ -4871,7 +4584,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F39" s="26" t="str">
-        <x:v>sk_codename_general_05</x:v>
+        <x:v>sk_strawberry_sundae</x:v>
       </x:c>
       <x:c r="G39" s="26"/>
       <x:c r="H39" s="26" t="n">
@@ -4986,10 +4699,10 @@
     <x:row r="42">
       <x:c r="A42" s="26"/>
       <x:c r="B42" s="26" t="str">
-        <x:v>codename_general_06</x:v>
+        <x:v>rock_sugar_pear</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>通用06</x:v>
+        <x:v>冰糖雪梨</x:v>
       </x:c>
       <x:c r="D42" s="26" t="n">
         <x:v>30</x:v>
@@ -4998,7 +4711,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F42" s="26" t="str">
-        <x:v>sk_codename_general_06</x:v>
+        <x:v>sk_rock_sugar_pear</x:v>
       </x:c>
       <x:c r="G42" s="26"/>
       <x:c r="H42" s="26" t="n">
@@ -5113,10 +4826,10 @@
     <x:row r="45">
       <x:c r="A45" s="26"/>
       <x:c r="B45" s="1" t="str">
-        <x:v>codename_transfer_02</x:v>
+        <x:v>popping_candy</x:v>
       </x:c>
       <x:c r="C45" s="1" t="str">
-        <x:v>传递02</x:v>
+        <x:v>跳跳糖</x:v>
       </x:c>
       <x:c r="D45" s="1" t="n">
         <x:v>30</x:v>
@@ -5125,7 +4838,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F45" s="1" t="str">
-        <x:v>sk_codename_transfer_02</x:v>
+        <x:v>sk_popping_candy</x:v>
       </x:c>
       <x:c r="G45" s="1"/>
       <x:c r="H45" s="1" t="n">
@@ -5261,10 +4974,10 @@
     <x:row r="48">
       <x:c r="A48" s="26"/>
       <x:c r="B48" s="26" t="str">
-        <x:v>codename_cake_02</x:v>
+        <x:v>mille_crepe_cake</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>蛋糕02</x:v>
+        <x:v>千层蛋糕</x:v>
       </x:c>
       <x:c r="D48" s="26" t="n">
         <x:v>30</x:v>
@@ -5273,7 +4986,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F48" s="26" t="str">
-        <x:v>sk_codename_cake_02</x:v>
+        <x:v>sk_mille_crepe_cake</x:v>
       </x:c>
       <x:c r="G48" s="26" t="str">
         <x:v>cake</x:v>
@@ -5390,10 +5103,10 @@
     <x:row r="51">
       <x:c r="A51" s="26"/>
       <x:c r="B51" s="1" t="str">
-        <x:v>codename_serving_02</x:v>
+        <x:v>soybean_glutinous_roll</x:v>
       </x:c>
       <x:c r="C51" s="1" t="str">
-        <x:v>份数02</x:v>
+        <x:v>驴打滚</x:v>
       </x:c>
       <x:c r="D51" s="1" t="n">
         <x:v>30</x:v>
@@ -5402,7 +5115,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F51" s="1" t="str">
-        <x:v>sk_codename_serving_02</x:v>
+        <x:v>sk_soybean_glutinous_roll</x:v>
       </x:c>
       <x:c r="G51" s="26"/>
       <x:c r="H51" s="1" t="n">
@@ -5538,10 +5251,10 @@
     <x:row r="54">
       <x:c r="A54" s="26"/>
       <x:c r="B54" s="26" t="str">
-        <x:v>eclair</x:v>
+        <x:v>sachima</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
-        <x:v>闪电泡芙</x:v>
+        <x:v>沙琪玛</x:v>
       </x:c>
       <x:c r="D54" s="26" t="n">
         <x:v>30</x:v>
@@ -5550,7 +5263,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F54" s="26" t="str">
-        <x:v>sk_eclair</x:v>
+        <x:v>sk_sachima</x:v>
       </x:c>
       <x:c r="G54" s="26"/>
       <x:c r="H54" s="26" t="n">
@@ -5792,10 +5505,10 @@
     <x:row r="60">
       <x:c r="A60" s="26"/>
       <x:c r="B60" s="1" t="str">
-        <x:v>chocolate_strip</x:v>
+        <x:v>chocolate_wafer</x:v>
       </x:c>
       <x:c r="C60" s="1" t="str">
-        <x:v>巧克力条</x:v>
+        <x:v>巧克力威化</x:v>
       </x:c>
       <x:c r="D60" s="1" t="n">
         <x:v>30</x:v>
@@ -5804,7 +5517,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F60" s="1" t="str">
-        <x:v>sk_chocolate_strip</x:v>
+        <x:v>sk_chocolate_wafer</x:v>
       </x:c>
       <x:c r="G60" s="26"/>
       <x:c r="H60" s="1" t="n">
@@ -6069,10 +5782,10 @@
     <x:row r="66">
       <x:c r="A66" s="26"/>
       <x:c r="B66" s="26" t="str">
-        <x:v>codename_cake_03</x:v>
+        <x:v>fondant_cake</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
-        <x:v>蛋糕03</x:v>
+        <x:v>翻糖蛋糕</x:v>
       </x:c>
       <x:c r="D66" s="26" t="n">
         <x:v>30</x:v>
@@ -6081,7 +5794,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F66" s="26" t="str">
-        <x:v>sk_codename_cake_03</x:v>
+        <x:v>sk_fondant_cake</x:v>
       </x:c>
       <x:c r="G66" s="26" t="str">
         <x:v>cake</x:v>
@@ -6168,10 +5881,10 @@
     <x:row r="68">
       <x:c r="A68" s="26"/>
       <x:c r="B68" s="26" t="str">
-        <x:v>codename_cake_04</x:v>
+        <x:v>matcha_cake</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
-        <x:v>蛋糕04</x:v>
+        <x:v>抹茶蛋糕</x:v>
       </x:c>
       <x:c r="D68" s="26" t="n">
         <x:v>30</x:v>
@@ -6180,7 +5893,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F68" s="26" t="str">
-        <x:v>sk_codename_cake_04</x:v>
+        <x:v>sk_matcha_cake</x:v>
       </x:c>
       <x:c r="G68" s="26" t="str">
         <x:v>cake</x:v>
@@ -6246,10 +5959,10 @@
     <x:row r="70">
       <x:c r="A70" s="26"/>
       <x:c r="B70" s="1" t="str">
-        <x:v>codename_serving_03</x:v>
+        <x:v>mung_bean_cake</x:v>
       </x:c>
       <x:c r="C70" s="1" t="str">
-        <x:v>份数03</x:v>
+        <x:v>绿豆糕</x:v>
       </x:c>
       <x:c r="D70" s="1" t="n">
         <x:v>30</x:v>
@@ -6258,7 +5971,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F70" s="1" t="str">
-        <x:v>sk_codename_serving_03</x:v>
+        <x:v>sk_mung_bean_cake</x:v>
       </x:c>
       <x:c r="G70" s="26"/>
       <x:c r="H70" s="1" t="n">
@@ -6343,10 +6056,10 @@
     <x:row r="72">
       <x:c r="A72" s="26"/>
       <x:c r="B72" s="26" t="str">
-        <x:v>codename_serving_04</x:v>
+        <x:v>egg_yolk_pastry</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
-        <x:v>份数04</x:v>
+        <x:v>蛋黄酥</x:v>
       </x:c>
       <x:c r="D72" s="26" t="n">
         <x:v>30</x:v>
@@ -6355,7 +6068,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F72" s="26" t="str">
-        <x:v>sk_codename_serving_04</x:v>
+        <x:v>sk_egg_yolk_pastry</x:v>
       </x:c>
       <x:c r="G72" s="26"/>
       <x:c r="H72" s="26" t="n">
@@ -6442,10 +6155,10 @@
     <x:row r="74">
       <x:c r="A74" s="26"/>
       <x:c r="B74" s="26" t="str">
-        <x:v>codename_transfer_03</x:v>
+        <x:v>chocolate_truffle</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
-        <x:v>传递03</x:v>
+        <x:v>松露巧克力</x:v>
       </x:c>
       <x:c r="D74" s="26" t="n">
         <x:v>30</x:v>
@@ -6454,7 +6167,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F74" s="26" t="str">
-        <x:v>sk_codename_transfer_03</x:v>
+        <x:v>sk_chocolate_truffle</x:v>
       </x:c>
       <x:c r="G74" s="26"/>
       <x:c r="H74" s="26" t="n">
@@ -6518,10 +6231,10 @@
     <x:row r="76">
       <x:c r="A76" s="26"/>
       <x:c r="B76" s="1" t="str">
-        <x:v>codename_transfer_04</x:v>
+        <x:v>liquor_chocolate</x:v>
       </x:c>
       <x:c r="C76" s="1" t="str">
-        <x:v>传递04</x:v>
+        <x:v>酒心巧克力</x:v>
       </x:c>
       <x:c r="D76" s="1" t="n">
         <x:v>30</x:v>
@@ -6530,7 +6243,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F76" s="1" t="str">
-        <x:v>sk_codename_transfer_04</x:v>
+        <x:v>sk_liquor_chocolate</x:v>
       </x:c>
       <x:c r="G76" s="26"/>
       <x:c r="H76" s="1" t="n">
@@ -6794,10 +6507,10 @@
     <x:row r="82">
       <x:c r="A82" s="26"/>
       <x:c r="B82" s="26" t="str">
-        <x:v>maple_sugar</x:v>
+        <x:v>toffee_candy</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
-        <x:v>枫糖</x:v>
+        <x:v>太妃糖</x:v>
       </x:c>
       <x:c r="D82" s="26" t="n">
         <x:v>40</x:v>
@@ -6806,7 +6519,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F82" s="26" t="str">
-        <x:v>sk_maple_sugar</x:v>
+        <x:v>sk_toffee_candy</x:v>
       </x:c>
       <x:c r="G82" s="26"/>
       <x:c r="H82" s="26" t="n">
@@ -6917,10 +6630,10 @@
     <x:row r="86">
       <x:c r="A86" s="26"/>
       <x:c r="B86" s="26" t="str">
-        <x:v>waffle</x:v>
+        <x:v>brown_sugar_steamed_cake</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
-        <x:v>华夫饼</x:v>
+        <x:v>红糖发糕</x:v>
       </x:c>
       <x:c r="D86" s="26" t="n">
         <x:v>40</x:v>
@@ -6929,7 +6642,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F86" s="26" t="str">
-        <x:v>sk_waffle</x:v>
+        <x:v>sk_brown_sugar_steamed_cake</x:v>
       </x:c>
       <x:c r="G86" s="26"/>
       <x:c r="H86" s="26" t="n">
@@ -7079,10 +6792,10 @@
     <x:row r="93">
       <x:c r="A93" s="26"/>
       <x:c r="B93" s="26" t="str">
-        <x:v>codename_general_07</x:v>
+        <x:v>fruit_shaved_ice</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
-        <x:v>通用07</x:v>
+        <x:v>水果刨冰</x:v>
       </x:c>
       <x:c r="D93" s="26" t="n">
         <x:v>40</x:v>
@@ -7091,7 +6804,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F93" s="26" t="str">
-        <x:v>sk_codename_general_07</x:v>
+        <x:v>sk_fruit_shaved_ice</x:v>
       </x:c>
       <x:c r="G93" s="26"/>
       <x:c r="H93" s="26" t="n">
@@ -7127,10 +6840,10 @@
     <x:row r="95">
       <x:c r="A95" s="26"/>
       <x:c r="B95" s="26" t="str">
-        <x:v>codename_general_08</x:v>
+        <x:v>coconut_milk_jelly</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
-        <x:v>通用08</x:v>
+        <x:v>椰奶冻</x:v>
       </x:c>
       <x:c r="D95" s="26" t="n">
         <x:v>40</x:v>
@@ -7139,7 +6852,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F95" s="26" t="str">
-        <x:v>sk_codename_general_08</x:v>
+        <x:v>sk_coconut_milk_jelly</x:v>
       </x:c>
       <x:c r="G95" s="26"/>
       <x:c r="H95" s="26" t="n">
@@ -7224,10 +6937,10 @@
     <x:row r="99">
       <x:c r="A99" s="26"/>
       <x:c r="B99" s="26" t="str">
-        <x:v>chocolate_sauce</x:v>
+        <x:v>nama_chocolate</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
-        <x:v>巧克力酱</x:v>
+        <x:v>生巧克力</x:v>
       </x:c>
       <x:c r="D99" s="26" t="n">
         <x:v>60</x:v>
@@ -7236,7 +6949,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F99" s="26" t="str">
-        <x:v>sk_chocolate_sauce</x:v>
+        <x:v>sk_nama_chocolate</x:v>
       </x:c>
       <x:c r="G99" s="26"/>
       <x:c r="H99" s="26" t="n">
@@ -7379,10 +7092,10 @@
     <x:row r="106">
       <x:c r="A106" s="26"/>
       <x:c r="B106" s="26" t="str">
-        <x:v>parfait</x:v>
+        <x:v>fermented_rice_balls</x:v>
       </x:c>
       <x:c r="C106" s="26" t="str">
-        <x:v>芭菲</x:v>
+        <x:v>酒酿圆子</x:v>
       </x:c>
       <x:c r="D106" s="26" t="n">
         <x:v>60</x:v>
@@ -7391,7 +7104,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F106" s="26" t="str">
-        <x:v>sk_parfait</x:v>
+        <x:v>sk_fermented_rice_balls</x:v>
       </x:c>
       <x:c r="G106" s="26"/>
       <x:c r="H106" s="26" t="n">
@@ -7562,10 +7275,10 @@
     <x:row r="115">
       <x:c r="A115" s="26"/>
       <x:c r="B115" s="26" t="str">
-        <x:v>apple_pie</x:v>
+        <x:v>double_skin_milk</x:v>
       </x:c>
       <x:c r="C115" s="26" t="str">
-        <x:v>苹果派</x:v>
+        <x:v>双皮奶</x:v>
       </x:c>
       <x:c r="D115" s="26" t="n">
         <x:v>100</x:v>
@@ -7574,7 +7287,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F115" s="26" t="str">
-        <x:v>sk_apple_pie</x:v>
+        <x:v>sk_double_skin_milk</x:v>
       </x:c>
       <x:c r="G115" s="26"/>
       <x:c r="H115" s="26" t="n">
@@ -7701,10 +7414,10 @@
     <x:row r="122">
       <x:c r="A122" s="26"/>
       <x:c r="B122" s="26" t="str">
-        <x:v>mantou</x:v>
+        <x:v>custard_bun</x:v>
       </x:c>
       <x:c r="C122" s="26" t="str">
-        <x:v>馒头</x:v>
+        <x:v>奶黄包</x:v>
       </x:c>
       <x:c r="D122" s="26" t="n">
         <x:v>10</x:v>
@@ -7737,8 +7450,8 @@
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.799999237060547"/>
   <x:cols>
     <x:col min="1" max="1" width="13.076923370361328" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="21.461538314819336" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="20.384614944458008" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="220" style="1" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="220" style="1" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="38" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="15.15384578704834" style="1" customWidth="1"/>
     <x:col min="6" max="6" width="10.307692527770996" style="1" customWidth="1"/>
@@ -8220,10 +7933,10 @@
       <x:c r="A14" s="31"/>
       <x:c r="B14" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_general_01</x:v>
+        <x:v>caramel_pudding</x:v>
       </x:c>
       <x:c r="C14" s="1" t="str">
-        <x:v>codename_general_01</x:v>
+        <x:v>caramel_pudding</x:v>
       </x:c>
       <x:c r="D14" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8250,7 +7963,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L14" s="31" t="str">
-        <x:v>通用01</x:v>
+        <x:v>焦糖布丁</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -8405,10 +8118,10 @@
       <x:c r="A19" s="31"/>
       <x:c r="B19" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>cream</x:v>
+        <x:v>cream_puff</x:v>
       </x:c>
       <x:c r="C19" s="1" t="str">
-        <x:v>cream</x:v>
+        <x:v>cream_puff</x:v>
       </x:c>
       <x:c r="D19" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8435,17 +8148,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L19" s="31" t="str">
-        <x:v>奶油</x:v>
+        <x:v>奶油泡芙</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="31"/>
       <x:c r="B20" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_general_02</x:v>
+        <x:v>ice_cream</x:v>
       </x:c>
       <x:c r="C20" s="1" t="str">
-        <x:v>codename_general_02</x:v>
+        <x:v>ice_cream</x:v>
       </x:c>
       <x:c r="D20" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8472,7 +8185,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L20" s="31" t="str">
-        <x:v>通用02</x:v>
+        <x:v>冰淇淋</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -8516,10 +8229,10 @@
       <x:c r="A22" s="31"/>
       <x:c r="B22" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>baguette</x:v>
+        <x:v>osmanthus_cake</x:v>
       </x:c>
       <x:c r="C22" s="1" t="str">
-        <x:v>baguette</x:v>
+        <x:v>osmanthus_cake</x:v>
       </x:c>
       <x:c r="D22" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8546,7 +8259,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L22" s="31" t="str">
-        <x:v>法棍</x:v>
+        <x:v>桂花糕</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -8590,10 +8303,10 @@
       <x:c r="A24" s="31"/>
       <x:c r="B24" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>cake_slice</x:v>
+        <x:v>napoleon_cake</x:v>
       </x:c>
       <x:c r="C24" s="1" t="str">
-        <x:v>cake_slice</x:v>
+        <x:v>napoleon_cake</x:v>
       </x:c>
       <x:c r="D24" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8620,17 +8333,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L24" s="31" t="str">
-        <x:v>蛋糕切角</x:v>
+        <x:v>拿破仑蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="31"/>
       <x:c r="B25" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>long_cake</x:v>
+        <x:v>honey_cake</x:v>
       </x:c>
       <x:c r="C25" s="1" t="str">
-        <x:v>long_cake</x:v>
+        <x:v>honey_cake</x:v>
       </x:c>
       <x:c r="D25" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8657,17 +8370,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L25" s="31" t="str">
-        <x:v>长条蛋糕</x:v>
+        <x:v>蜂蜜蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="31"/>
       <x:c r="B26" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_cake_01</x:v>
+        <x:v>tree_ring_cake</x:v>
       </x:c>
       <x:c r="C26" s="1" t="str">
-        <x:v>codename_cake_01</x:v>
+        <x:v>tree_ring_cake</x:v>
       </x:c>
       <x:c r="D26" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8694,17 +8407,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L26" s="31" t="str">
-        <x:v>蛋糕01</x:v>
+        <x:v>年轮蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="31"/>
       <x:c r="B27" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_transfer_01</x:v>
+        <x:v>nougat</x:v>
       </x:c>
       <x:c r="C27" s="1" t="str">
-        <x:v>codename_transfer_01</x:v>
+        <x:v>nougat</x:v>
       </x:c>
       <x:c r="D27" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8731,17 +8444,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L27" s="31" t="str">
-        <x:v>传递01</x:v>
+        <x:v>牛轧糖</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="31"/>
       <x:c r="B28" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_serving_01</x:v>
+        <x:v>hawthorn_cake</x:v>
       </x:c>
       <x:c r="C28" s="8" t="str">
-        <x:v>codename_serving_01</x:v>
+        <x:v>hawthorn_cake</x:v>
       </x:c>
       <x:c r="D28" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8768,17 +8481,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L28" s="31" t="str">
-        <x:v>份数01</x:v>
+        <x:v>山楂糕</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="31"/>
       <x:c r="B29" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_general_03</x:v>
+        <x:v>souffle</x:v>
       </x:c>
       <x:c r="C29" s="8" t="str">
-        <x:v>codename_general_03</x:v>
+        <x:v>souffle</x:v>
       </x:c>
       <x:c r="D29" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8805,17 +8518,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L29" s="31" t="str">
-        <x:v>通用03</x:v>
+        <x:v>舒芙蕾</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="31"/>
       <x:c r="B30" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_general_04</x:v>
+        <x:v>fruit_tart</x:v>
       </x:c>
       <x:c r="C30" s="8" t="str">
-        <x:v>codename_general_04</x:v>
+        <x:v>fruit_tart</x:v>
       </x:c>
       <x:c r="D30" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8842,17 +8555,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L30" s="31" t="str">
-        <x:v>通用04</x:v>
+        <x:v>水果挞</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="31"/>
       <x:c r="B31" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_general_05</x:v>
+        <x:v>strawberry_sundae</x:v>
       </x:c>
       <x:c r="C31" s="8" t="str">
-        <x:v>codename_general_05</x:v>
+        <x:v>strawberry_sundae</x:v>
       </x:c>
       <x:c r="D31" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8879,17 +8592,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L31" s="31" t="str">
-        <x:v>通用05</x:v>
+        <x:v>草莓圣代</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="31"/>
       <x:c r="B32" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_general_06</x:v>
+        <x:v>rock_sugar_pear</x:v>
       </x:c>
       <x:c r="C32" s="8" t="str">
-        <x:v>codename_general_06</x:v>
+        <x:v>rock_sugar_pear</x:v>
       </x:c>
       <x:c r="D32" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8916,17 +8629,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L32" s="31" t="str">
-        <x:v>通用06</x:v>
+        <x:v>冰糖雪梨</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="31"/>
       <x:c r="B33" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_transfer_02</x:v>
+        <x:v>popping_candy</x:v>
       </x:c>
       <x:c r="C33" s="8" t="str">
-        <x:v>codename_transfer_02</x:v>
+        <x:v>popping_candy</x:v>
       </x:c>
       <x:c r="D33" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8953,17 +8666,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L33" s="31" t="str">
-        <x:v>传递02</x:v>
+        <x:v>跳跳糖</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="31"/>
       <x:c r="B34" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_cake_02</x:v>
+        <x:v>mille_crepe_cake</x:v>
       </x:c>
       <x:c r="C34" s="8" t="str">
-        <x:v>codename_cake_02</x:v>
+        <x:v>mille_crepe_cake</x:v>
       </x:c>
       <x:c r="D34" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8990,17 +8703,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L34" s="31" t="str">
-        <x:v>蛋糕02</x:v>
+        <x:v>千层蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="31"/>
       <x:c r="B35" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_serving_02</x:v>
+        <x:v>soybean_glutinous_roll</x:v>
       </x:c>
       <x:c r="C35" s="8" t="str">
-        <x:v>codename_serving_02</x:v>
+        <x:v>soybean_glutinous_roll</x:v>
       </x:c>
       <x:c r="D35" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9027,17 +8740,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L35" s="31" t="str">
-        <x:v>份数02</x:v>
+        <x:v>驴打滚</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="31"/>
       <x:c r="B36" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>eclair</x:v>
+        <x:v>sachima</x:v>
       </x:c>
       <x:c r="C36" s="8" t="str">
-        <x:v>eclair</x:v>
+        <x:v>sachima</x:v>
       </x:c>
       <x:c r="D36" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9064,7 +8777,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L36" s="31" t="str">
-        <x:v>闪电泡芙</x:v>
+        <x:v>沙琪玛</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -9108,10 +8821,10 @@
       <x:c r="A38" s="31"/>
       <x:c r="B38" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>chocolate_strip</x:v>
+        <x:v>chocolate_wafer</x:v>
       </x:c>
       <x:c r="C38" s="8" t="str">
-        <x:v>chocolate_strip</x:v>
+        <x:v>chocolate_wafer</x:v>
       </x:c>
       <x:c r="D38" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9138,7 +8851,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L38" s="31" t="str">
-        <x:v>巧克力条</x:v>
+        <x:v>巧克力威化</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -9182,10 +8895,10 @@
       <x:c r="A40" s="31"/>
       <x:c r="B40" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_cake_03</x:v>
+        <x:v>fondant_cake</x:v>
       </x:c>
       <x:c r="C40" s="8" t="str">
-        <x:v>codename_cake_03</x:v>
+        <x:v>fondant_cake</x:v>
       </x:c>
       <x:c r="D40" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9212,17 +8925,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L40" s="31" t="str">
-        <x:v>蛋糕03</x:v>
+        <x:v>翻糖蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="31"/>
       <x:c r="B41" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_cake_04</x:v>
+        <x:v>matcha_cake</x:v>
       </x:c>
       <x:c r="C41" s="8" t="str">
-        <x:v>codename_cake_04</x:v>
+        <x:v>matcha_cake</x:v>
       </x:c>
       <x:c r="D41" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9249,17 +8962,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L41" s="31" t="str">
-        <x:v>蛋糕04</x:v>
+        <x:v>抹茶蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="31"/>
       <x:c r="B42" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_serving_03</x:v>
+        <x:v>mung_bean_cake</x:v>
       </x:c>
       <x:c r="C42" s="8" t="str">
-        <x:v>codename_serving_03</x:v>
+        <x:v>mung_bean_cake</x:v>
       </x:c>
       <x:c r="D42" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9286,17 +8999,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L42" s="31" t="str">
-        <x:v>份数03</x:v>
+        <x:v>绿豆糕</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="31"/>
       <x:c r="B43" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_serving_04</x:v>
+        <x:v>egg_yolk_pastry</x:v>
       </x:c>
       <x:c r="C43" s="8" t="str">
-        <x:v>codename_serving_04</x:v>
+        <x:v>egg_yolk_pastry</x:v>
       </x:c>
       <x:c r="D43" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9323,16 +9036,16 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L43" s="31" t="str">
-        <x:v>份数04</x:v>
+        <x:v>蛋黄酥</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="31"/>
       <x:c r="B44" s="31" t="str">
-        <x:v>codename_transfer_03</x:v>
+        <x:v>chocolate_truffle</x:v>
       </x:c>
       <x:c r="C44" s="8" t="str">
-        <x:v>codename_transfer_03</x:v>
+        <x:v>chocolate_truffle</x:v>
       </x:c>
       <x:c r="D44" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9359,16 +9072,16 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L44" t="str">
-        <x:v>传递03</x:v>
+        <x:v>松露巧克力</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="31"/>
       <x:c r="B45" s="31" t="str">
-        <x:v>codename_transfer_04</x:v>
+        <x:v>liquor_chocolate</x:v>
       </x:c>
       <x:c r="C45" s="8" t="str">
-        <x:v>codename_transfer_04</x:v>
+        <x:v>liquor_chocolate</x:v>
       </x:c>
       <x:c r="D45" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9395,7 +9108,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L45" t="str">
-        <x:v>传递04</x:v>
+        <x:v>酒心巧克力</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -9473,10 +9186,10 @@
     <x:row r="48">
       <x:c r="A48" s="31"/>
       <x:c r="B48" s="31" t="str">
-        <x:v>maple_sugar</x:v>
+        <x:v>toffee_candy</x:v>
       </x:c>
       <x:c r="C48" s="8" t="str">
-        <x:v>maple_sugar</x:v>
+        <x:v>toffee_candy</x:v>
       </x:c>
       <x:c r="D48" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9503,7 +9216,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L48" t="str">
-        <x:v>枫糖</x:v>
+        <x:v>太妃糖</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -9545,10 +9258,10 @@
     <x:row r="50">
       <x:c r="A50" s="31"/>
       <x:c r="B50" s="31" t="str">
-        <x:v>waffle</x:v>
+        <x:v>brown_sugar_steamed_cake</x:v>
       </x:c>
       <x:c r="C50" s="8" t="str">
-        <x:v>waffle</x:v>
+        <x:v>brown_sugar_steamed_cake</x:v>
       </x:c>
       <x:c r="D50" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9575,7 +9288,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L50" t="str">
-        <x:v>华夫饼</x:v>
+        <x:v>红糖发糕</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -9653,10 +9366,10 @@
     <x:row r="53">
       <x:c r="A53" s="31"/>
       <x:c r="B53" s="31" t="str">
-        <x:v>codename_general_07</x:v>
+        <x:v>fruit_shaved_ice</x:v>
       </x:c>
       <x:c r="C53" s="31" t="str">
-        <x:v>codename_general_07</x:v>
+        <x:v>fruit_shaved_ice</x:v>
       </x:c>
       <x:c r="D53" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9683,16 +9396,16 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L53" t="str">
-        <x:v>通用07</x:v>
+        <x:v>水果刨冰</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="31"/>
       <x:c r="B54" s="31" t="str">
-        <x:v>codename_general_08</x:v>
+        <x:v>coconut_milk_jelly</x:v>
       </x:c>
       <x:c r="C54" s="31" t="str">
-        <x:v>codename_general_08</x:v>
+        <x:v>coconut_milk_jelly</x:v>
       </x:c>
       <x:c r="D54" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9719,7 +9432,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L54" t="str">
-        <x:v>通用08</x:v>
+        <x:v>椰奶冻</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -9761,10 +9474,10 @@
     <x:row r="56">
       <x:c r="A56" s="31"/>
       <x:c r="B56" s="31" t="str">
-        <x:v>chocolate_sauce</x:v>
+        <x:v>nama_chocolate</x:v>
       </x:c>
       <x:c r="C56" s="31" t="str">
-        <x:v>chocolate_sauce</x:v>
+        <x:v>nama_chocolate</x:v>
       </x:c>
       <x:c r="D56" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9791,7 +9504,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L56" t="str">
-        <x:v>巧克力酱</x:v>
+        <x:v>生巧克力</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -9869,10 +9582,10 @@
     <x:row r="59">
       <x:c r="A59" s="31"/>
       <x:c r="B59" s="31" t="str">
-        <x:v>parfait</x:v>
+        <x:v>fermented_rice_balls</x:v>
       </x:c>
       <x:c r="C59" s="31" t="str">
-        <x:v>parfait</x:v>
+        <x:v>fermented_rice_balls</x:v>
       </x:c>
       <x:c r="D59" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9899,7 +9612,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L59" t="str">
-        <x:v>芭菲</x:v>
+        <x:v>酒酿圆子</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -9977,10 +9690,10 @@
     <x:row r="62">
       <x:c r="A62" s="31"/>
       <x:c r="B62" s="31" t="str">
-        <x:v>apple_pie</x:v>
+        <x:v>double_skin_milk</x:v>
       </x:c>
       <x:c r="C62" s="31" t="str">
-        <x:v>apple_pie</x:v>
+        <x:v>double_skin_milk</x:v>
       </x:c>
       <x:c r="D62" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -10007,7 +9720,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L62" t="str">
-        <x:v>苹果派</x:v>
+        <x:v>双皮奶</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -11210,14 +10923,15 @@
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.799999237060547"/>
   <x:cols>
     <x:col min="1" max="1" width="13.076923370361328" style="26" customWidth="1"/>
-    <x:col min="2" max="2" width="23.230770111083984" style="26" customWidth="1"/>
+    <x:col min="2" max="2" width="240" style="26" hidden="0" customWidth="1"/>
     <x:col min="3" max="4" width="53.230770111083984" style="26" customWidth="1"/>
     <x:col min="5" max="6" width="9" style="26" customWidth="0"/>
-    <x:col min="7" max="7" width="36.38461685180664" style="26" customWidth="1"/>
-    <x:col min="8" max="8" width="28.923076629638672" style="26" customWidth="1"/>
+    <x:col min="7" max="7" width="240" style="26" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="240" style="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="9" style="26" customWidth="0"/>
-    <x:col min="10" max="10" width="17.30769157409668" style="26" customWidth="1"/>
+    <x:col min="10" max="10" width="220" style="26" hidden="0" customWidth="1"/>
     <x:col min="11" max="16384" width="9" style="26" customWidth="0"/>
+    <x:col min="3" max="3" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -11261,14 +10975,14 @@
       <x:c r="C4" s="26" t="str">
         <x:v>sk_arrow_cookie_1_1</x:v>
       </x:c>
-      <x:c r="G4" s="26" t="s">
+      <x:c r="G4" s="26" t="str">
+        <x:v>sk_arrow_cookie_1_1</x:v>
+      </x:c>
+      <x:c r="J4" s="26" t="str">
+        <x:v>arrow_cookie_1</x:v>
+      </x:c>
+      <x:c r="K4" s="26" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="J4" s="26" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="K4" s="26" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -11279,14 +10993,14 @@
       <x:c r="C5" s="26" t="str">
         <x:v>sk_arrow_cookie_2_1</x:v>
       </x:c>
-      <x:c r="G5" s="26" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J5" s="26" t="s">
-        <x:v>58</x:v>
+      <x:c r="G5" s="26" t="str">
+        <x:v>sk_arrow_cookie_2_1</x:v>
+      </x:c>
+      <x:c r="J5" s="26" t="str">
+        <x:v>arrow_cookie_2</x:v>
       </x:c>
       <x:c r="K5" s="26" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -11297,14 +11011,14 @@
       <x:c r="C6" s="26" t="str">
         <x:v>sk_arrow_cookie_3_1</x:v>
       </x:c>
-      <x:c r="G6" s="26" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="J6" s="26" t="s">
-        <x:v>61</x:v>
+      <x:c r="G6" s="26" t="str">
+        <x:v>sk_arrow_cookie_3_1</x:v>
+      </x:c>
+      <x:c r="J6" s="26" t="str">
+        <x:v>arrow_cookie_3</x:v>
       </x:c>
       <x:c r="K6" s="26" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -11315,14 +11029,14 @@
       <x:c r="C7" s="26" t="str">
         <x:v>sk_arrow_cookie_4_1</x:v>
       </x:c>
-      <x:c r="G7" s="26" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="J7" s="26" t="s">
-        <x:v>64</x:v>
+      <x:c r="G7" s="26" t="str">
+        <x:v>sk_arrow_cookie_4_1</x:v>
+      </x:c>
+      <x:c r="J7" s="26" t="str">
+        <x:v>arrow_cookie_4</x:v>
       </x:c>
       <x:c r="K7" s="26" t="s">
-        <x:v>65</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -11333,14 +11047,14 @@
       <x:c r="C8" s="26" t="str">
         <x:v>sk_jelly_1</x:v>
       </x:c>
-      <x:c r="G8" s="26" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="J8" s="26" t="s">
-        <x:v>67</x:v>
+      <x:c r="G8" s="26" t="str">
+        <x:v>sk_jelly_1</x:v>
+      </x:c>
+      <x:c r="J8" s="26" t="str">
+        <x:v>jelly</x:v>
       </x:c>
       <x:c r="K8" s="26" t="s">
-        <x:v>68</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -11351,14 +11065,14 @@
       <x:c r="C9" s="26" t="str">
         <x:v>sk_cupcake_1</x:v>
       </x:c>
-      <x:c r="G9" s="26" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="J9" s="26" t="s">
-        <x:v>70</x:v>
+      <x:c r="G9" s="26" t="str">
+        <x:v>sk_cupcake_1</x:v>
+      </x:c>
+      <x:c r="J9" s="26" t="str">
+        <x:v>cupcake</x:v>
       </x:c>
       <x:c r="K9" s="26" t="s">
-        <x:v>71</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -11369,14 +11083,14 @@
       <x:c r="C10" s="26" t="str">
         <x:v>sk_eggtart_1</x:v>
       </x:c>
-      <x:c r="G10" s="26" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="J10" s="26" t="s">
-        <x:v>73</x:v>
+      <x:c r="G10" s="26" t="str">
+        <x:v>sk_eggtart_1</x:v>
+      </x:c>
+      <x:c r="J10" s="26" t="str">
+        <x:v>eggtart</x:v>
       </x:c>
       <x:c r="K10" s="26" t="s">
-        <x:v>74</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -11387,17 +11101,17 @@
       <x:c r="C11" s="26" t="str">
         <x:v>sk_sugarbean_1|sk_sugarbean_2</x:v>
       </x:c>
-      <x:c r="G11" s="26" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H11" s="26" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="J11" s="26" t="s">
-        <x:v>77</x:v>
+      <x:c r="G11" s="26" t="str">
+        <x:v>sk_sugarbean_1</x:v>
+      </x:c>
+      <x:c r="H11" s="26" t="str">
+        <x:v>sk_sugarbean_2</x:v>
+      </x:c>
+      <x:c r="J11" s="26" t="str">
+        <x:v>sugarbean</x:v>
       </x:c>
       <x:c r="K11" s="26" t="s">
-        <x:v>78</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -11408,17 +11122,17 @@
       <x:c r="C12" s="26" t="str">
         <x:v>sk_cheesecake_1|sk_cheesecake_2</x:v>
       </x:c>
-      <x:c r="G12" s="26" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H12" s="26" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="J12" s="26" t="s">
-        <x:v>81</x:v>
+      <x:c r="G12" s="26" t="str">
+        <x:v>sk_cheesecake_1</x:v>
+      </x:c>
+      <x:c r="H12" s="26" t="str">
+        <x:v>sk_cheesecake_2</x:v>
+      </x:c>
+      <x:c r="J12" s="26" t="str">
+        <x:v>cheesecake</x:v>
       </x:c>
       <x:c r="K12" s="26" t="s">
-        <x:v>82</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -11429,35 +11143,35 @@
       <x:c r="C13" s="26" t="str">
         <x:v>sk_mousse_1</x:v>
       </x:c>
-      <x:c r="G13" s="26" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="J13" s="26" t="s">
-        <x:v>84</x:v>
+      <x:c r="G13" s="26" t="str">
+        <x:v>sk_mousse_1</x:v>
+      </x:c>
+      <x:c r="J13" s="26" t="str">
+        <x:v>mousse</x:v>
       </x:c>
       <x:c r="K13" s="26" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14"/>
       <x:c r="B14" s="26" t="str">
-        <x:v>sk_codename_general_01</x:v>
+        <x:v>sk_caramel_pudding</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>sk_codename_general_01_1</x:v>
-      </x:c>
-      <x:c r="G14" s="26" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H14" s="26" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="J14" s="26" t="s">
-        <x:v>88</x:v>
+        <x:v>sk_caramel_pudding_1</x:v>
+      </x:c>
+      <x:c r="G14" s="26" t="str">
+        <x:v>sk_fruit_candy_1</x:v>
+      </x:c>
+      <x:c r="H14" s="26" t="str">
+        <x:v>sk_fruit_candy_2</x:v>
+      </x:c>
+      <x:c r="J14" s="26" t="str">
+        <x:v>fruit_candy</x:v>
       </x:c>
       <x:c r="K14" s="26" t="s">
-        <x:v>89</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -11468,17 +11182,17 @@
       <x:c r="C15" s="26" t="str">
         <x:v>sk_fruit_candy_1|sk_fruit_candy_2</x:v>
       </x:c>
-      <x:c r="G15" s="26" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H15" s="26" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="J15" s="26" t="s">
-        <x:v>92</x:v>
+      <x:c r="G15" s="26" t="str">
+        <x:v>sk_choco_bar_1</x:v>
+      </x:c>
+      <x:c r="H15" s="26" t="str">
+        <x:v>sk_choco_bar_2</x:v>
+      </x:c>
+      <x:c r="J15" s="26" t="str">
+        <x:v>choco_bar</x:v>
       </x:c>
       <x:c r="K15" s="26" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -11489,14 +11203,14 @@
       <x:c r="C16" s="26" t="str">
         <x:v>sk_choco_bar_1|sk_choco_bar_2</x:v>
       </x:c>
-      <x:c r="G16" s="26" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="J16" s="26" t="s">
-        <x:v>95</x:v>
+      <x:c r="G16" s="26" t="str">
+        <x:v>sk_mochi_1</x:v>
+      </x:c>
+      <x:c r="J16" s="26" t="str">
+        <x:v>mochi</x:v>
       </x:c>
       <x:c r="K16" s="26" t="s">
-        <x:v>96</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -11507,17 +11221,17 @@
       <x:c r="C17" s="26" t="str">
         <x:v>sk_mochi_1</x:v>
       </x:c>
-      <x:c r="G17" s="26" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H17" s="26" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="J17" s="26" t="s">
-        <x:v>99</x:v>
+      <x:c r="G17" s="26" t="str">
+        <x:v>sk_cup_cake_1</x:v>
+      </x:c>
+      <x:c r="H17" s="26" t="str">
+        <x:v>sk_cup_cake_2</x:v>
+      </x:c>
+      <x:c r="J17" s="26" t="str">
+        <x:v>cup_cake</x:v>
       </x:c>
       <x:c r="K17" s="26" t="s">
-        <x:v>100</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -11528,50 +11242,50 @@
       <x:c r="C18" s="26" t="str">
         <x:v>sk_cup_cake_1|sk_cup_cake_2</x:v>
       </x:c>
-      <x:c r="G18" s="26" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="J18" s="26" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="K18" s="26" t="s">
-        <x:v>103</x:v>
+      <x:c r="G18" s="26" t="str">
+        <x:v>sk_cream_puff_1</x:v>
+      </x:c>
+      <x:c r="J18" s="26" t="str">
+        <x:v>cream_puff</x:v>
+      </x:c>
+      <x:c r="K18" s="26" t="str">
+        <x:v>奶油泡芙</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
       <x:c r="B19" s="26" t="str">
-        <x:v>sk_cream</x:v>
+        <x:v>sk_cream_puff</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
-        <x:v>sk_cream_1</x:v>
-      </x:c>
-      <x:c r="G19" s="26" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="J19" s="26" t="s">
-        <x:v>105</x:v>
+        <x:v>sk_cream_puff_1</x:v>
+      </x:c>
+      <x:c r="G19" s="26" t="str">
+        <x:v>sk_eggroll_1</x:v>
+      </x:c>
+      <x:c r="J19" s="26" t="str">
+        <x:v>eggroll</x:v>
       </x:c>
       <x:c r="K19" s="26" t="s">
-        <x:v>106</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20"/>
       <x:c r="B20" s="26" t="str">
-        <x:v>sk_codename_general_02</x:v>
+        <x:v>sk_ice_cream</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
-        <x:v>sk_codename_general_02_1</x:v>
-      </x:c>
-      <x:c r="G20" s="26" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="J20" s="26" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="K20" s="26" t="s">
-        <x:v>109</x:v>
+        <x:v>sk_ice_cream_1</x:v>
+      </x:c>
+      <x:c r="G20" s="26" t="str">
+        <x:v>sk_osmanthus_cake_1</x:v>
+      </x:c>
+      <x:c r="J20" s="26" t="str">
+        <x:v>osmanthus_cake</x:v>
+      </x:c>
+      <x:c r="K20" s="26" t="str">
+        <x:v>桂花糕</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -11582,38 +11296,38 @@
       <x:c r="C21" s="26" t="str">
         <x:v>sk_eggroll_1</x:v>
       </x:c>
-      <x:c r="G21" s="26" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H21" s="26" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="J21" s="26" t="s">
-        <x:v>112</x:v>
+      <x:c r="G21" s="26" t="str">
+        <x:v>sk_tanghulu_1</x:v>
+      </x:c>
+      <x:c r="H21" s="26" t="str">
+        <x:v>sk_tanghulu_2</x:v>
+      </x:c>
+      <x:c r="J21" s="26" t="str">
+        <x:v>tanghulu</x:v>
       </x:c>
       <x:c r="K21" s="26" t="s">
-        <x:v>113</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22"/>
       <x:c r="B22" s="26" t="str">
-        <x:v>sk_baguette</x:v>
+        <x:v>sk_osmanthus_cake</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>sk_baguette_1</x:v>
-      </x:c>
-      <x:c r="G22" s="26" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="H22" s="26" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="J22" s="26" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="K22" s="26" t="s">
-        <x:v>117</x:v>
+        <x:v>sk_osmanthus_cake_1</x:v>
+      </x:c>
+      <x:c r="G22" s="26" t="str">
+        <x:v>sk_napoleon_cake_1</x:v>
+      </x:c>
+      <x:c r="H22" s="26" t="str">
+        <x:v>sk_napoleon_cake_2</x:v>
+      </x:c>
+      <x:c r="J22" s="26" t="str">
+        <x:v>napoleon_cake</x:v>
+      </x:c>
+      <x:c r="K22" s="26" t="str">
+        <x:v>拿破仑蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -11624,269 +11338,269 @@
       <x:c r="C23" s="26" t="str">
         <x:v>sk_tanghulu_1|sk_tanghulu_2</x:v>
       </x:c>
-      <x:c r="G23" s="26" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="H23" s="26" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="J23" s="26" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="K23" s="26" t="s">
-        <x:v>121</x:v>
+      <x:c r="G23" s="26" t="str">
+        <x:v>sk_honey_cake_1</x:v>
+      </x:c>
+      <x:c r="H23" s="26" t="str">
+        <x:v>sk_honey_cake_2</x:v>
+      </x:c>
+      <x:c r="J23" s="26" t="str">
+        <x:v>honey_cake</x:v>
+      </x:c>
+      <x:c r="K23" s="26" t="str">
+        <x:v>蜂蜜蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24"/>
       <x:c r="B24" s="26" t="str">
-        <x:v>sk_cake_slice</x:v>
+        <x:v>sk_napoleon_cake</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>sk_cake_slice_1|sk_cake_slice_2</x:v>
-      </x:c>
-      <x:c r="G24" s="26" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="J24" s="26" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="K24" s="26" t="s">
-        <x:v>124</x:v>
+        <x:v>sk_napoleon_cake_1|sk_napoleon_cake_2</x:v>
+      </x:c>
+      <x:c r="G24" s="26" t="str">
+        <x:v>sk_sachima_1</x:v>
+      </x:c>
+      <x:c r="J24" s="26" t="str">
+        <x:v>sachima</x:v>
+      </x:c>
+      <x:c r="K24" s="26" t="str">
+        <x:v>沙琪玛</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25"/>
       <x:c r="B25" s="26" t="str">
-        <x:v>sk_long_cake</x:v>
+        <x:v>sk_honey_cake</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
-        <x:v>sk_long_cake_1|sk_long_cake_2</x:v>
-      </x:c>
-      <x:c r="G25" s="26" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="J25" s="26" t="s">
-        <x:v>126</x:v>
+        <x:v>sk_honey_cake_1|sk_honey_cake_2</x:v>
+      </x:c>
+      <x:c r="G25" s="26" t="str">
+        <x:v>sk_gummy_1</x:v>
+      </x:c>
+      <x:c r="J25" s="26" t="str">
+        <x:v>gummy</x:v>
       </x:c>
       <x:c r="K25" s="26" t="s">
-        <x:v>127</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26"/>
       <x:c r="B26" s="26" t="str">
-        <x:v>sk_codename_cake_01</x:v>
+        <x:v>sk_tree_ring_cake</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
-        <x:v>sk_codename_cake_01_1</x:v>
-      </x:c>
-      <x:c r="G26" s="26" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="H26" s="26" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="J26" s="26" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="K26" s="26" t="s">
-        <x:v>131</x:v>
+        <x:v>sk_tree_ring_cake_1</x:v>
+      </x:c>
+      <x:c r="G26" s="26" t="str">
+        <x:v>sk_chocolate_wafer_1</x:v>
+      </x:c>
+      <x:c r="H26" s="26" t="str">
+        <x:v>sk_chocolate_wafer_2</x:v>
+      </x:c>
+      <x:c r="J26" s="26" t="str">
+        <x:v>chocolate_wafer</x:v>
+      </x:c>
+      <x:c r="K26" s="26" t="str">
+        <x:v>巧克力威化</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27"/>
       <x:c r="B27" s="26" t="str">
-        <x:v>sk_codename_transfer_01</x:v>
+        <x:v>sk_nougat</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
-        <x:v>sk_codename_transfer_01_1|sk_codename_transfer_01_2</x:v>
-      </x:c>
-      <x:c r="G27" s="26" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H27" s="26" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="J27" s="26" t="s">
-        <x:v>134</x:v>
+        <x:v>sk_nougat_1|sk_nougat_2</x:v>
+      </x:c>
+      <x:c r="G27" s="26" t="str">
+        <x:v>sk_cake_roll_1</x:v>
+      </x:c>
+      <x:c r="H27" s="26" t="str">
+        <x:v>sk_cake_roll_2</x:v>
+      </x:c>
+      <x:c r="J27" s="26" t="str">
+        <x:v>cake_roll</x:v>
       </x:c>
       <x:c r="K27" s="26" t="s">
-        <x:v>135</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28"/>
       <x:c r="B28" s="26" t="str">
-        <x:v>sk_codename_serving_01</x:v>
+        <x:v>sk_hawthorn_cake</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>sk_codename_serving_01_1</x:v>
-      </x:c>
-      <x:c r="G28" s="26" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="J28" s="26" t="s">
-        <x:v>137</x:v>
+        <x:v>sk_hawthorn_cake_1</x:v>
+      </x:c>
+      <x:c r="G28" s="26" t="str">
+        <x:v>sk_palmier_1</x:v>
+      </x:c>
+      <x:c r="J28" s="26" t="str">
+        <x:v>palmier</x:v>
       </x:c>
       <x:c r="K28" s="26" t="s">
-        <x:v>138</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29"/>
       <x:c r="B29" s="26" t="str">
-        <x:v>sk_codename_general_03</x:v>
+        <x:v>sk_souffle</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
-        <x:v>sk_codename_general_03_1</x:v>
-      </x:c>
-      <x:c r="G29" s="26" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="J29" s="26" t="s">
-        <x:v>140</x:v>
+        <x:v>sk_souffle_1</x:v>
+      </x:c>
+      <x:c r="G29" s="26" t="str">
+        <x:v>sk_chiffion_1</x:v>
+      </x:c>
+      <x:c r="J29" s="26" t="str">
+        <x:v>chiffion</x:v>
       </x:c>
       <x:c r="K29" s="26" t="s">
-        <x:v>141</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30"/>
       <x:c r="B30" s="26" t="str">
-        <x:v>sk_codename_general_04</x:v>
+        <x:v>sk_fruit_tart</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>sk_codename_general_04_1</x:v>
-      </x:c>
-      <x:c r="G30" s="26" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="J30" s="26" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="K30" s="26" t="s">
-        <x:v>144</x:v>
+        <x:v>sk_fruit_tart_1</x:v>
+      </x:c>
+      <x:c r="G30" s="26" t="str">
+        <x:v>sk_toffee_candy_1</x:v>
+      </x:c>
+      <x:c r="J30" s="26" t="str">
+        <x:v>toffee_candy</x:v>
+      </x:c>
+      <x:c r="K30" s="26" t="str">
+        <x:v>太妃糖</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31"/>
       <x:c r="B31" s="26" t="str">
-        <x:v>sk_codename_general_05</x:v>
+        <x:v>sk_strawberry_sundae</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
-        <x:v>sk_codename_general_05_1</x:v>
-      </x:c>
-      <x:c r="G31" s="26" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="J31" s="26" t="s">
-        <x:v>146</x:v>
+        <x:v>sk_strawberry_sundae_1</x:v>
+      </x:c>
+      <x:c r="G31" s="26" t="str">
+        <x:v>sk_taosu_1</x:v>
+      </x:c>
+      <x:c r="J31" s="26" t="str">
+        <x:v>taosu</x:v>
       </x:c>
       <x:c r="K31" s="26" t="s">
-        <x:v>147</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32"/>
       <x:c r="B32" s="26" t="str">
-        <x:v>sk_codename_general_06</x:v>
+        <x:v>sk_rock_sugar_pear</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>sk_codename_general_06_1|sk_codename_general_06_2</x:v>
-      </x:c>
-      <x:c r="G32" s="26" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="J32" s="26" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="K32" s="26" t="s">
-        <x:v>150</x:v>
+        <x:v>sk_rock_sugar_pear_1|sk_rock_sugar_pear_2</x:v>
+      </x:c>
+      <x:c r="G32" s="26" t="str">
+        <x:v>sk_brown_sugar_steamed_cake_1</x:v>
+      </x:c>
+      <x:c r="J32" s="26" t="str">
+        <x:v>brown_sugar_steamed_cake</x:v>
+      </x:c>
+      <x:c r="K32" s="26" t="str">
+        <x:v>红糖发糕</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33"/>
       <x:c r="B33" s="26" t="str">
-        <x:v>sk_codename_transfer_02</x:v>
+        <x:v>sk_popping_candy</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>sk_codename_transfer_02_1</x:v>
-      </x:c>
-      <x:c r="G33" s="26" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H33" s="26" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="J33" s="26" t="s">
-        <x:v>153</x:v>
+        <x:v>sk_popping_candy_1</x:v>
+      </x:c>
+      <x:c r="G33" s="26" t="str">
+        <x:v>sk_cream_cake_1</x:v>
+      </x:c>
+      <x:c r="H33" s="26" t="str">
+        <x:v>sk_cream_cake_2</x:v>
+      </x:c>
+      <x:c r="J33" s="26" t="str">
+        <x:v>cream_cake</x:v>
       </x:c>
       <x:c r="K33" s="26" t="s">
-        <x:v>154</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34"/>
       <x:c r="B34" s="26" t="str">
-        <x:v>sk_codename_cake_02</x:v>
+        <x:v>sk_mille_crepe_cake</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>sk_codename_cake_02_1</x:v>
-      </x:c>
-      <x:c r="G34" s="26" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H34" s="26" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="J34" s="26" t="s">
-        <x:v>157</x:v>
+        <x:v>sk_mille_crepe_cake_1</x:v>
+      </x:c>
+      <x:c r="G34" s="26" t="str">
+        <x:v>sk_candycane_1</x:v>
+      </x:c>
+      <x:c r="H34" s="26" t="str">
+        <x:v>sk_candycane_2</x:v>
+      </x:c>
+      <x:c r="J34" s="26" t="str">
+        <x:v>candycane</x:v>
       </x:c>
       <x:c r="K34" s="26" t="s">
-        <x:v>158</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35"/>
       <x:c r="B35" s="26" t="str">
-        <x:v>sk_codename_serving_02</x:v>
+        <x:v>sk_soybean_glutinous_roll</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>sk_codename_serving_02_1</x:v>
-      </x:c>
-      <x:c r="G35" s="26" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="H35" s="26" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="J35" s="26" t="s">
-        <x:v>161</x:v>
+        <x:v>sk_soybean_glutinous_roll_1</x:v>
+      </x:c>
+      <x:c r="G35" s="26" t="str">
+        <x:v>sk_black_forest_cake_1</x:v>
+      </x:c>
+      <x:c r="H35" s="26" t="str">
+        <x:v>sk_black_forest_cake_2</x:v>
+      </x:c>
+      <x:c r="J35" s="26" t="str">
+        <x:v>black_forest_cake</x:v>
       </x:c>
       <x:c r="K35" s="26" t="s">
-        <x:v>162</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36"/>
       <x:c r="B36" s="26" t="str">
-        <x:v>sk_eclair</x:v>
+        <x:v>sk_sachima</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>sk_eclair_1</x:v>
-      </x:c>
-      <x:c r="G36" s="26" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="H36" s="26" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="J36" s="26" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="K36" s="26" t="s">
-        <x:v>166</x:v>
+        <x:v>sk_sachima_1</x:v>
+      </x:c>
+      <x:c r="G36" s="26" t="str">
+        <x:v>sk_nama_chocolate_1</x:v>
+      </x:c>
+      <x:c r="H36" s="26" t="str">
+        <x:v>sk_nama_chocolate_2</x:v>
+      </x:c>
+      <x:c r="J36" s="26" t="str">
+        <x:v>nama_chocolate</x:v>
+      </x:c>
+      <x:c r="K36" s="26" t="str">
+        <x:v>生巧克力</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -11897,35 +11611,35 @@
       <x:c r="C37" s="26" t="str">
         <x:v>sk_gummy_1</x:v>
       </x:c>
-      <x:c r="G37" s="26" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="J37" s="26" t="s">
-        <x:v>168</x:v>
+      <x:c r="G37" s="26" t="str">
+        <x:v>sk_mango_sago_1</x:v>
+      </x:c>
+      <x:c r="J37" s="26" t="str">
+        <x:v>mango_sago</x:v>
       </x:c>
       <x:c r="K37" s="26" t="s">
-        <x:v>169</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38"/>
       <x:c r="B38" s="26" t="str">
-        <x:v>sk_chocolate_strip</x:v>
+        <x:v>sk_chocolate_wafer</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>sk_chocolate_strip_1|sk_chocolate_strip_2</x:v>
-      </x:c>
-      <x:c r="G38" s="26" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H38" s="26" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="J38" s="26" t="s">
-        <x:v>172</x:v>
+        <x:v>sk_chocolate_wafer_1|sk_chocolate_wafer_2</x:v>
+      </x:c>
+      <x:c r="G38" s="26" t="str">
+        <x:v>sk_fruit_cake_1</x:v>
+      </x:c>
+      <x:c r="H38" s="26" t="str">
+        <x:v>sk_fruit_cake_2</x:v>
+      </x:c>
+      <x:c r="J38" s="26" t="str">
+        <x:v>fruit_cake</x:v>
       </x:c>
       <x:c r="K38" s="26" t="s">
-        <x:v>173</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -11936,107 +11650,107 @@
       <x:c r="C39" s="26" t="str">
         <x:v>sk_cake_roll_1|sk_cake_roll_2</x:v>
       </x:c>
-      <x:c r="G39" s="26" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="J39" s="26" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="K39" s="26" t="s">
-        <x:v>176</x:v>
+      <x:c r="G39" s="26" t="str">
+        <x:v>sk_fermented_rice_balls_1</x:v>
+      </x:c>
+      <x:c r="J39" s="26" t="str">
+        <x:v>fermented_rice_balls</x:v>
+      </x:c>
+      <x:c r="K39" s="26" t="str">
+        <x:v>酒酿圆子</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40"/>
       <x:c r="B40" s="26" t="str">
-        <x:v>sk_codename_cake_03</x:v>
+        <x:v>sk_fondant_cake</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
-        <x:v>sk_codename_cake_03_1|sk_codename_cake_03_2</x:v>
-      </x:c>
-      <x:c r="G40" s="26" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="J40" s="26" t="s">
-        <x:v>178</x:v>
+        <x:v>sk_fondant_cake_1|sk_fondant_cake_2</x:v>
+      </x:c>
+      <x:c r="G40" s="26" t="str">
+        <x:v>sk_marshmallow_1</x:v>
+      </x:c>
+      <x:c r="J40" s="26" t="str">
+        <x:v>marshmallow</x:v>
       </x:c>
       <x:c r="K40" s="26" t="s">
-        <x:v>179</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41"/>
       <x:c r="B41" s="26" t="str">
-        <x:v>sk_codename_cake_04</x:v>
+        <x:v>sk_matcha_cake</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>sk_codename_cake_04_1</x:v>
-      </x:c>
-      <x:c r="G41" s="26" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="H41" s="26" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="J41" s="26" t="s">
-        <x:v>182</x:v>
+        <x:v>sk_matcha_cake_1</x:v>
+      </x:c>
+      <x:c r="G41" s="26" t="str">
+        <x:v>sk_big_lollipop_1</x:v>
+      </x:c>
+      <x:c r="H41" s="26" t="str">
+        <x:v>sk_big_lollipop_2</x:v>
+      </x:c>
+      <x:c r="J41" s="26" t="str">
+        <x:v>big_lollipop</x:v>
       </x:c>
       <x:c r="K41" s="26" t="s">
-        <x:v>183</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42"/>
       <x:c r="B42" s="26" t="str">
-        <x:v>sk_codename_serving_03</x:v>
+        <x:v>sk_mung_bean_cake</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>sk_codename_serving_03_1</x:v>
-      </x:c>
-      <x:c r="G42" s="26" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="J42" s="26" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="K42" s="26" t="s">
-        <x:v>186</x:v>
+        <x:v>sk_mung_bean_cake_1</x:v>
+      </x:c>
+      <x:c r="G42" s="26" t="str">
+        <x:v>sk_double_skin_milk_1</x:v>
+      </x:c>
+      <x:c r="J42" s="26" t="str">
+        <x:v>double_skin_milk</x:v>
+      </x:c>
+      <x:c r="K42" s="26" t="str">
+        <x:v>双皮奶</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43"/>
       <x:c r="B43" s="26" t="str">
-        <x:v>sk_codename_serving_04</x:v>
+        <x:v>sk_egg_yolk_pastry</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
-        <x:v>sk_codename_serving_04_1</x:v>
-      </x:c>
-      <x:c r="G43" s="26" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="J43" s="26" t="s">
-        <x:v>188</x:v>
+        <x:v>sk_egg_yolk_pastry_1</x:v>
+      </x:c>
+      <x:c r="G43" s="26" t="str">
+        <x:v>sk_double_cake_1</x:v>
+      </x:c>
+      <x:c r="J43" s="26" t="str">
+        <x:v>double_cake</x:v>
       </x:c>
       <x:c r="K43" s="26" t="s">
-        <x:v>189</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44"/>
       <x:c r="B44" s="26" t="str">
-        <x:v>sk_codename_transfer_03</x:v>
+        <x:v>sk_chocolate_truffle</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>sk_codename_transfer_03_1</x:v>
+        <x:v>sk_chocolate_truffle_1</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45"/>
       <x:c r="B45" s="26" t="str">
-        <x:v>sk_codename_transfer_04</x:v>
+        <x:v>sk_liquor_chocolate</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>sk_codename_transfer_04_1|sk_codename_transfer_04_2</x:v>
+        <x:v>sk_liquor_chocolate_1|sk_liquor_chocolate_2</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -12060,10 +11774,10 @@
     <x:row r="48">
       <x:c r="A48"/>
       <x:c r="B48" s="26" t="str">
-        <x:v>sk_maple_sugar</x:v>
+        <x:v>sk_toffee_candy</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>sk_maple_sugar_1</x:v>
+        <x:v>sk_toffee_candy_1</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -12078,10 +11792,10 @@
     <x:row r="50">
       <x:c r="A50"/>
       <x:c r="B50" s="26" t="str">
-        <x:v>sk_waffle</x:v>
+        <x:v>sk_brown_sugar_steamed_cake</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
-        <x:v>sk_waffle_1</x:v>
+        <x:v>sk_brown_sugar_steamed_cake_1</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -12105,19 +11819,19 @@
     <x:row r="53">
       <x:c r="A53"/>
       <x:c r="B53" s="26" t="str">
-        <x:v>sk_codename_general_07</x:v>
+        <x:v>sk_fruit_shaved_ice</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
-        <x:v>sk_codename_general_07_1</x:v>
+        <x:v>sk_fruit_shaved_ice_1</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54"/>
       <x:c r="B54" s="26" t="str">
-        <x:v>sk_codename_general_08</x:v>
+        <x:v>sk_coconut_milk_jelly</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
-        <x:v>sk_codename_general_08_1</x:v>
+        <x:v>sk_coconut_milk_jelly_1</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -12132,10 +11846,10 @@
     <x:row r="56">
       <x:c r="A56"/>
       <x:c r="B56" s="26" t="str">
-        <x:v>sk_chocolate_sauce</x:v>
+        <x:v>sk_nama_chocolate</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
-        <x:v>sk_chocolate_sauce_1|sk_chocolate_sauce_2</x:v>
+        <x:v>sk_nama_chocolate_1|sk_nama_chocolate_2</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -12159,10 +11873,10 @@
     <x:row r="59">
       <x:c r="A59"/>
       <x:c r="B59" s="26" t="str">
-        <x:v>sk_parfait</x:v>
+        <x:v>sk_fermented_rice_balls</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
-        <x:v>sk_parfait_1</x:v>
+        <x:v>sk_fermented_rice_balls_1</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -12186,10 +11900,10 @@
     <x:row r="62">
       <x:c r="A62"/>
       <x:c r="B62" s="26" t="str">
-        <x:v>sk_apple_pie</x:v>
+        <x:v>sk_double_skin_milk</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
-        <x:v>sk_apple_pie_1</x:v>
+        <x:v>sk_double_skin_milk_1</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -12234,19 +11948,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="I1" t="s">
         <x:v>9</x:v>
@@ -12258,28 +11972,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="I2" s="29" t="s">
-        <x:v>202</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="J2"/>
     </x:row>
@@ -12297,13 +12011,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
         <x:v>23</x:v>
@@ -12315,62 +12029,62 @@
     </x:row>
     <x:row r="4">
       <x:c r="B4" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="J4" t="s">
-        <x:v>210</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="B5" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>40</x:v>
       </x:c>
       <x:c r="J5" t="s">
-        <x:v>215</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34">
       <x:c r="B6" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D6" s="18" t="s">
-        <x:v>218</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>219</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G6" s="1">
         <x:v>10</x:v>
@@ -12379,48 +12093,48 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="J6" t="s">
-        <x:v>220</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="B7" s="1" t="s">
-        <x:v>221</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="J7" t="s">
-        <x:v>225</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34">
       <x:c r="B8" s="28" t="s">
-        <x:v>226</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C8" s="28" t="s">
-        <x:v>227</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D8" s="12" t="s">
-        <x:v>228</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E8" s="28" t="s">
-        <x:v>229</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="F8" s="28"/>
       <x:c r="G8" s="28" t="s">
-        <x:v>230</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H8" s="28"/>
       <x:c r="I8">
@@ -12430,16 +12144,16 @@
     </x:row>
     <x:row r="9" ht="34">
       <x:c r="B9" s="28" t="s">
-        <x:v>231</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C9" s="28" t="s">
-        <x:v>232</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D9" s="12" t="s">
-        <x:v>233</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E9" s="28" t="s">
-        <x:v>234</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F9" s="28"/>
       <x:c r="G9" s="28">
@@ -12602,22 +12316,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>235</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>236</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E1" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>191</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>237</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H1" t="s">
-        <x:v>190</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -12625,25 +12339,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>238</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C2" t="s">
-        <x:v>239</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D2" t="s">
-        <x:v>240</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E2" t="s">
-        <x:v>241</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F2" t="s">
-        <x:v>242</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G2" t="s">
-        <x:v>243</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H2" t="s">
-        <x:v>244</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -12663,7 +12377,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="F3" t="s">
-        <x:v>245</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G3" t="s">
         <x:v>48</x:v>
@@ -12674,7 +12388,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="B4" t="s">
-        <x:v>246</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C4">
         <x:v>0</x:v>
@@ -12683,21 +12397,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E4" t="s">
-        <x:v>247</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F4" t="s">
-        <x:v>248</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G4">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H4" t="s">
-        <x:v>249</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="B5" t="s">
-        <x:v>250</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C5">
         <x:v>1</x:v>
@@ -12706,16 +12420,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E5" t="s">
-        <x:v>247</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F5" t="s">
-        <x:v>251</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G5">
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="H5" t="s">
-        <x:v>252</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="L5">
         <x:v>8</x:v>
@@ -12726,7 +12440,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="B6" t="s">
-        <x:v>253</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C6">
         <x:v>2</x:v>
@@ -12735,16 +12449,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E6" t="s">
-        <x:v>247</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F6" t="s">
-        <x:v>254</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G6">
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="H6" t="s">
-        <x:v>255</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12757,7 +12471,7 @@
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.799999237060547"/>
   <x:cols>
     <x:col min="1" max="1" width="13.076923370361328" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="36.38461685180664" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="255" style="1" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12.15384578704834" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="19.769229888916016" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="16.384614944458008" style="1" customWidth="1"/>
@@ -12785,46 +12499,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>257</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="R1" s="26"/>
       <x:c r="S1" s="26"/>
@@ -12835,49 +12549,49 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>271</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>275</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>277</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>278</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="M2" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="N2" s="1" t="s">
-        <x:v>281</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="O2" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="P2" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="R2" s="26"/>
       <x:c r="S2" s="26"/>
@@ -12891,34 +12605,34 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="K3" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="L3" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M3" s="1" t="s">
         <x:v>26</x:v>
@@ -12933,10 +12647,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="R3" s="26" t="s">
-        <x:v>289</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="S3" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="T3" s="26"/>
     </x:row>
@@ -12984,10 +12698,10 @@
       <x:c r="P4" s="18"/>
       <x:c r="Q4" s="26"/>
       <x:c r="R4" s="26" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="S4" s="27" t="s">
-        <x:v>290</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="T4" s="26"/>
     </x:row>
@@ -13035,10 +12749,10 @@
       <x:c r="P5" s="18"/>
       <x:c r="Q5" s="26"/>
       <x:c r="R5" s="26" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="S5" s="27" t="s">
-        <x:v>291</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="T5" s="26"/>
     </x:row>
@@ -13086,10 +12800,10 @@
       <x:c r="P6" s="18"/>
       <x:c r="Q6" s="26"/>
       <x:c r="R6" s="26" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="S6" s="27" t="s">
-        <x:v>292</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="T6" s="26"/>
     </x:row>
@@ -13137,10 +12851,10 @@
       <x:c r="P7" s="18"/>
       <x:c r="Q7" s="26"/>
       <x:c r="R7" s="26" t="s">
-        <x:v>65</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="S7" s="27" t="s">
-        <x:v>293</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="T7" s="26"/>
     </x:row>
@@ -13188,10 +12902,10 @@
       <x:c r="P8" s="18"/>
       <x:c r="Q8" s="26"/>
       <x:c r="R8" s="26" t="s">
-        <x:v>68</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="S8" s="27" t="s">
-        <x:v>294</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="T8" s="26"/>
     </x:row>
@@ -13241,10 +12955,10 @@
       </x:c>
       <x:c r="Q9" s="26"/>
       <x:c r="R9" s="26" t="s">
-        <x:v>71</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S9" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T9" s="26"/>
     </x:row>
@@ -13292,10 +13006,10 @@
       <x:c r="P10" s="18"/>
       <x:c r="Q10" s="26"/>
       <x:c r="R10" s="26" t="s">
-        <x:v>74</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="S10" s="27" t="s">
-        <x:v>291</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="T10" s="26"/>
     </x:row>
@@ -13343,10 +13057,10 @@
       <x:c r="P11" s="18"/>
       <x:c r="Q11" s="26"/>
       <x:c r="R11" s="26" t="s">
-        <x:v>78</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="S11" s="27" t="s">
-        <x:v>290</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="T11" s="26"/>
     </x:row>
@@ -13395,10 +13109,10 @@
       </x:c>
       <x:c r="Q12" s="26"/>
       <x:c r="R12" s="26" t="s">
-        <x:v>78</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="S12" s="27" t="s">
-        <x:v>296</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T12" s="26"/>
     </x:row>
@@ -13445,10 +13159,10 @@
       <x:c r="P13" s="18"/>
       <x:c r="Q13" s="26"/>
       <x:c r="R13" s="26" t="s">
-        <x:v>82</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="S13" s="27" t="s">
-        <x:v>294</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="T13" s="26"/>
     </x:row>
@@ -13497,10 +13211,10 @@
       </x:c>
       <x:c r="Q14" s="26"/>
       <x:c r="R14" s="26" t="s">
-        <x:v>82</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="S14" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T14" s="26"/>
     </x:row>
@@ -13550,17 +13264,17 @@
       </x:c>
       <x:c r="Q15" s="26"/>
       <x:c r="R15" s="26" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="S15" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T15" s="26"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="26"/>
       <x:c r="B16" s="1" t="str">
-        <x:v>sk_codename_general_01_1</x:v>
+        <x:v>sk_caramel_pudding_1</x:v>
       </x:c>
       <x:c r="C16" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -13603,10 +13317,10 @@
       <x:c r="P16" s="26"/>
       <x:c r="Q16" s="26"/>
       <x:c r="R16" s="26" t="s">
-        <x:v>89</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="S16" s="27" t="s">
-        <x:v>293</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="T16" s="26"/>
     </x:row>
@@ -13653,10 +13367,10 @@
       <x:c r="P17" s="18"/>
       <x:c r="Q17" s="26"/>
       <x:c r="R17" s="26" t="s">
-        <x:v>89</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="S17" s="27" t="s">
-        <x:v>296</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T17" s="26"/>
     </x:row>
@@ -13705,10 +13419,10 @@
       </x:c>
       <x:c r="Q18" s="26"/>
       <x:c r="R18" s="26" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="S18" s="27" t="s">
-        <x:v>294</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="T18" s="26"/>
     </x:row>
@@ -13756,10 +13470,10 @@
       <x:c r="P19" s="18"/>
       <x:c r="Q19" s="26"/>
       <x:c r="R19" s="26" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="S19" s="27" t="s">
-        <x:v>296</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T19" s="26"/>
     </x:row>
@@ -13808,10 +13522,10 @@
       </x:c>
       <x:c r="Q20" s="26"/>
       <x:c r="R20" s="26" t="s">
-        <x:v>96</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="S20" s="27" t="s">
-        <x:v>292</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="T20" s="26"/>
     </x:row>
@@ -13861,10 +13575,10 @@
       <x:c r="P21" s="26"/>
       <x:c r="Q21" s="26"/>
       <x:c r="R21" s="26" t="s">
-        <x:v>100</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="S21" s="27" t="s">
-        <x:v>297</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="T21" s="26"/>
     </x:row>
@@ -13911,10 +13625,10 @@
       <x:c r="P22" s="1"/>
       <x:c r="Q22" s="26"/>
       <x:c r="R22" s="26" t="s">
-        <x:v>100</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="S22" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T22" s="26"/>
     </x:row>
@@ -13963,17 +13677,17 @@
       </x:c>
       <x:c r="Q23" s="26"/>
       <x:c r="R23" s="26" t="s">
-        <x:v>103</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="S23" s="27" t="s">
-        <x:v>298</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="T23" s="26"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="26"/>
       <x:c r="B24" s="1" t="str">
-        <x:v>sk_cream_1</x:v>
+        <x:v>sk_cream_puff_1</x:v>
       </x:c>
       <x:c r="C24" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14014,17 +13728,17 @@
       <x:c r="P24" s="18"/>
       <x:c r="Q24" s="26"/>
       <x:c r="R24" s="26" t="s">
-        <x:v>106</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="S24" s="27" t="s">
-        <x:v>299</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="T24" s="26"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="26"/>
       <x:c r="B25" s="1" t="str">
-        <x:v>sk_codename_general_02_1</x:v>
+        <x:v>sk_ice_cream_1</x:v>
       </x:c>
       <x:c r="C25" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14065,10 +13779,10 @@
       <x:c r="P25" s="18"/>
       <x:c r="Q25" s="26"/>
       <x:c r="R25" s="26" t="s">
-        <x:v>109</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="S25" s="27" t="s">
-        <x:v>294</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="T25" s="26"/>
     </x:row>
@@ -14116,17 +13830,17 @@
       <x:c r="P26" s="26"/>
       <x:c r="Q26" s="26"/>
       <x:c r="R26" s="26" t="s">
-        <x:v>113</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="S26" s="27" t="s">
-        <x:v>290</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="T26" s="26"/>
     </x:row>
     <x:row r="27" ht="17">
       <x:c r="A27" s="26"/>
       <x:c r="B27" s="1" t="str">
-        <x:v>sk_baguette_1</x:v>
+        <x:v>sk_osmanthus_cake_1</x:v>
       </x:c>
       <x:c r="C27" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14166,10 +13880,10 @@
       <x:c r="P27" s="18"/>
       <x:c r="Q27" s="26"/>
       <x:c r="R27" s="26" t="s">
-        <x:v>113</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="S27" s="27" t="s">
-        <x:v>296</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T27" s="26"/>
     </x:row>
@@ -14216,10 +13930,10 @@
       <x:c r="P28" s="26"/>
       <x:c r="Q28" s="26"/>
       <x:c r="R28" s="26" t="s">
-        <x:v>117</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="S28" s="27" t="s">
-        <x:v>300</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="T28" s="26"/>
     </x:row>
@@ -14268,17 +13982,17 @@
       </x:c>
       <x:c r="Q29" s="26"/>
       <x:c r="R29" s="26" t="s">
-        <x:v>117</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="S29" s="27" t="s">
-        <x:v>299</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="T29" s="26"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="26"/>
       <x:c r="B30" s="1" t="str">
-        <x:v>sk_cake_slice_1</x:v>
+        <x:v>sk_napoleon_cake_1</x:v>
       </x:c>
       <x:c r="C30" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14320,17 +14034,17 @@
       <x:c r="P30" s="26"/>
       <x:c r="Q30" s="26"/>
       <x:c r="R30" s="26" t="s">
-        <x:v>121</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="S30" s="27" t="s">
-        <x:v>294</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="T30" s="26"/>
     </x:row>
     <x:row r="31" ht="17">
       <x:c r="A31" s="26"/>
       <x:c r="B31" s="1" t="str">
-        <x:v>sk_cake_slice_2</x:v>
+        <x:v>sk_napoleon_cake_2</x:v>
       </x:c>
       <x:c r="C31" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14370,17 +14084,17 @@
       <x:c r="P31" s="18"/>
       <x:c r="Q31" s="26"/>
       <x:c r="R31" s="26" t="s">
-        <x:v>121</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="S31" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T31" s="26"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="26"/>
       <x:c r="B32" s="1" t="str">
-        <x:v>sk_long_cake_1</x:v>
+        <x:v>sk_honey_cake_1</x:v>
       </x:c>
       <x:c r="C32" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14420,17 +14134,17 @@
       <x:c r="P32" s="18"/>
       <x:c r="Q32" s="26"/>
       <x:c r="R32" s="26" t="s">
-        <x:v>124</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="S32" s="27" t="s">
-        <x:v>297</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="T32" s="26"/>
     </x:row>
     <x:row r="33" s="25" customFormat="1">
       <x:c r="A33" s="8"/>
       <x:c r="B33" s="8" t="str">
-        <x:v>sk_long_cake_2</x:v>
+        <x:v>sk_honey_cake_2</x:v>
       </x:c>
       <x:c r="C33" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14472,17 +14186,17 @@
       </x:c>
       <x:c r="Q33" s="26"/>
       <x:c r="R33" s="26" t="s">
-        <x:v>127</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="S33" s="27" t="s">
-        <x:v>297</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="T33" s="26"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="26"/>
       <x:c r="B34" s="1" t="str">
-        <x:v>sk_codename_cake_01_1</x:v>
+        <x:v>sk_tree_ring_cake_1</x:v>
       </x:c>
       <x:c r="C34" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14525,17 +14239,17 @@
       </x:c>
       <x:c r="Q34" s="26"/>
       <x:c r="R34" s="26" t="s">
-        <x:v>131</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="S34" s="27" t="s">
-        <x:v>294</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="T34" s="26"/>
     </x:row>
     <x:row r="35" ht="17">
       <x:c r="A35" s="26"/>
       <x:c r="B35" s="1" t="str">
-        <x:v>sk_codename_transfer_01_1</x:v>
+        <x:v>sk_nougat_1</x:v>
       </x:c>
       <x:c r="C35" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14575,17 +14289,17 @@
       <x:c r="P35" s="18"/>
       <x:c r="Q35" s="26"/>
       <x:c r="R35" s="26" t="s">
-        <x:v>131</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="S35" s="27" t="s">
-        <x:v>296</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T35" s="26"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="26"/>
       <x:c r="B36" s="1" t="str">
-        <x:v>sk_codename_transfer_01_2</x:v>
+        <x:v>sk_nougat_2</x:v>
       </x:c>
       <x:c r="C36" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14627,17 +14341,17 @@
       </x:c>
       <x:c r="Q36" s="26"/>
       <x:c r="R36" s="26" t="s">
-        <x:v>135</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="S36" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T36" s="26"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="26"/>
       <x:c r="B37" s="1" t="str">
-        <x:v>sk_codename_serving_01_1</x:v>
+        <x:v>sk_hawthorn_cake_1</x:v>
       </x:c>
       <x:c r="C37" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14682,17 +14396,17 @@
       <x:c r="P37" s="26"/>
       <x:c r="Q37" s="26"/>
       <x:c r="R37" s="26" t="s">
-        <x:v>135</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="S37" s="27" t="s">
-        <x:v>300</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="T37" s="26"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="26"/>
       <x:c r="B38" s="1" t="str">
-        <x:v>sk_codename_general_03_1</x:v>
+        <x:v>sk_souffle_1</x:v>
       </x:c>
       <x:c r="C38" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14733,17 +14447,17 @@
       <x:c r="P38" s="26"/>
       <x:c r="Q38" s="26"/>
       <x:c r="R38" s="26" t="s">
-        <x:v>138</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="S38" s="27" t="s">
-        <x:v>291</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="T38" s="26"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="26"/>
       <x:c r="B39" s="1" t="str">
-        <x:v>sk_codename_general_04_1</x:v>
+        <x:v>sk_fruit_tart_1</x:v>
       </x:c>
       <x:c r="C39" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14786,17 +14500,17 @@
       <x:c r="P39" s="1"/>
       <x:c r="Q39" s="26"/>
       <x:c r="R39" s="26" t="s">
-        <x:v>141</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="S39" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T39" s="26"/>
     </x:row>
     <x:row r="40" ht="17">
       <x:c r="A40" s="26"/>
       <x:c r="B40" s="1" t="str">
-        <x:v>sk_codename_general_05_1</x:v>
+        <x:v>sk_strawberry_sundae_1</x:v>
       </x:c>
       <x:c r="C40" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14839,17 +14553,17 @@
       <x:c r="P40" s="18"/>
       <x:c r="Q40" s="26"/>
       <x:c r="R40" s="26" t="s">
-        <x:v>144</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="S40" s="27" t="s">
-        <x:v>298</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="T40" s="26"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="26"/>
       <x:c r="B41" s="1" t="str">
-        <x:v>sk_codename_general_06_1</x:v>
+        <x:v>sk_rock_sugar_pear_1</x:v>
       </x:c>
       <x:c r="C41" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14889,17 +14603,17 @@
       <x:c r="P41" s="18"/>
       <x:c r="Q41" s="26"/>
       <x:c r="R41" s="26" t="s">
-        <x:v>147</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="S41" s="27" t="s">
-        <x:v>299</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="T41" s="26"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="26"/>
       <x:c r="B42" s="1" t="str">
-        <x:v>sk_codename_general_06_2</x:v>
+        <x:v>sk_rock_sugar_pear_2</x:v>
       </x:c>
       <x:c r="C42" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14939,17 +14653,17 @@
       <x:c r="P42" s="26"/>
       <x:c r="Q42" s="26"/>
       <x:c r="R42" s="26" t="s">
-        <x:v>150</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="S42" s="27" t="s">
-        <x:v>297</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="T42" s="26"/>
     </x:row>
     <x:row r="43" ht="17">
       <x:c r="A43" s="26"/>
       <x:c r="B43" s="1" t="str">
-        <x:v>sk_codename_transfer_02_1</x:v>
+        <x:v>sk_popping_candy_1</x:v>
       </x:c>
       <x:c r="C43" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14992,17 +14706,17 @@
       <x:c r="P43" s="18"/>
       <x:c r="Q43" s="26"/>
       <x:c r="R43" s="26" t="s">
-        <x:v>154</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="S43" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T43" s="26"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="26"/>
       <x:c r="B44" s="1" t="str">
-        <x:v>sk_codename_cake_02_1</x:v>
+        <x:v>sk_mille_crepe_cake_1</x:v>
       </x:c>
       <x:c r="C44" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15047,17 +14761,17 @@
       </x:c>
       <x:c r="Q44" s="26"/>
       <x:c r="R44" s="26" t="s">
-        <x:v>154</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="S44" s="27" t="s">
-        <x:v>297</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="T44" s="26"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="26"/>
       <x:c r="B45" s="1" t="str">
-        <x:v>sk_codename_serving_02_1</x:v>
+        <x:v>sk_soybean_glutinous_roll_1</x:v>
       </x:c>
       <x:c r="C45" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15100,17 +14814,17 @@
       <x:c r="P45" s="18"/>
       <x:c r="Q45" s="26"/>
       <x:c r="R45" s="26" t="s">
-        <x:v>158</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="S45" s="27" t="s">
-        <x:v>158</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="T45" s="26"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="26"/>
       <x:c r="B46" s="1" t="str">
-        <x:v>sk_eclair_1</x:v>
+        <x:v>sk_sachima_1</x:v>
       </x:c>
       <x:c r="C46" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15155,10 +14869,10 @@
       <x:c r="P46" s="1"/>
       <x:c r="Q46" s="26"/>
       <x:c r="R46" s="26" t="s">
-        <x:v>158</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="S46" s="27" t="s">
-        <x:v>296</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T46" s="26"/>
     </x:row>
@@ -15208,17 +14922,17 @@
       <x:c r="P47" s="26"/>
       <x:c r="Q47" s="26"/>
       <x:c r="R47" s="26" t="s">
-        <x:v>162</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="S47" s="27" t="s">
-        <x:v>299</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="T47" s="26"/>
     </x:row>
     <x:row r="48" ht="17">
       <x:c r="A48" s="26"/>
       <x:c r="B48" s="1" t="str">
-        <x:v>sk_chocolate_strip_1</x:v>
+        <x:v>sk_chocolate_wafer_1</x:v>
       </x:c>
       <x:c r="C48" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15258,17 +14972,17 @@
       <x:c r="P48" s="18"/>
       <x:c r="Q48" s="26"/>
       <x:c r="R48" s="26" t="s">
-        <x:v>162</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="S48" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T48" s="26"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="26"/>
       <x:c r="B49" s="1" t="str">
-        <x:v>sk_chocolate_strip_2</x:v>
+        <x:v>sk_chocolate_wafer_2</x:v>
       </x:c>
       <x:c r="C49" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15310,10 +15024,10 @@
       </x:c>
       <x:c r="Q49" s="26"/>
       <x:c r="R49" s="26" t="s">
-        <x:v>166</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="S49" s="27" t="s">
-        <x:v>290</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="T49" s="26"/>
     </x:row>
@@ -15362,10 +15076,10 @@
       </x:c>
       <x:c r="Q50" s="26"/>
       <x:c r="R50" s="26" t="s">
-        <x:v>166</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="S50" s="27" t="s">
-        <x:v>296</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T50" s="26"/>
     </x:row>
@@ -15414,17 +15128,17 @@
       <x:c r="P51" s="18"/>
       <x:c r="Q51" s="26"/>
       <x:c r="R51" s="26" t="s">
-        <x:v>169</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="S51" s="27" t="s">
-        <x:v>294</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="T51" s="26"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="26"/>
       <x:c r="B52" s="1" t="str">
-        <x:v>sk_codename_cake_03_1</x:v>
+        <x:v>sk_fondant_cake_1</x:v>
       </x:c>
       <x:c r="C52" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15466,17 +15180,17 @@
       <x:c r="P52" s="18"/>
       <x:c r="Q52" s="26"/>
       <x:c r="R52" s="26" t="s">
-        <x:v>173</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S52" s="27" t="s">
-        <x:v>299</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="T52" s="26"/>
     </x:row>
     <x:row r="53" ht="17">
       <x:c r="A53" s="26"/>
       <x:c r="B53" s="1" t="str">
-        <x:v>sk_codename_cake_03_2</x:v>
+        <x:v>sk_fondant_cake_2</x:v>
       </x:c>
       <x:c r="C53" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15518,17 +15232,17 @@
       </x:c>
       <x:c r="Q53" s="26"/>
       <x:c r="R53" s="26" t="s">
-        <x:v>173</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S53" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T53" s="26"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="26"/>
       <x:c r="B54" s="1" t="str">
-        <x:v>sk_codename_cake_04_1</x:v>
+        <x:v>sk_matcha_cake_1</x:v>
       </x:c>
       <x:c r="C54" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15572,17 +15286,17 @@
       </x:c>
       <x:c r="Q54" s="26"/>
       <x:c r="R54" s="26" t="s">
-        <x:v>176</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="S54" s="27" t="s">
-        <x:v>298</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="T54" s="26"/>
     </x:row>
     <x:row r="55" ht="17">
       <x:c r="A55" s="26"/>
       <x:c r="B55" s="1" t="str">
-        <x:v>sk_codename_serving_03_1</x:v>
+        <x:v>sk_mung_bean_cake_1</x:v>
       </x:c>
       <x:c r="C55" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15622,17 +15336,17 @@
       <x:c r="P55" s="18"/>
       <x:c r="Q55" s="26"/>
       <x:c r="R55" s="26" t="s">
-        <x:v>179</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S55" s="27" t="s">
-        <x:v>301</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="T55" s="26"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="26"/>
       <x:c r="B56" s="1" t="str">
-        <x:v>sk_codename_serving_04_1</x:v>
+        <x:v>sk_egg_yolk_pastry_1</x:v>
       </x:c>
       <x:c r="C56" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15675,17 +15389,17 @@
       <x:c r="P56" s="18"/>
       <x:c r="Q56" s="26"/>
       <x:c r="R56" s="26" t="s">
-        <x:v>183</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S56" s="27" t="s">
-        <x:v>183</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="T56" s="26"/>
     </x:row>
     <x:row r="57" ht="17">
       <x:c r="A57" s="26"/>
       <x:c r="B57" s="1" t="str">
-        <x:v>sk_codename_transfer_03_1</x:v>
+        <x:v>sk_chocolate_truffle_1</x:v>
       </x:c>
       <x:c r="C57" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15730,17 +15444,17 @@
       </x:c>
       <x:c r="Q57" s="26"/>
       <x:c r="R57" s="26" t="s">
-        <x:v>183</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S57" s="27" t="s">
-        <x:v>298</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="T57" s="26"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="26"/>
       <x:c r="B58" s="1" t="str">
-        <x:v>sk_codename_transfer_04_1</x:v>
+        <x:v>sk_liquor_chocolate_1</x:v>
       </x:c>
       <x:c r="C58" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15781,17 +15495,17 @@
       <x:c r="P58" s="26"/>
       <x:c r="Q58" s="26"/>
       <x:c r="R58" s="26" t="s">
-        <x:v>186</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="S58" s="27" t="s">
-        <x:v>298</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="T58" s="26"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="26"/>
       <x:c r="B59" s="1" t="str">
-        <x:v>sk_codename_transfer_04_2</x:v>
+        <x:v>sk_liquor_chocolate_2</x:v>
       </x:c>
       <x:c r="C59" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15833,10 +15547,10 @@
       </x:c>
       <x:c r="Q59" s="26"/>
       <x:c r="R59" s="26" t="s">
-        <x:v>189</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="S59" s="27" t="s">
-        <x:v>189</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="T59" s="26"/>
     </x:row>
@@ -15939,7 +15653,7 @@
     <x:row r="62">
       <x:c r="A62" s="26"/>
       <x:c r="B62" s="26" t="str">
-        <x:v>sk_maple_sugar_1</x:v>
+        <x:v>sk_toffee_candy_1</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>OnSettle</x:v>
@@ -16041,7 +15755,7 @@
     <x:row r="64">
       <x:c r="A64" s="26"/>
       <x:c r="B64" s="26" t="str">
-        <x:v>sk_waffle_1</x:v>
+        <x:v>sk_brown_sugar_steamed_cake_1</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>OnSettle</x:v>
@@ -16279,7 +15993,7 @@
     <x:row r="69">
       <x:c r="A69" s="26"/>
       <x:c r="B69" s="26" t="str">
-        <x:v>sk_codename_general_07_1</x:v>
+        <x:v>sk_fruit_shaved_ice_1</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>OnSettle</x:v>
@@ -16327,7 +16041,7 @@
     <x:row r="70">
       <x:c r="A70" s="26"/>
       <x:c r="B70" s="26" t="str">
-        <x:v>sk_codename_general_08_1</x:v>
+        <x:v>sk_coconut_milk_jelly_1</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>OnSettle</x:v>
@@ -16478,7 +16192,7 @@
     <x:row r="73" ht="34" customHeight="1">
       <x:c r="A73" s="26"/>
       <x:c r="B73" s="26" t="str">
-        <x:v>sk_chocolate_sauce_1</x:v>
+        <x:v>sk_nama_chocolate_1</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>OnSettle</x:v>
@@ -16524,7 +16238,7 @@
     <x:row r="74">
       <x:c r="A74" s="26"/>
       <x:c r="B74" s="26" t="str">
-        <x:v>sk_chocolate_sauce_2</x:v>
+        <x:v>sk_nama_chocolate_2</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>OnSettle</x:v>
@@ -16714,7 +16428,7 @@
     <x:row r="78">
       <x:c r="A78" s="26"/>
       <x:c r="B78" s="26" t="str">
-        <x:v>sk_parfait_1</x:v>
+        <x:v>sk_fermented_rice_balls_1</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>OnSettle</x:v>
@@ -16901,7 +16615,7 @@
     <x:row r="82">
       <x:c r="A82" s="26"/>
       <x:c r="B82" s="26" t="str">
-        <x:v>sk_apple_pie_1</x:v>
+        <x:v>sk_double_skin_milk_1</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>OnSettle</x:v>
@@ -17010,6 +16724,13 @@
     <x:col min="14" max="15" width="12.923076629638672" style="1" customWidth="0"/>
     <x:col min="16" max="16" width="13.923076629638672" style="1" customWidth="1"/>
     <x:col min="17" max="16384" width="9.230769157409668" style="1" customWidth="0"/>
+    <x:col min="22" max="22" width="11.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="11.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="13.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="27.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="33.33000183105469" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="36.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
@@ -17035,48 +16756,69 @@
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17.600000381469727">
       <x:c r="D4" s="9" t="s">
-        <x:v>302</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E4" s="9" t="s">
-        <x:v>303</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F4" s="9" t="s">
-        <x:v>304</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G4" s="9" t="s">
-        <x:v>305</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="Q4" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="R4" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="S4" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="T4" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="U4" s="1" t="s">
-        <x:v>310</x:v>
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="V4" s="39" t="str">
+        <x:v>视觉主流派</x:v>
+      </x:c>
+      <x:c r="W4" s="39" t="str">
+        <x:v>视觉次流派</x:v>
+      </x:c>
+      <x:c r="X4" s="39" t="str">
+        <x:v>现实甜品原型</x:v>
+      </x:c>
+      <x:c r="Y4" s="39" t="str">
+        <x:v>参考链接</x:v>
+      </x:c>
+      <x:c r="Z4" s="39" t="str">
+        <x:v>轮廓/构图</x:v>
+      </x:c>
+      <x:c r="AA4" s="39" t="str">
+        <x:v>器皿/包装与材质</x:v>
+      </x:c>
+      <x:c r="AB4" s="39" t="str">
+        <x:v>美术状态</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="34">
       <x:c r="C5" s="10" t="s">
-        <x:v>311</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D5" s="11" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E5" s="11" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F5" s="11">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G5" s="11" t="s">
-        <x:v>313</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="Q5" s="1">
         <x:v>2</x:v>
@@ -17084,20 +16826,27 @@
       <x:c r="R5" s="1">
         <x:v>2.25</x:v>
       </x:c>
+      <x:c r="V5" s="45"/>
+      <x:c r="W5" s="45"/>
+      <x:c r="X5" s="44"/>
+      <x:c r="Y5" s="44"/>
+      <x:c r="Z5" s="44"/>
+      <x:c r="AA5" s="44"/>
+      <x:c r="AB5" s="45"/>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="34">
       <x:c r="C6" s="10"/>
       <x:c r="D6" s="11" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E6" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F6" s="8">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G6" s="15" t="s">
-        <x:v>314</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="Q6" s="1">
         <x:v>2</x:v>
@@ -17108,20 +16857,27 @@
       <x:c r="S6" s="1">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="V6" s="45"/>
+      <x:c r="W6" s="45"/>
+      <x:c r="X6" s="44"/>
+      <x:c r="Y6" s="44"/>
+      <x:c r="Z6" s="44"/>
+      <x:c r="AA6" s="44"/>
+      <x:c r="AB6" s="45"/>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="34">
       <x:c r="C7" s="10"/>
       <x:c r="D7" s="11" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E7" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F7" s="15">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G7" s="15" t="s">
-        <x:v>316</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="Q7" s="1">
         <x:v>2</x:v>
@@ -17132,29 +16888,43 @@
       <x:c r="S7" s="1">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="V7" s="45"/>
+      <x:c r="W7" s="45"/>
+      <x:c r="X7" s="44"/>
+      <x:c r="Y7" s="44"/>
+      <x:c r="Z7" s="44"/>
+      <x:c r="AA7" s="44"/>
+      <x:c r="AB7" s="45"/>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17">
       <x:c r="C8" s="10"/>
       <x:c r="D8" s="8"/>
       <x:c r="E8" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F8" s="15"/>
       <x:c r="G8" s="15"/>
+      <x:c r="V8" s="45"/>
+      <x:c r="W8" s="45"/>
+      <x:c r="X8" s="44"/>
+      <x:c r="Y8" s="44"/>
+      <x:c r="Z8" s="44"/>
+      <x:c r="AA8" s="44"/>
+      <x:c r="AB8" s="45"/>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="34">
       <x:c r="C9" s="10"/>
       <x:c r="D9" s="11" t="s">
-        <x:v>65</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E9" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F9" s="15">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G9" s="15" t="s">
-        <x:v>317</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="Q9" s="1">
         <x:v>2</x:v>
@@ -17165,52 +16935,66 @@
       <x:c r="S9" s="1">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="V9" s="45"/>
+      <x:c r="W9" s="45"/>
+      <x:c r="X9" s="44"/>
+      <x:c r="Y9" s="44"/>
+      <x:c r="Z9" s="44"/>
+      <x:c r="AA9" s="44"/>
+      <x:c r="AB9" s="45"/>
     </x:row>
     <x:row r="10" s="1" customFormat="1">
       <x:c r="C10" s="10"/>
       <x:c r="D10" s="8"/>
       <x:c r="E10" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F10" s="8"/>
       <x:c r="G10" s="15"/>
       <x:c r="I10" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="K10" s="1" t="s">
-        <x:v>320</x:v>
-      </x:c>
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="V10" s="45"/>
+      <x:c r="W10" s="45"/>
+      <x:c r="X10" s="44"/>
+      <x:c r="Y10" s="44"/>
+      <x:c r="Z10" s="44"/>
+      <x:c r="AA10" s="44"/>
+      <x:c r="AB10" s="45"/>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="34">
       <x:c r="C11" s="12" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="D11" s="9" t="s">
-        <x:v>68</x:v>
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="str">
+        <x:v>果冻</x:v>
       </x:c>
       <x:c r="E11" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F11" s="8">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G11" s="16" t="s">
-        <x:v>322</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="I11" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K11" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="M11" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="Q11" s="1">
         <x:v>2</x:v>
@@ -17221,29 +17005,48 @@
       <x:c r="S11" s="1">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="V11" s="45" t="str">
+        <x:v>通用</x:v>
+      </x:c>
+      <x:c r="W11" s="45" t="str"/>
+      <x:c r="X11" s="44" t="str">
+        <x:v>果冻</x:v>
+      </x:c>
+      <x:c r="Y11" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%9E%9C%E5%86%BB%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z11" s="44" t="str">
+        <x:v>2×1单份果冻；保持现实比例，用器皿或自然长形适配格子</x:v>
+      </x:c>
+      <x:c r="AA11" s="44" t="str">
+        <x:v>白瓷、透明但不半透明的风格化杯碗或烘焙纸托；不使用流派专属纹样</x:v>
+      </x:c>
+      <x:c r="AB11" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1" ht="34">
       <x:c r="C12" s="12"/>
-      <x:c r="D12" s="8" t="s">
-        <x:v>71</x:v>
+      <x:c r="D12" s="8" t="str">
+        <x:v>糖霜蛋糕</x:v>
       </x:c>
       <x:c r="E12" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F12" s="15">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G12" s="15" t="s">
-        <x:v>326</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="I12" s="1" t="s">
-        <x:v>327</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="M12" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="Q12" s="1">
         <x:v>2</x:v>
@@ -17251,29 +17054,50 @@
       <x:c r="U12" s="1">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="V12" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W12" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="X12" s="44" t="str">
+        <x:v>糖霜蛋糕</x:v>
+      </x:c>
+      <x:c r="Y12" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E7%B3%96%E9%9C%9C%E8%9B%8B%E7%B3%95%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z12" s="44" t="str">
+        <x:v>2×1蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA12" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB12" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1" ht="34">
       <x:c r="C13" s="12"/>
-      <x:c r="D13" s="8" t="s">
-        <x:v>74</x:v>
+      <x:c r="D13" s="8" t="str">
+        <x:v>蛋挞</x:v>
       </x:c>
       <x:c r="E13" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F13" s="8">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G13" s="15" t="s">
-        <x:v>330</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="I13" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K13" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="Q13" s="1">
         <x:v>2</x:v>
@@ -17281,56 +17105,94 @@
       <x:c r="S13" s="1">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="V13" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W13" s="45" t="str"/>
+      <x:c r="X13" s="44" t="str">
+        <x:v>蛋挞</x:v>
+      </x:c>
+      <x:c r="Y13" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E8%9B%8B%E6%8C%9E%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z13" s="44" t="str">
+        <x:v>2×1单份东方甜点；用糕、酥、糯米或甜品碗形成完整单体</x:v>
+      </x:c>
+      <x:c r="AA13" s="44" t="str">
+        <x:v>青瓷、竹托或中式纸托三选一；暖金、豆沙红、芝麻黑与米白为主</x:v>
+      </x:c>
+      <x:c r="AB13" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" s="1" customFormat="1" ht="51">
       <x:c r="C14" s="12"/>
-      <x:c r="D14" s="8" t="s">
-        <x:v>78</x:v>
+      <x:c r="D14" s="8" t="str">
+        <x:v>糖豆</x:v>
       </x:c>
       <x:c r="E14" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F14" s="15">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G14" s="15" t="s">
-        <x:v>333</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="I14" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K14" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="Q14" s="1">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="V14" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W14" s="45" t="str"/>
+      <x:c r="X14" s="44" t="str">
+        <x:v>糖豆</x:v>
+      </x:c>
+      <x:c r="Y14" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E7%B3%96%E8%B1%86%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z14" s="44" t="str">
+        <x:v>2×1单体糖果或巧克力；包装走势服从格子比例，保持强轮廓</x:v>
+      </x:c>
+      <x:c r="AA14" s="44" t="str">
+        <x:v>无餐盘；使用糖纸、锡纸或纸托；糖晶高光与巧克力哑光形成材质差</x:v>
+      </x:c>
+      <x:c r="AB14" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" s="1" customFormat="1" ht="34">
       <x:c r="C15" s="12"/>
-      <x:c r="D15" s="8" t="s">
-        <x:v>82</x:v>
+      <x:c r="D15" s="8" t="str">
+        <x:v>芝士蛋糕</x:v>
       </x:c>
       <x:c r="E15" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F15" s="8">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G15" s="15" t="s">
-        <x:v>337</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="I15" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="K15" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="Q15" s="1">
         <x:v>2</x:v>
@@ -17341,188 +17203,324 @@
       <x:c r="U15" s="1">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="V15" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W15" s="45" t="str"/>
+      <x:c r="X15" s="44" t="str">
+        <x:v>芝士蛋糕</x:v>
+      </x:c>
+      <x:c r="Y15" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E8%8A%9D%E5%A3%AB%E8%9B%8B%E7%B3%95%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z15" s="44" t="str">
+        <x:v>2×1蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA15" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB15" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" s="1" customFormat="1" ht="34">
       <x:c r="C16" s="12"/>
-      <x:c r="D16" s="8" t="s">
-        <x:v>85</x:v>
+      <x:c r="D16" s="8" t="str">
+        <x:v>慕斯蛋糕</x:v>
       </x:c>
       <x:c r="E16" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F16" s="15">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G16" s="15" t="s">
-        <x:v>340</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="I16" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="K16" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="Q16" s="1">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="V16" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W16" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="X16" s="44" t="str">
+        <x:v>慕斯蛋糕</x:v>
+      </x:c>
+      <x:c r="Y16" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%85%95%E6%96%AF%E8%9B%8B%E7%B3%95%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z16" s="44" t="str">
+        <x:v>2×1蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA16" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB16" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" s="1" customFormat="1" ht="34">
       <x:c r="C17" s="12"/>
-      <x:c r="D17" s="8" t="s">
-        <x:v>342</x:v>
+      <x:c r="D17" s="8" t="str">
+        <x:v>焦糖布丁</x:v>
       </x:c>
       <x:c r="E17" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F17" s="15">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G17" s="15" t="s">
-        <x:v>343</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="I17" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="V17" s="45" t="str">
+        <x:v>通用</x:v>
+      </x:c>
+      <x:c r="W17" s="45" t="str"/>
+      <x:c r="X17" s="44" t="str">
+        <x:v>焦糖布丁</x:v>
+      </x:c>
+      <x:c r="Y17" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E7%84%A6%E7%B3%96%E5%B8%83%E4%B8%81+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z17" s="44" t="str">
+        <x:v>2×1单份焦糖布丁；保持现实比例，用器皿或自然长形适配格子</x:v>
+      </x:c>
+      <x:c r="AA17" s="44" t="str">
+        <x:v>白瓷、透明但不半透明的风格化杯碗或烘焙纸托；不使用流派专属纹样</x:v>
+      </x:c>
+      <x:c r="AB17" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="1" customFormat="1" ht="34">
       <x:c r="C18" s="12"/>
-      <x:c r="D18" s="8" t="s">
-        <x:v>89</x:v>
+      <x:c r="D18" s="8" t="str">
+        <x:v>水果糖</x:v>
       </x:c>
       <x:c r="E18" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F18" s="8">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G18" s="15" t="s">
-        <x:v>344</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="I18" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K18" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="Q18" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="S18" s="1">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="V18" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W18" s="45" t="str"/>
+      <x:c r="X18" s="44" t="str">
+        <x:v>水果糖</x:v>
+      </x:c>
+      <x:c r="Y18" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%B0%B4%E6%9E%9C%E7%B3%96%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z18" s="44" t="str">
+        <x:v>1×2单体糖果或巧克力；包装走势服从格子比例，保持强轮廓</x:v>
+      </x:c>
+      <x:c r="AA18" s="44" t="str">
+        <x:v>无餐盘；使用糖纸、锡纸或纸托；糖晶高光与巧克力哑光形成材质差</x:v>
+      </x:c>
+      <x:c r="AB18" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="19" s="1" customFormat="1" ht="17">
       <x:c r="C19" s="12"/>
       <x:c r="D19" s="8"/>
       <x:c r="E19" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F19" s="15"/>
       <x:c r="G19" s="15"/>
+      <x:c r="V19" s="45"/>
+      <x:c r="W19" s="45"/>
+      <x:c r="X19" s="44"/>
+      <x:c r="Y19" s="44"/>
+      <x:c r="Z19" s="44"/>
+      <x:c r="AA19" s="44"/>
+      <x:c r="AB19" s="45"/>
     </x:row>
     <x:row r="20" s="1" customFormat="1" ht="51">
       <x:c r="C20" s="12"/>
-      <x:c r="D20" s="8" t="s">
-        <x:v>93</x:v>
+      <x:c r="D20" s="8" t="str">
+        <x:v>巧克力棒</x:v>
       </x:c>
       <x:c r="E20" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F20" s="8">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G20" s="15" t="s">
-        <x:v>346</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="I20" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K20" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="Q20" s="1">
         <x:v>2</x:v>
+      </x:c>
+      <x:c r="V20" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W20" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="X20" s="44" t="str">
+        <x:v>巧克力棒</x:v>
+      </x:c>
+      <x:c r="Y20" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E5%B7%A7%E5%85%8B%E5%8A%9B%E6%A3%92%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z20" s="44" t="str">
+        <x:v>1×2单体糖果或巧克力；包装走势服从格子比例，保持强轮廓</x:v>
+      </x:c>
+      <x:c r="AA20" s="44" t="str">
+        <x:v>无餐盘；使用糖纸、锡纸或纸托；糖晶高光与巧克力哑光形成材质差</x:v>
+      </x:c>
+      <x:c r="AB20" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="21" s="1" customFormat="1" ht="17">
       <x:c r="C21" s="12"/>
       <x:c r="D21" s="8"/>
       <x:c r="E21" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F21" s="15"/>
       <x:c r="G21" s="15"/>
-      <x:c r="V21" s="8"/>
+      <x:c r="V21" s="45"/>
+      <x:c r="W21" s="45"/>
+      <x:c r="X21" s="44"/>
+      <x:c r="Y21" s="44"/>
+      <x:c r="Z21" s="44"/>
+      <x:c r="AA21" s="44"/>
+      <x:c r="AB21" s="45"/>
     </x:row>
     <x:row r="22" s="1" customFormat="1" ht="34">
       <x:c r="C22" s="12"/>
-      <x:c r="D22" s="8" t="s">
-        <x:v>96</x:v>
+      <x:c r="D22" s="8" t="str">
+        <x:v>麻薯</x:v>
       </x:c>
       <x:c r="E22" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F22" s="8">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G22" s="15" t="s">
-        <x:v>348</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K22" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="Q22" s="1">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="V22" s="15"/>
+      <x:c r="V22" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W22" s="45" t="str"/>
+      <x:c r="X22" s="44" t="str">
+        <x:v>麻薯</x:v>
+      </x:c>
+      <x:c r="Y22" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E9%BA%BB%E8%96%AF%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z22" s="44" t="str">
+        <x:v>1×2单份东方甜点；用糕、酥、糯米或甜品碗形成完整单体</x:v>
+      </x:c>
+      <x:c r="AA22" s="44" t="str">
+        <x:v>青瓷、竹托或中式纸托三选一；暖金、豆沙红、芝麻黑与米白为主</x:v>
+      </x:c>
+      <x:c r="AB22" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" s="1" customFormat="1" ht="17">
       <x:c r="C23" s="12"/>
       <x:c r="D23" s="8"/>
       <x:c r="E23" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F23" s="15"/>
       <x:c r="G23" s="8"/>
-      <x:c r="V23" s="15"/>
+      <x:c r="V23" s="45"/>
+      <x:c r="W23" s="45"/>
+      <x:c r="X23" s="44"/>
+      <x:c r="Y23" s="44"/>
+      <x:c r="Z23" s="44"/>
+      <x:c r="AA23" s="44"/>
+      <x:c r="AB23" s="45"/>
     </x:row>
     <x:row r="24" s="1" customFormat="1" ht="34">
       <x:c r="C24" s="12"/>
-      <x:c r="D24" s="8" t="s">
-        <x:v>100</x:v>
+      <x:c r="D24" s="8" t="str">
+        <x:v>杯子蛋糕</x:v>
       </x:c>
       <x:c r="E24" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F24" s="8">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G24" s="15" t="s">
-        <x:v>350</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="I24" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K24" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="Q24" s="1">
         <x:v>2</x:v>
@@ -17533,107 +17531,179 @@
       <x:c r="U24" s="1">
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="V24" s="15"/>
+      <x:c r="V24" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W24" s="45" t="str"/>
+      <x:c r="X24" s="44" t="str">
+        <x:v>杯子蛋糕</x:v>
+      </x:c>
+      <x:c r="Y24" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%9D%AF%E5%AD%90%E8%9B%8B%E7%B3%95%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z24" s="44" t="str">
+        <x:v>1×2蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA24" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB24" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" s="1" customFormat="1" ht="17">
       <x:c r="C25" s="12"/>
       <x:c r="D25" s="8"/>
       <x:c r="E25" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F25" s="15"/>
       <x:c r="G25" s="15"/>
-      <x:c r="V25" s="18"/>
+      <x:c r="V25" s="45"/>
+      <x:c r="W25" s="45"/>
+      <x:c r="X25" s="44"/>
+      <x:c r="Y25" s="44"/>
+      <x:c r="Z25" s="44"/>
+      <x:c r="AA25" s="44"/>
+      <x:c r="AB25" s="45"/>
     </x:row>
     <x:row r="26" s="1" customFormat="1" ht="34">
       <x:c r="C26" s="12"/>
-      <x:c r="D26" s="8" t="s">
-        <x:v>103</x:v>
+      <x:c r="D26" s="8" t="str">
+        <x:v>奶油泡芙</x:v>
       </x:c>
       <x:c r="E26" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F26" s="8">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G26" s="17" t="s">
-        <x:v>352</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="I26" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K26" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="Q26" s="1">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="V26" s="8"/>
+      <x:c r="V26" s="45" t="str">
+        <x:v>通用</x:v>
+      </x:c>
+      <x:c r="W26" s="45" t="str"/>
+      <x:c r="X26" s="44" t="str">
+        <x:v>奶油泡芙</x:v>
+      </x:c>
+      <x:c r="Y26" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E5%A5%B6%E6%B2%B9%E6%B3%A1%E8%8A%99+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z26" s="44" t="str">
+        <x:v>1×2单份奶油泡芙；保持现实比例，用器皿或自然长形适配格子</x:v>
+      </x:c>
+      <x:c r="AA26" s="44" t="str">
+        <x:v>白瓷、透明但不半透明的风格化杯碗或烘焙纸托；不使用流派专属纹样</x:v>
+      </x:c>
+      <x:c r="AB26" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" s="1" customFormat="1" ht="17">
       <x:c r="C27" s="12"/>
       <x:c r="D27" s="8"/>
       <x:c r="E27" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F27" s="15"/>
       <x:c r="G27" s="15"/>
-      <x:c r="V27" s="15"/>
+      <x:c r="V27" s="45"/>
+      <x:c r="W27" s="45"/>
+      <x:c r="X27" s="44"/>
+      <x:c r="Y27" s="44"/>
+      <x:c r="Z27" s="44"/>
+      <x:c r="AA27" s="44"/>
+      <x:c r="AB27" s="45"/>
     </x:row>
     <x:row r="28" s="1" customFormat="1" ht="34">
       <x:c r="C28" s="12"/>
-      <x:c r="D28" s="8" t="s">
-        <x:v>354</x:v>
+      <x:c r="D28" s="8" t="str">
+        <x:v>冰淇淋</x:v>
       </x:c>
       <x:c r="E28" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F28" s="15">
         <x:v>100</x:v>
       </x:c>
       <x:c r="G28" s="15" t="s">
-        <x:v>355</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="I28" s="1" t="s">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="V28" s="15"/>
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="V28" s="45" t="str">
+        <x:v>通用</x:v>
+      </x:c>
+      <x:c r="W28" s="45" t="str"/>
+      <x:c r="X28" s="44" t="str">
+        <x:v>冰淇淋</x:v>
+      </x:c>
+      <x:c r="Y28" s="44" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/%E5%86%B0%E6%B7%87%E6%B7%8B</x:v>
+      </x:c>
+      <x:c r="Z28" s="44" t="str">
+        <x:v>1×2单份冰淇淋；保持现实比例，用器皿或自然长形适配格子</x:v>
+      </x:c>
+      <x:c r="AA28" s="44" t="str">
+        <x:v>白瓷、透明但不半透明的风格化杯碗或烘焙纸托；不使用流派专属纹样</x:v>
+      </x:c>
+      <x:c r="AB28" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" s="1" customFormat="1" ht="17">
       <x:c r="C29" s="12"/>
       <x:c r="D29" s="8"/>
       <x:c r="E29" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F29" s="15"/>
       <x:c r="G29" s="15"/>
-      <x:c r="V29" s="15"/>
+      <x:c r="V29" s="45"/>
+      <x:c r="W29" s="45"/>
+      <x:c r="X29" s="44"/>
+      <x:c r="Y29" s="44"/>
+      <x:c r="Z29" s="44"/>
+      <x:c r="AA29" s="44"/>
+      <x:c r="AB29" s="45"/>
     </x:row>
     <x:row r="30" s="1" customFormat="1" ht="34">
       <x:c r="C30" s="13" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="D30" s="8" t="s">
-        <x:v>106</x:v>
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="D30" s="8" t="str">
+        <x:v>蛋卷</x:v>
       </x:c>
       <x:c r="E30" s="15" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F30" s="8"/>
       <x:c r="G30" s="15" t="s">
-        <x:v>358</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="I30" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K30" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="Q30" s="1">
         <x:v>3</x:v>
@@ -17650,1083 +17720,1942 @@
       <x:c r="U30" s="1">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="V30" s="15"/>
+      <x:c r="V30" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W30" s="45" t="str"/>
+      <x:c r="X30" s="44" t="str">
+        <x:v>蛋卷</x:v>
+      </x:c>
+      <x:c r="Y30" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E8%9B%8B%E5%8D%B7%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z30" s="44" t="str">
+        <x:v>3×1单份东方甜点；用糕、酥、糯米或甜品碗形成完整单体</x:v>
+      </x:c>
+      <x:c r="AA30" s="44" t="str">
+        <x:v>青瓷、竹托或中式纸托三选一；暖金、豆沙红、芝麻黑与米白为主</x:v>
+      </x:c>
+      <x:c r="AB30" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" s="1" customFormat="1" ht="34">
       <x:c r="C31" s="13"/>
-      <x:c r="D31" s="8" t="s">
-        <x:v>109</x:v>
+      <x:c r="D31" s="8" t="str">
+        <x:v>桂花糕</x:v>
       </x:c>
       <x:c r="E31" s="15" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F31" s="15"/>
       <x:c r="G31" s="15" t="s">
-        <x:v>360</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="I31" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="K31" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="U31" s="8"/>
-      <x:c r="V31" s="15"/>
+      <x:c r="V31" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W31" s="45" t="str"/>
+      <x:c r="X31" s="44" t="str">
+        <x:v>桂花糕</x:v>
+      </x:c>
+      <x:c r="Y31" s="44" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/%E6%A1%82%E8%8A%B1%E7%B3%95</x:v>
+      </x:c>
+      <x:c r="Z31" s="44" t="str">
+        <x:v>3×1单份东方甜点；用糕、酥、糯米或甜品碗形成完整单体</x:v>
+      </x:c>
+      <x:c r="AA31" s="44" t="str">
+        <x:v>青瓷、竹托或中式纸托三选一；暖金、豆沙红、芝麻黑与米白为主</x:v>
+      </x:c>
+      <x:c r="AB31" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" s="1" customFormat="1" ht="34">
       <x:c r="C32" s="13"/>
-      <x:c r="D32" s="8" t="s">
-        <x:v>113</x:v>
+      <x:c r="D32" s="8" t="str">
+        <x:v>糖葫芦</x:v>
       </x:c>
       <x:c r="E32" s="8" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F32" s="8"/>
       <x:c r="G32" s="15" t="s">
-        <x:v>361</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="I32" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K32" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="U32" s="8"/>
-      <x:c r="V32" s="15"/>
+      <x:c r="V32" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W32" s="45" t="str"/>
+      <x:c r="X32" s="44" t="str">
+        <x:v>糖葫芦</x:v>
+      </x:c>
+      <x:c r="Y32" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E7%B3%96%E8%91%AB%E8%8A%A6%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z32" s="44" t="str">
+        <x:v>3×1单体糖果或巧克力；包装走势服从格子比例，保持强轮廓</x:v>
+      </x:c>
+      <x:c r="AA32" s="44" t="str">
+        <x:v>无餐盘；使用糖纸、锡纸或纸托；糖晶高光与巧克力哑光形成材质差</x:v>
+      </x:c>
+      <x:c r="AB32" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" s="1" customFormat="1" ht="34">
       <x:c r="C33" s="13"/>
-      <x:c r="D33" s="8" t="s">
-        <x:v>117</x:v>
+      <x:c r="D33" s="8" t="str">
+        <x:v>拿破仑蛋糕</x:v>
       </x:c>
       <x:c r="E33" s="8" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F33" s="15"/>
       <x:c r="G33" s="15" t="s">
-        <x:v>362</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="I33" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K33" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="U33" s="15"/>
-      <x:c r="V33" s="8"/>
+      <x:c r="V33" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W33" s="45" t="str"/>
+      <x:c r="X33" s="44" t="str">
+        <x:v>拿破仑蛋糕</x:v>
+      </x:c>
+      <x:c r="Y33" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%8B%BF%E7%A0%B4%E4%BB%91%E8%9B%8B%E7%B3%95+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z33" s="44" t="str">
+        <x:v>3×1蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA33" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB33" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" s="1" customFormat="1" ht="34">
       <x:c r="C34" s="13"/>
-      <x:c r="D34" s="8" t="s">
-        <x:v>121</x:v>
+      <x:c r="D34" s="8" t="str">
+        <x:v>蜂蜜蛋糕</x:v>
       </x:c>
       <x:c r="E34" s="8" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F34" s="15"/>
       <x:c r="G34" s="15" t="s">
-        <x:v>363</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="I34" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K34" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="U34" s="15"/>
-      <x:c r="V34" s="18"/>
+      <x:c r="V34" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W34" s="45" t="str"/>
+      <x:c r="X34" s="44" t="str">
+        <x:v>蜂蜜蛋糕</x:v>
+      </x:c>
+      <x:c r="Y34" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E8%9C%82%E8%9C%9C%E8%9B%8B%E7%B3%95+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z34" s="44" t="str">
+        <x:v>3×1蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA34" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB34" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" s="1" customFormat="1" ht="34">
       <x:c r="C35" s="13"/>
-      <x:c r="D35" s="8" t="s">
-        <x:v>364</x:v>
+      <x:c r="D35" s="8" t="str">
+        <x:v>年轮蛋糕</x:v>
       </x:c>
       <x:c r="E35" s="8" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F35" s="15"/>
       <x:c r="G35" s="15" t="s">
-        <x:v>365</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="I35" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="U35" s="15"/>
-      <x:c r="V35" s="18"/>
+      <x:c r="V35" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W35" s="45" t="str"/>
+      <x:c r="X35" s="44" t="str">
+        <x:v>年轮蛋糕</x:v>
+      </x:c>
+      <x:c r="Y35" s="44" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/%E5%B9%B4%E8%BC%AA%E8%9B%8B%E7%B3%95</x:v>
+      </x:c>
+      <x:c r="Z35" s="44" t="str">
+        <x:v>3×1蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA35" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB35" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" s="1" customFormat="1" ht="34">
       <x:c r="C36" s="13"/>
-      <x:c r="D36" s="8" t="s">
-        <x:v>366</x:v>
+      <x:c r="D36" s="8" t="str">
+        <x:v>牛轧糖</x:v>
       </x:c>
       <x:c r="E36" s="8" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F36" s="15"/>
       <x:c r="G36" s="15" t="s">
-        <x:v>367</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="I36" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="U36" s="15"/>
-      <x:c r="V36" s="18"/>
+      <x:c r="V36" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W36" s="45" t="str"/>
+      <x:c r="X36" s="44" t="str">
+        <x:v>牛轧糖</x:v>
+      </x:c>
+      <x:c r="Y36" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E7%89%9B%E8%BD%A7%E7%B3%96+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z36" s="44" t="str">
+        <x:v>3×1单体糖果或巧克力；包装走势服从格子比例，保持强轮廓</x:v>
+      </x:c>
+      <x:c r="AA36" s="44" t="str">
+        <x:v>无餐盘；使用糖纸、锡纸或纸托；糖晶高光与巧克力哑光形成材质差</x:v>
+      </x:c>
+      <x:c r="AB36" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" s="1" customFormat="1" ht="34">
       <x:c r="C37" s="13"/>
-      <x:c r="D37" s="8" t="s">
-        <x:v>368</x:v>
+      <x:c r="D37" s="8" t="str">
+        <x:v>山楂糕</x:v>
       </x:c>
       <x:c r="E37" s="8" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F37" s="15"/>
       <x:c r="G37" s="18" t="s">
-        <x:v>369</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="I37" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="U37" s="15"/>
-      <x:c r="V37" s="18"/>
+      <x:c r="V37" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W37" s="45" t="str"/>
+      <x:c r="X37" s="44" t="str">
+        <x:v>山楂糕</x:v>
+      </x:c>
+      <x:c r="Y37" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E5%B1%B1%E6%A5%82%E7%B3%95+%E4%B8%AD%E5%BC%8F%E7%94%9C%E7%82%B9</x:v>
+      </x:c>
+      <x:c r="Z37" s="44" t="str">
+        <x:v>3×1单份东方甜点；用糕、酥、糯米或甜品碗形成完整单体</x:v>
+      </x:c>
+      <x:c r="AA37" s="44" t="str">
+        <x:v>青瓷、竹托或中式纸托三选一；暖金、豆沙红、芝麻黑与米白为主</x:v>
+      </x:c>
+      <x:c r="AB37" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" s="1" customFormat="1" ht="34">
       <x:c r="C38" s="13"/>
-      <x:c r="D38" s="8" t="s">
-        <x:v>370</x:v>
+      <x:c r="D38" s="8" t="str">
+        <x:v>舒芙蕾</x:v>
       </x:c>
       <x:c r="E38" s="8" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F38" s="15">
         <x:v>300</x:v>
       </x:c>
       <x:c r="G38" s="18" t="s">
-        <x:v>371</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="I38" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="U38" s="15"/>
-      <x:c r="V38" s="18"/>
+      <x:c r="V38" s="45" t="str">
+        <x:v>通用</x:v>
+      </x:c>
+      <x:c r="W38" s="45" t="str"/>
+      <x:c r="X38" s="44" t="str">
+        <x:v>舒芙蕾</x:v>
+      </x:c>
+      <x:c r="Y38" s="44" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/%E8%88%92%E8%8A%99%E8%95%BE</x:v>
+      </x:c>
+      <x:c r="Z38" s="44" t="str">
+        <x:v>3×1单份舒芙蕾；保持现实比例，用器皿或自然长形适配格子</x:v>
+      </x:c>
+      <x:c r="AA38" s="44" t="str">
+        <x:v>白瓷、透明但不半透明的风格化杯碗或烘焙纸托；不使用流派专属纹样</x:v>
+      </x:c>
+      <x:c r="AB38" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" s="1" customFormat="1" ht="34">
       <x:c r="C39" s="13"/>
-      <x:c r="D39" s="8" t="s">
-        <x:v>372</x:v>
+      <x:c r="D39" s="8" t="str">
+        <x:v>水果挞</x:v>
       </x:c>
       <x:c r="E39" s="8" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F39" s="15"/>
       <x:c r="G39" s="18" t="s">
-        <x:v>373</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="I39" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="U39" s="15"/>
-      <x:c r="V39" s="18"/>
+      <x:c r="V39" s="45" t="str">
+        <x:v>通用</x:v>
+      </x:c>
+      <x:c r="W39" s="45" t="str"/>
+      <x:c r="X39" s="44" t="str">
+        <x:v>水果挞</x:v>
+      </x:c>
+      <x:c r="Y39" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%B0%B4%E6%9E%9C%E6%8C%9E+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z39" s="44" t="str">
+        <x:v>3×1单份水果挞；保持现实比例，用器皿或自然长形适配格子</x:v>
+      </x:c>
+      <x:c r="AA39" s="44" t="str">
+        <x:v>白瓷、透明但不半透明的风格化杯碗或烘焙纸托；不使用流派专属纹样</x:v>
+      </x:c>
+      <x:c r="AB39" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" s="1" customFormat="1" ht="34">
       <x:c r="C40" s="13"/>
-      <x:c r="D40" s="8" t="s">
-        <x:v>374</x:v>
+      <x:c r="D40" s="8" t="str">
+        <x:v>草莓圣代</x:v>
       </x:c>
       <x:c r="E40" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F40" s="15"/>
       <x:c r="G40" s="18" t="s">
-        <x:v>375</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="I40" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="U40" s="15"/>
-      <x:c r="V40" s="18"/>
+      <x:c r="V40" s="45" t="str">
+        <x:v>通用</x:v>
+      </x:c>
+      <x:c r="W40" s="45" t="str"/>
+      <x:c r="X40" s="44" t="str">
+        <x:v>草莓圣代</x:v>
+      </x:c>
+      <x:c r="Y40" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E8%8D%89%E8%8E%93%E5%9C%A3%E4%BB%A3+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z40" s="44" t="str">
+        <x:v>1×3单份草莓圣代；保持现实比例，用器皿或自然长形适配格子</x:v>
+      </x:c>
+      <x:c r="AA40" s="44" t="str">
+        <x:v>白瓷、透明但不半透明的风格化杯碗或烘焙纸托；不使用流派专属纹样</x:v>
+      </x:c>
+      <x:c r="AB40" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" s="1" customFormat="1">
       <x:c r="C41" s="13"/>
       <x:c r="D41" s="8"/>
       <x:c r="E41" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F41" s="15"/>
       <x:c r="G41" s="18"/>
       <x:c r="U41" s="15"/>
-      <x:c r="V41" s="18"/>
+      <x:c r="V41" s="45"/>
+      <x:c r="W41" s="45"/>
+      <x:c r="X41" s="44"/>
+      <x:c r="Y41" s="44"/>
+      <x:c r="Z41" s="44"/>
+      <x:c r="AA41" s="44"/>
+      <x:c r="AB41" s="45"/>
     </x:row>
     <x:row r="42" s="1" customFormat="1">
       <x:c r="C42" s="13"/>
       <x:c r="D42" s="8"/>
       <x:c r="E42" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F42" s="15"/>
       <x:c r="G42" s="18"/>
       <x:c r="U42" s="15"/>
-      <x:c r="V42" s="18"/>
+      <x:c r="V42" s="45"/>
+      <x:c r="W42" s="45"/>
+      <x:c r="X42" s="44"/>
+      <x:c r="Y42" s="44"/>
+      <x:c r="Z42" s="44"/>
+      <x:c r="AA42" s="44"/>
+      <x:c r="AB42" s="45"/>
     </x:row>
     <x:row r="43" s="1" customFormat="1" ht="34">
       <x:c r="C43" s="13"/>
-      <x:c r="D43" s="8" t="s">
-        <x:v>376</x:v>
+      <x:c r="D43" s="8" t="str">
+        <x:v>冰糖雪梨</x:v>
       </x:c>
       <x:c r="E43" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F43" s="15"/>
       <x:c r="G43" s="18" t="s">
-        <x:v>377</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="I43" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="U43" s="15"/>
-      <x:c r="V43" s="18"/>
+      <x:c r="V43" s="45" t="str">
+        <x:v>通用</x:v>
+      </x:c>
+      <x:c r="W43" s="45" t="str"/>
+      <x:c r="X43" s="44" t="str">
+        <x:v>冰糖雪梨</x:v>
+      </x:c>
+      <x:c r="Y43" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E5%86%B0%E7%B3%96%E9%9B%AA%E6%A2%A8+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z43" s="44" t="str">
+        <x:v>1×3单份冰糖雪梨；保持现实比例，用器皿或自然长形适配格子</x:v>
+      </x:c>
+      <x:c r="AA43" s="44" t="str">
+        <x:v>白瓷、透明但不半透明的风格化杯碗或烘焙纸托；不使用流派专属纹样</x:v>
+      </x:c>
+      <x:c r="AB43" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" s="1" customFormat="1">
       <x:c r="C44" s="13"/>
       <x:c r="D44" s="8"/>
       <x:c r="E44" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F44" s="15"/>
       <x:c r="G44" s="18"/>
       <x:c r="U44" s="15"/>
-      <x:c r="V44" s="18"/>
+      <x:c r="V44" s="45"/>
+      <x:c r="W44" s="45"/>
+      <x:c r="X44" s="44"/>
+      <x:c r="Y44" s="44"/>
+      <x:c r="Z44" s="44"/>
+      <x:c r="AA44" s="44"/>
+      <x:c r="AB44" s="45"/>
     </x:row>
     <x:row r="45" s="1" customFormat="1">
       <x:c r="C45" s="13"/>
       <x:c r="D45" s="8"/>
       <x:c r="E45" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F45" s="15"/>
       <x:c r="G45" s="18"/>
       <x:c r="U45" s="15"/>
-      <x:c r="V45" s="18"/>
+      <x:c r="V45" s="45"/>
+      <x:c r="W45" s="45"/>
+      <x:c r="X45" s="44"/>
+      <x:c r="Y45" s="44"/>
+      <x:c r="Z45" s="44"/>
+      <x:c r="AA45" s="44"/>
+      <x:c r="AB45" s="45"/>
     </x:row>
     <x:row r="46" s="1" customFormat="1" ht="51">
       <x:c r="C46" s="13"/>
-      <x:c r="D46" s="8" t="s">
-        <x:v>378</x:v>
+      <x:c r="D46" s="8" t="str">
+        <x:v>跳跳糖</x:v>
       </x:c>
       <x:c r="E46" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F46" s="15"/>
       <x:c r="G46" s="18" t="s">
-        <x:v>379</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="I46" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="U46" s="15"/>
-      <x:c r="V46" s="18"/>
+      <x:c r="V46" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W46" s="45" t="str"/>
+      <x:c r="X46" s="44" t="str">
+        <x:v>跳跳糖</x:v>
+      </x:c>
+      <x:c r="Y46" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E8%B7%B3%E8%B7%B3%E7%B3%96+%E7%B3%96%E6%9E%9C</x:v>
+      </x:c>
+      <x:c r="Z46" s="44" t="str">
+        <x:v>1×3单体糖果或巧克力；包装走势服从格子比例，保持强轮廓</x:v>
+      </x:c>
+      <x:c r="AA46" s="44" t="str">
+        <x:v>无餐盘；使用糖纸、锡纸或纸托；糖晶高光与巧克力哑光形成材质差</x:v>
+      </x:c>
+      <x:c r="AB46" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" s="1" customFormat="1">
       <x:c r="C47" s="13"/>
       <x:c r="D47" s="8"/>
       <x:c r="E47" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F47" s="15"/>
       <x:c r="G47" s="15"/>
       <x:c r="U47" s="15"/>
-      <x:c r="V47" s="18"/>
+      <x:c r="V47" s="45"/>
+      <x:c r="W47" s="45"/>
+      <x:c r="X47" s="44"/>
+      <x:c r="Y47" s="44"/>
+      <x:c r="Z47" s="44"/>
+      <x:c r="AA47" s="44"/>
+      <x:c r="AB47" s="45"/>
     </x:row>
     <x:row r="48" s="1" customFormat="1">
       <x:c r="C48" s="13"/>
       <x:c r="D48" s="8"/>
       <x:c r="E48" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F48" s="15"/>
       <x:c r="G48" s="15"/>
       <x:c r="O48" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="U48" s="15"/>
-      <x:c r="V48" s="18"/>
+      <x:c r="V48" s="45"/>
+      <x:c r="W48" s="45"/>
+      <x:c r="X48" s="44"/>
+      <x:c r="Y48" s="44"/>
+      <x:c r="Z48" s="44"/>
+      <x:c r="AA48" s="44"/>
+      <x:c r="AB48" s="45"/>
     </x:row>
     <x:row r="49" s="1" customFormat="1" ht="34">
       <x:c r="C49" s="13"/>
-      <x:c r="D49" s="8" t="s">
-        <x:v>381</x:v>
+      <x:c r="D49" s="8" t="str">
+        <x:v>千层蛋糕</x:v>
       </x:c>
       <x:c r="E49" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F49" s="15"/>
       <x:c r="G49" s="15" t="s">
-        <x:v>382</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="I49" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="O49" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="U49" s="15"/>
-      <x:c r="V49" s="18"/>
+      <x:c r="V49" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W49" s="45" t="str"/>
+      <x:c r="X49" s="44" t="str">
+        <x:v>千层蛋糕</x:v>
+      </x:c>
+      <x:c r="Y49" s="44" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/%E5%8D%83%E5%B1%A4%E8%9B%8B%E7%B3%95</x:v>
+      </x:c>
+      <x:c r="Z49" s="44" t="str">
+        <x:v>1×3蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA49" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB49" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" s="1" customFormat="1">
       <x:c r="C50" s="13"/>
       <x:c r="D50" s="8"/>
       <x:c r="E50" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F50" s="15"/>
       <x:c r="G50" s="15"/>
       <x:c r="O50" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="U50" s="15"/>
-      <x:c r="V50" s="18"/>
+      <x:c r="V50" s="45"/>
+      <x:c r="W50" s="45"/>
+      <x:c r="X50" s="44"/>
+      <x:c r="Y50" s="44"/>
+      <x:c r="Z50" s="44"/>
+      <x:c r="AA50" s="44"/>
+      <x:c r="AB50" s="45"/>
     </x:row>
     <x:row r="51" s="1" customFormat="1">
       <x:c r="C51" s="13"/>
       <x:c r="D51" s="8"/>
       <x:c r="E51" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F51" s="15"/>
       <x:c r="G51" s="15"/>
       <x:c r="O51" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="U51" s="15"/>
-      <x:c r="V51" s="18"/>
+      <x:c r="V51" s="45"/>
+      <x:c r="W51" s="45"/>
+      <x:c r="X51" s="44"/>
+      <x:c r="Y51" s="44"/>
+      <x:c r="Z51" s="44"/>
+      <x:c r="AA51" s="44"/>
+      <x:c r="AB51" s="45"/>
     </x:row>
     <x:row r="52" s="1" customFormat="1" ht="34">
       <x:c r="C52" s="13"/>
-      <x:c r="D52" s="8" t="s">
-        <x:v>386</x:v>
+      <x:c r="D52" s="8" t="str">
+        <x:v>驴打滚</x:v>
       </x:c>
       <x:c r="E52" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F52" s="15"/>
       <x:c r="G52" s="15" t="s">
-        <x:v>387</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="I52" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="O52" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="U52" s="15"/>
-      <x:c r="V52" s="18"/>
+      <x:c r="V52" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W52" s="45" t="str"/>
+      <x:c r="X52" s="44" t="str">
+        <x:v>驴打滚</x:v>
+      </x:c>
+      <x:c r="Y52" s="44" t="str">
+        <x:v>https://en.wikipedia.org/wiki/List_of_Chinese_desserts</x:v>
+      </x:c>
+      <x:c r="Z52" s="44" t="str">
+        <x:v>1×3单份东方甜点；用糕、酥、糯米或甜品碗形成完整单体</x:v>
+      </x:c>
+      <x:c r="AA52" s="44" t="str">
+        <x:v>青瓷、竹托或中式纸托三选一；暖金、豆沙红、芝麻黑与米白为主</x:v>
+      </x:c>
+      <x:c r="AB52" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" s="1" customFormat="1">
       <x:c r="C53" s="13"/>
       <x:c r="D53" s="8"/>
       <x:c r="E53" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F53" s="15"/>
       <x:c r="G53" s="15"/>
       <x:c r="U53" s="15"/>
-      <x:c r="V53" s="18"/>
+      <x:c r="V53" s="45"/>
+      <x:c r="W53" s="45"/>
+      <x:c r="X53" s="44"/>
+      <x:c r="Y53" s="44"/>
+      <x:c r="Z53" s="44"/>
+      <x:c r="AA53" s="44"/>
+      <x:c r="AB53" s="45"/>
     </x:row>
     <x:row r="54" s="1" customFormat="1">
       <x:c r="C54" s="13"/>
       <x:c r="D54" s="8"/>
       <x:c r="E54" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F54" s="15"/>
       <x:c r="G54" s="15"/>
       <x:c r="M54" s="18"/>
       <x:c r="U54" s="15"/>
-      <x:c r="V54" s="18"/>
+      <x:c r="V54" s="45"/>
+      <x:c r="W54" s="45"/>
+      <x:c r="X54" s="44"/>
+      <x:c r="Y54" s="44"/>
+      <x:c r="Z54" s="44"/>
+      <x:c r="AA54" s="44"/>
+      <x:c r="AB54" s="45"/>
     </x:row>
     <x:row r="55" s="1" customFormat="1" ht="34">
       <x:c r="C55" s="13"/>
-      <x:c r="D55" s="8" t="s">
-        <x:v>124</x:v>
+      <x:c r="D55" s="8" t="str">
+        <x:v>沙琪玛</x:v>
       </x:c>
       <x:c r="E55" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F55" s="8"/>
       <x:c r="G55" s="15" t="s">
-        <x:v>389</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="I55" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K55" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="O55" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="Q55" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="V55" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W55" s="45" t="str"/>
+      <x:c r="X55" s="44" t="str">
+        <x:v>沙琪玛</x:v>
+      </x:c>
+      <x:c r="Y55" s="44" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/%E6%B2%99%E7%90%AA%E7%91%AA</x:v>
+      </x:c>
+      <x:c r="Z55" s="44" t="str">
+        <x:v>1×3单份东方甜点；用糕、酥、糯米或甜品碗形成完整单体</x:v>
+      </x:c>
+      <x:c r="AA55" s="44" t="str">
+        <x:v>青瓷、竹托或中式纸托三选一；暖金、豆沙红、芝麻黑与米白为主</x:v>
+      </x:c>
+      <x:c r="AB55" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="56" s="1" customFormat="1">
       <x:c r="C56" s="13"/>
       <x:c r="D56" s="8"/>
       <x:c r="E56" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F56" s="8"/>
       <x:c r="G56" s="8"/>
       <x:c r="O56" s="1" t="s">
-        <x:v>392</x:v>
-      </x:c>
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="V56" s="45"/>
+      <x:c r="W56" s="45"/>
+      <x:c r="X56" s="44"/>
+      <x:c r="Y56" s="44"/>
+      <x:c r="Z56" s="44"/>
+      <x:c r="AA56" s="44"/>
+      <x:c r="AB56" s="45"/>
     </x:row>
     <x:row r="57" s="1" customFormat="1">
       <x:c r="C57" s="13"/>
       <x:c r="D57" s="8"/>
       <x:c r="E57" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F57" s="15"/>
       <x:c r="G57" s="15"/>
+      <x:c r="V57" s="45"/>
+      <x:c r="W57" s="45"/>
+      <x:c r="X57" s="44"/>
+      <x:c r="Y57" s="44"/>
+      <x:c r="Z57" s="44"/>
+      <x:c r="AA57" s="44"/>
+      <x:c r="AB57" s="45"/>
     </x:row>
     <x:row r="58" s="1" customFormat="1" ht="51">
       <x:c r="C58" s="13"/>
-      <x:c r="D58" s="14" t="s">
-        <x:v>127</x:v>
+      <x:c r="D58" s="14" t="str">
+        <x:v>软糖</x:v>
       </x:c>
       <x:c r="E58" s="14" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F58" s="14"/>
       <x:c r="G58" s="19" t="s">
-        <x:v>393</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="I58" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K58" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="O58" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="V58" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W58" s="45" t="str"/>
+      <x:c r="X58" s="44" t="str">
+        <x:v>软糖</x:v>
+      </x:c>
+      <x:c r="Y58" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E8%BD%AF%E7%B3%96%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z58" s="44" t="str">
+        <x:v>1×3单体糖果或巧克力；包装走势服从格子比例，保持强轮廓</x:v>
+      </x:c>
+      <x:c r="AA58" s="44" t="str">
+        <x:v>无餐盘；使用糖纸、锡纸或纸托；糖晶高光与巧克力哑光形成材质差</x:v>
+      </x:c>
+      <x:c r="AB58" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="59" s="1" customFormat="1">
       <x:c r="C59" s="13"/>
       <x:c r="D59" s="8"/>
       <x:c r="E59" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F59" s="8"/>
       <x:c r="G59" s="8"/>
       <x:c r="O59" s="1" t="s">
-        <x:v>395</x:v>
-      </x:c>
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="V59" s="45"/>
+      <x:c r="W59" s="45"/>
+      <x:c r="X59" s="44"/>
+      <x:c r="Y59" s="44"/>
+      <x:c r="Z59" s="44"/>
+      <x:c r="AA59" s="44"/>
+      <x:c r="AB59" s="45"/>
     </x:row>
     <x:row r="60" s="1" customFormat="1">
       <x:c r="C60" s="13"/>
       <x:c r="D60" s="8"/>
       <x:c r="E60" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F60" s="15"/>
       <x:c r="G60" s="15"/>
       <x:c r="O60" s="1" t="s">
-        <x:v>396</x:v>
-      </x:c>
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="V60" s="45"/>
+      <x:c r="W60" s="45"/>
+      <x:c r="X60" s="44"/>
+      <x:c r="Y60" s="44"/>
+      <x:c r="Z60" s="44"/>
+      <x:c r="AA60" s="44"/>
+      <x:c r="AB60" s="45"/>
     </x:row>
     <x:row r="61" s="1" customFormat="1" ht="51">
       <x:c r="C61" s="13"/>
-      <x:c r="D61" s="8" t="s">
-        <x:v>131</x:v>
+      <x:c r="D61" s="8" t="str">
+        <x:v>巧克力威化</x:v>
       </x:c>
       <x:c r="E61" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F61" s="8"/>
       <x:c r="G61" s="15" t="s">
-        <x:v>397</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="I61" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K61" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="O61" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="V61" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W61" s="45" t="str"/>
+      <x:c r="X61" s="44" t="str">
+        <x:v>巧克力威化</x:v>
+      </x:c>
+      <x:c r="Y61" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E5%B7%A7%E5%85%8B%E5%8A%9B%E5%A8%81%E5%8C%96+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z61" s="44" t="str">
+        <x:v>单根纵向巧克力威化；层状断面与独立糖纸形成长轮廓</x:v>
+      </x:c>
+      <x:c r="AA61" s="44" t="str">
+        <x:v>彩色独立糖纸只包住下端；巧克力光泽与威化哑光分层</x:v>
+      </x:c>
+      <x:c r="AB61" s="45" t="str">
+        <x:v>四套画风打样</x:v>
       </x:c>
     </x:row>
     <x:row r="62" s="1" customFormat="1">
       <x:c r="C62" s="13"/>
       <x:c r="D62" s="8"/>
       <x:c r="E62" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F62" s="15"/>
       <x:c r="G62" s="15"/>
       <x:c r="O62" s="1" t="s">
-        <x:v>399</x:v>
-      </x:c>
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="V62" s="45"/>
+      <x:c r="W62" s="45"/>
+      <x:c r="X62" s="44"/>
+      <x:c r="Y62" s="44"/>
+      <x:c r="Z62" s="44"/>
+      <x:c r="AA62" s="44"/>
+      <x:c r="AB62" s="45"/>
     </x:row>
     <x:row r="63" s="1" customFormat="1" ht="17">
       <x:c r="C63" s="13"/>
       <x:c r="D63" s="15"/>
       <x:c r="E63" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F63" s="8"/>
       <x:c r="G63" s="8"/>
       <x:c r="O63" s="1" t="s">
-        <x:v>400</x:v>
-      </x:c>
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="V63" s="45"/>
+      <x:c r="W63" s="45"/>
+      <x:c r="X63" s="44"/>
+      <x:c r="Y63" s="44"/>
+      <x:c r="Z63" s="44"/>
+      <x:c r="AA63" s="44"/>
+      <x:c r="AB63" s="45"/>
     </x:row>
     <x:row r="64" s="1" customFormat="1" ht="34">
       <x:c r="C64" s="13"/>
-      <x:c r="D64" s="15" t="s">
-        <x:v>135</x:v>
+      <x:c r="D64" s="15" t="str">
+        <x:v>蛋糕卷</x:v>
       </x:c>
       <x:c r="E64" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F64" s="15"/>
       <x:c r="G64" s="15" t="s">
-        <x:v>401</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="I64" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="O64" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="V64" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W64" s="45" t="str"/>
+      <x:c r="X64" s="44" t="str">
+        <x:v>蛋糕卷</x:v>
+      </x:c>
+      <x:c r="Y64" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E8%9B%8B%E7%B3%95%E5%8D%B7%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z64" s="44" t="str">
+        <x:v>1×3蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA64" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB64" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="65" s="1" customFormat="1">
       <x:c r="C65" s="13"/>
       <x:c r="D65" s="8"/>
       <x:c r="E65" s="8" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F65" s="8"/>
       <x:c r="G65" s="8"/>
       <x:c r="O65" s="1" t="s">
-        <x:v>403</x:v>
-      </x:c>
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="V65" s="45"/>
+      <x:c r="W65" s="45"/>
+      <x:c r="X65" s="44"/>
+      <x:c r="Y65" s="44"/>
+      <x:c r="Z65" s="44"/>
+      <x:c r="AA65" s="44"/>
+      <x:c r="AB65" s="45"/>
     </x:row>
     <x:row r="66" s="1" customFormat="1" ht="17">
       <x:c r="C66" s="13"/>
       <x:c r="D66" s="15"/>
       <x:c r="E66" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F66" s="15"/>
       <x:c r="G66" s="15"/>
       <x:c r="O66" s="1" t="s">
-        <x:v>404</x:v>
-      </x:c>
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="V66" s="45"/>
+      <x:c r="W66" s="45"/>
+      <x:c r="X66" s="44"/>
+      <x:c r="Y66" s="44"/>
+      <x:c r="Z66" s="44"/>
+      <x:c r="AA66" s="44"/>
+      <x:c r="AB66" s="45"/>
     </x:row>
     <x:row r="67" s="1" customFormat="1" ht="34">
       <x:c r="C67" s="20"/>
-      <x:c r="D67" s="8" t="s">
-        <x:v>405</x:v>
+      <x:c r="D67" s="8" t="str">
+        <x:v>翻糖蛋糕</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F67" s="8"/>
       <x:c r="G67" s="15" t="str">
         <x:v>左侧随机1个食物视为蛋糕；欢乐蛋糕−10层</x:v>
       </x:c>
       <x:c r="I67" t="s">
-        <x:v>338</x:v>
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="V67" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W67" s="45" t="str"/>
+      <x:c r="X67" s="44" t="str">
+        <x:v>翻糖蛋糕</x:v>
+      </x:c>
+      <x:c r="Y67" s="44" t="str">
+        <x:v>https://www.cosmopolitan.com.hk/lifestyle/cake-types-introductions</x:v>
+      </x:c>
+      <x:c r="Z67" s="44" t="str">
+        <x:v>2×2蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA67" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB67" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
       </x:c>
     </x:row>
     <x:row r="68" s="1" customFormat="1">
       <x:c r="C68" s="20"/>
       <x:c r="D68" s="8"/>
       <x:c r="E68" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F68" s="8"/>
       <x:c r="G68" s="15"/>
+      <x:c r="V68" s="45"/>
+      <x:c r="W68" s="45"/>
+      <x:c r="X68" s="44"/>
+      <x:c r="Y68" s="44"/>
+      <x:c r="Z68" s="44"/>
+      <x:c r="AA68" s="44"/>
+      <x:c r="AB68" s="45"/>
     </x:row>
     <x:row r="69" s="1" customFormat="1" ht="17">
       <x:c r="C69" s="20"/>
-      <x:c r="D69" s="8" t="s">
-        <x:v>406</x:v>
+      <x:c r="D69" s="8" t="str">
+        <x:v>抹茶蛋糕</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F69" s="8"/>
       <x:c r="G69" s="15" t="s">
-        <x:v>407</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="I69" t="s">
-        <x:v>338</x:v>
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="V69" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W69" s="45" t="str"/>
+      <x:c r="X69" s="44" t="str">
+        <x:v>抹茶蛋糕</x:v>
+      </x:c>
+      <x:c r="Y69" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%8A%B9%E8%8C%B6%E8%9B%8B%E7%B3%95+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z69" s="44" t="str">
+        <x:v>低矮圆形抹茶蛋糕；切面清楚，顶部只保留一簇红豆与奶油</x:v>
+      </x:c>
+      <x:c r="AA69" s="44" t="str">
+        <x:v>象牙色扇贝边蛋糕托；抹茶绿、奶油白、少量红豆红</x:v>
+      </x:c>
+      <x:c r="AB69" s="45" t="str">
+        <x:v>四套画风打样</x:v>
       </x:c>
     </x:row>
     <x:row r="70" s="1" customFormat="1">
       <x:c r="C70" s="20"/>
       <x:c r="D70" s="8"/>
       <x:c r="E70" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F70" s="8"/>
       <x:c r="G70" s="15"/>
+      <x:c r="V70" s="45"/>
+      <x:c r="W70" s="45"/>
+      <x:c r="X70" s="44"/>
+      <x:c r="Y70" s="44"/>
+      <x:c r="Z70" s="44"/>
+      <x:c r="AA70" s="44"/>
+      <x:c r="AB70" s="45"/>
     </x:row>
     <x:row r="71" s="1" customFormat="1" ht="17">
       <x:c r="C71" s="20"/>
-      <x:c r="D71" s="8" t="s">
-        <x:v>408</x:v>
+      <x:c r="D71" s="8" t="str">
+        <x:v>绿豆糕</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F71" s="8"/>
       <x:c r="G71" s="15" t="s">
-        <x:v>409</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="I71" t="s">
-        <x:v>331</x:v>
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="V71" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W71" s="45" t="str"/>
+      <x:c r="X71" s="44" t="str">
+        <x:v>绿豆糕</x:v>
+      </x:c>
+      <x:c r="Y71" s="44" t="str">
+        <x:v>https://en.wikipedia.org/wiki/List_of_Chinese_desserts</x:v>
+      </x:c>
+      <x:c r="Z71" s="44" t="str">
+        <x:v>2×2单份东方甜点；用糕、酥、糯米或甜品碗形成完整单体</x:v>
+      </x:c>
+      <x:c r="AA71" s="44" t="str">
+        <x:v>青瓷、竹托或中式纸托三选一；暖金、豆沙红、芝麻黑与米白为主</x:v>
+      </x:c>
+      <x:c r="AB71" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
       </x:c>
     </x:row>
     <x:row r="72" s="1" customFormat="1">
       <x:c r="C72" s="20"/>
       <x:c r="D72" s="8"/>
       <x:c r="E72" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F72" s="8"/>
       <x:c r="G72" s="15"/>
+      <x:c r="V72" s="45"/>
+      <x:c r="W72" s="45"/>
+      <x:c r="X72" s="44"/>
+      <x:c r="Y72" s="44"/>
+      <x:c r="Z72" s="44"/>
+      <x:c r="AA72" s="44"/>
+      <x:c r="AB72" s="45"/>
     </x:row>
     <x:row r="73" s="1" customFormat="1" ht="34">
       <x:c r="C73" s="20"/>
-      <x:c r="D73" s="8" t="s">
-        <x:v>410</x:v>
+      <x:c r="D73" s="8" t="str">
+        <x:v>蛋黄酥</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F73" s="8"/>
       <x:c r="G73" s="15" t="s">
-        <x:v>411</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="I73" t="s">
-        <x:v>331</x:v>
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="V73" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W73" s="45" t="str"/>
+      <x:c r="X73" s="44" t="str">
+        <x:v>蛋黄酥</x:v>
+      </x:c>
+      <x:c r="Y73" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E8%9B%8B%E9%BB%84%E9%85%A5+%E4%B8%AD%E5%BC%8F%E7%94%9C%E7%82%B9</x:v>
+      </x:c>
+      <x:c r="Z73" s="44" t="str">
+        <x:v>单颗圆形蛋黄酥；酥皮开口露出蛋黄夹心</x:v>
+      </x:c>
+      <x:c r="AA73" s="44" t="str">
+        <x:v>青瓷小托；金黄酥皮、橙黄蛋心、少量黑芝麻</x:v>
+      </x:c>
+      <x:c r="AB73" s="45" t="str">
+        <x:v>四套画风打样</x:v>
       </x:c>
     </x:row>
     <x:row r="74" s="1" customFormat="1">
       <x:c r="C74" s="20"/>
       <x:c r="D74" s="8"/>
       <x:c r="E74" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F74" s="8"/>
       <x:c r="G74" s="15"/>
+      <x:c r="V74" s="45"/>
+      <x:c r="W74" s="45"/>
+      <x:c r="X74" s="44"/>
+      <x:c r="Y74" s="44"/>
+      <x:c r="Z74" s="44"/>
+      <x:c r="AA74" s="44"/>
+      <x:c r="AB74" s="45"/>
     </x:row>
     <x:row r="75" s="1" customFormat="1" ht="51">
       <x:c r="C75" s="20"/>
-      <x:c r="D75" s="8" t="s">
-        <x:v>412</x:v>
+      <x:c r="D75" s="8" t="str">
+        <x:v>松露巧克力</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F75" s="8"/>
       <x:c r="G75" s="19" t="s">
-        <x:v>413</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="I75" t="s">
-        <x:v>334</x:v>
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="V75" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W75" s="45" t="str"/>
+      <x:c r="X75" s="44" t="str">
+        <x:v>松露巧克力</x:v>
+      </x:c>
+      <x:c r="Y75" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%9D%BE%E9%9C%B2%E5%B7%A7%E5%85%8B%E5%8A%9B+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z75" s="44" t="str">
+        <x:v>单颗放大的圆形松露巧克力；可展示一处切面夹心</x:v>
+      </x:c>
+      <x:c r="AA75" s="44" t="str">
+        <x:v>无盘；短幅金色糖纸或可可纸托；可可粉哑光与夹心高光</x:v>
+      </x:c>
+      <x:c r="AB75" s="45" t="str">
+        <x:v>四套画风打样</x:v>
       </x:c>
     </x:row>
     <x:row r="76" s="1" customFormat="1">
       <x:c r="C76" s="20"/>
       <x:c r="D76" s="8"/>
       <x:c r="E76" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F76" s="8"/>
+      <x:c r="V76" s="45"/>
+      <x:c r="W76" s="45"/>
+      <x:c r="X76" s="44"/>
+      <x:c r="Y76" s="44"/>
+      <x:c r="Z76" s="44"/>
+      <x:c r="AA76" s="44"/>
+      <x:c r="AB76" s="45"/>
     </x:row>
     <x:row r="77" s="1" customFormat="1" ht="51">
       <x:c r="C77" s="20"/>
-      <x:c r="D77" s="8" t="s">
-        <x:v>414</x:v>
+      <x:c r="D77" s="8" t="str">
+        <x:v>酒心巧克力</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F77" s="8"/>
       <x:c r="G77" s="15" t="s">
-        <x:v>415</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="I77" t="s">
-        <x:v>334</x:v>
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="V77" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W77" s="45" t="str"/>
+      <x:c r="X77" s="44" t="str">
+        <x:v>酒心巧克力</x:v>
+      </x:c>
+      <x:c r="Y77" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E9%85%92%E5%BF%83%E5%B7%A7%E5%85%8B%E5%8A%9B+%E7%B3%96%E6%9E%9C</x:v>
+      </x:c>
+      <x:c r="Z77" s="44" t="str">
+        <x:v>2×2单体糖果或巧克力；包装走势服从格子比例，保持强轮廓</x:v>
+      </x:c>
+      <x:c r="AA77" s="44" t="str">
+        <x:v>无餐盘；使用糖纸、锡纸或纸托；糖晶高光与巧克力哑光形成材质差</x:v>
+      </x:c>
+      <x:c r="AB77" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
       </x:c>
     </x:row>
     <x:row r="78" s="1" customFormat="1">
       <x:c r="C78" s="20"/>
       <x:c r="D78" s="8"/>
       <x:c r="E78" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F78" s="8"/>
       <x:c r="G78" s="15"/>
+      <x:c r="V78" s="45"/>
+      <x:c r="W78" s="45"/>
+      <x:c r="X78" s="44"/>
+      <x:c r="Y78" s="44"/>
+      <x:c r="Z78" s="44"/>
+      <x:c r="AA78" s="44"/>
+      <x:c r="AB78" s="45"/>
     </x:row>
     <x:row r="79" s="1" customFormat="1" ht="34">
       <x:c r="C79" s="20" t="s">
-        <x:v>416</x:v>
-      </x:c>
-      <x:c r="D79" s="8" t="s">
-        <x:v>138</x:v>
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="D79" s="8" t="str">
+        <x:v>蝴蝶酥</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F79" s="8"/>
       <x:c r="G79" s="15" t="s">
-        <x:v>417</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="I79" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K79" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="O79" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="V79" s="45" t="str">
+        <x:v>通用</x:v>
+      </x:c>
+      <x:c r="W79" s="45" t="str"/>
+      <x:c r="X79" s="44" t="str">
+        <x:v>蝴蝶酥</x:v>
+      </x:c>
+      <x:c r="Y79" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E8%9D%B4%E8%9D%B6%E9%85%A5%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z79" s="44" t="str">
+        <x:v>2×2单份蝴蝶酥；保持现实比例，用器皿或自然长形适配格子</x:v>
+      </x:c>
+      <x:c r="AA79" s="44" t="str">
+        <x:v>白瓷、透明但不半透明的风格化杯碗或烘焙纸托；不使用流派专属纹样</x:v>
+      </x:c>
+      <x:c r="AB79" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="80" s="1" customFormat="1">
       <x:c r="C80" s="20"/>
       <x:c r="D80" s="15"/>
       <x:c r="E80" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F80" s="15"/>
       <x:c r="G80" s="15"/>
       <x:c r="M80" s="15"/>
       <x:c r="O80" s="1" t="s">
-        <x:v>419</x:v>
-      </x:c>
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="V80" s="45"/>
+      <x:c r="W80" s="45"/>
+      <x:c r="X80" s="44"/>
+      <x:c r="Y80" s="44"/>
+      <x:c r="Z80" s="44"/>
+      <x:c r="AA80" s="44"/>
+      <x:c r="AB80" s="45"/>
     </x:row>
     <x:row r="81" s="1" customFormat="1" ht="34">
       <x:c r="C81" s="20"/>
-      <x:c r="D81" s="21" t="s">
-        <x:v>141</x:v>
+      <x:c r="D81" s="21" t="str">
+        <x:v>戚风蛋糕</x:v>
       </x:c>
       <x:c r="E81" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F81" s="8">
         <x:v>40</x:v>
       </x:c>
       <x:c r="G81" s="15" t="s">
-        <x:v>420</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="I81" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="M81" s="18"/>
       <x:c r="O81" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="V81" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W81" s="45" t="str"/>
+      <x:c r="X81" s="44" t="str">
+        <x:v>戚风蛋糕</x:v>
+      </x:c>
+      <x:c r="Y81" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%88%9A%E9%A3%8E%E8%9B%8B%E7%B3%95%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z81" s="44" t="str">
+        <x:v>2×2蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA81" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB81" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="82" s="1" customFormat="1" ht="34">
       <x:c r="C82" s="20"/>
       <x:c r="D82" s="8"/>
       <x:c r="E82" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F82" s="8"/>
       <x:c r="G82" s="8"/>
       <x:c r="M82" s="18" t="s">
-        <x:v>422</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="O82" s="1" t="s">
-        <x:v>423</x:v>
-      </x:c>
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="V82" s="45"/>
+      <x:c r="W82" s="45"/>
+      <x:c r="X82" s="44"/>
+      <x:c r="Y82" s="44"/>
+      <x:c r="Z82" s="44"/>
+      <x:c r="AA82" s="44"/>
+      <x:c r="AB82" s="45"/>
     </x:row>
     <x:row r="83" s="1" customFormat="1" ht="34">
       <x:c r="C83" s="20"/>
-      <x:c r="D83" s="21" t="s">
-        <x:v>144</x:v>
+      <x:c r="D83" s="21" t="str">
+        <x:v>太妃糖</x:v>
       </x:c>
       <x:c r="E83" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F83" s="8">
         <x:v>40</x:v>
       </x:c>
       <x:c r="G83" s="15" t="s">
-        <x:v>424</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="I83" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="M83" s="18" t="s">
-        <x:v>425</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="O83" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="V83" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W83" s="45" t="str"/>
+      <x:c r="X83" s="44" t="str">
+        <x:v>太妃糖</x:v>
+      </x:c>
+      <x:c r="Y83" s="44" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/%E5%A4%AA%E5%A6%83%E7%B3%96</x:v>
+      </x:c>
+      <x:c r="Z83" s="44" t="str">
+        <x:v>2×2单体糖果或巧克力；包装走势服从格子比例，保持强轮廓</x:v>
+      </x:c>
+      <x:c r="AA83" s="44" t="str">
+        <x:v>无餐盘；使用糖纸、锡纸或纸托；糖晶高光与巧克力哑光形成材质差</x:v>
+      </x:c>
+      <x:c r="AB83" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="84" s="1" customFormat="1">
       <x:c r="C84" s="20"/>
       <x:c r="D84" s="8"/>
       <x:c r="E84" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F84" s="8"/>
       <x:c r="G84" s="8"/>
       <x:c r="M84" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="O84" s="1" t="s">
-        <x:v>428</x:v>
-      </x:c>
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="V84" s="45"/>
+      <x:c r="W84" s="45"/>
+      <x:c r="X84" s="44"/>
+      <x:c r="Y84" s="44"/>
+      <x:c r="Z84" s="44"/>
+      <x:c r="AA84" s="44"/>
+      <x:c r="AB84" s="45"/>
     </x:row>
     <x:row r="85" s="1" customFormat="1" ht="51">
       <x:c r="C85" s="20"/>
-      <x:c r="D85" s="22" t="s">
-        <x:v>147</x:v>
+      <x:c r="D85" s="22" t="str">
+        <x:v>桃酥</x:v>
       </x:c>
       <x:c r="E85" s="14" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F85" s="14">
         <x:v>40</x:v>
       </x:c>
       <x:c r="G85" s="19" t="s">
-        <x:v>429</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="I85" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K85" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="O85" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="V85" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W85" s="45" t="str"/>
+      <x:c r="X85" s="44" t="str">
+        <x:v>桃酥</x:v>
+      </x:c>
+      <x:c r="Y85" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%A1%83%E9%85%A5%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z85" s="44" t="str">
+        <x:v>2×2单份东方甜点；用糕、酥、糯米或甜品碗形成完整单体</x:v>
+      </x:c>
+      <x:c r="AA85" s="44" t="str">
+        <x:v>青瓷、竹托或中式纸托三选一；暖金、豆沙红、芝麻黑与米白为主</x:v>
+      </x:c>
+      <x:c r="AB85" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="86" s="1" customFormat="1">
       <x:c r="C86" s="20"/>
       <x:c r="D86" s="8"/>
       <x:c r="E86" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F86" s="8"/>
       <x:c r="G86" s="8"/>
+      <x:c r="V86" s="45"/>
+      <x:c r="W86" s="45"/>
+      <x:c r="X86" s="44"/>
+      <x:c r="Y86" s="44"/>
+      <x:c r="Z86" s="44"/>
+      <x:c r="AA86" s="44"/>
+      <x:c r="AB86" s="45"/>
     </x:row>
     <x:row r="87" s="1" customFormat="1" ht="34">
       <x:c r="C87" s="20"/>
-      <x:c r="D87" s="21" t="s">
-        <x:v>150</x:v>
+      <x:c r="D87" s="21" t="str">
+        <x:v>红糖发糕</x:v>
       </x:c>
       <x:c r="E87" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F87" s="8">
         <x:v>40</x:v>
       </x:c>
       <x:c r="G87" s="15" t="s">
-        <x:v>431</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="I87" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K87" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="V87" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W87" s="45" t="str"/>
+      <x:c r="X87" s="44" t="str">
+        <x:v>红糖发糕</x:v>
+      </x:c>
+      <x:c r="Y87" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E7%BA%A2%E7%B3%96%E5%8F%91%E7%B3%95+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z87" s="44" t="str">
+        <x:v>2×2单份东方甜点；用糕、酥、糯米或甜品碗形成完整单体</x:v>
+      </x:c>
+      <x:c r="AA87" s="44" t="str">
+        <x:v>青瓷、竹托或中式纸托三选一；暖金、豆沙红、芝麻黑与米白为主</x:v>
+      </x:c>
+      <x:c r="AB87" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="88" s="1" customFormat="1" ht="17.600000381469727">
       <x:c r="C88" s="20"/>
       <x:c r="D88" s="21"/>
       <x:c r="E88" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F88" s="8"/>
       <x:c r="G88" s="15"/>
+      <x:c r="V88" s="45"/>
+      <x:c r="W88" s="45"/>
+      <x:c r="X88" s="44"/>
+      <x:c r="Y88" s="44"/>
+      <x:c r="Z88" s="44"/>
+      <x:c r="AA88" s="44"/>
+      <x:c r="AB88" s="45"/>
     </x:row>
     <x:row r="89" s="1" customFormat="1" ht="51">
       <x:c r="C89" s="20"/>
-      <x:c r="D89" s="21" t="s">
-        <x:v>154</x:v>
+      <x:c r="D89" s="21" t="str">
+        <x:v>奶油蛋糕</x:v>
       </x:c>
       <x:c r="E89" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F89" s="8">
         <x:v>40</x:v>
       </x:c>
       <x:c r="G89" s="15" t="s">
-        <x:v>432</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="I89" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K89" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="V89" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W89" s="45" t="str"/>
+      <x:c r="X89" s="44" t="str">
+        <x:v>奶油蛋糕</x:v>
+      </x:c>
+      <x:c r="Y89" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E5%A5%B6%E6%B2%B9%E8%9B%8B%E7%B3%95%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z89" s="44" t="str">
+        <x:v>2×2蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA89" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB89" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="90" s="1" customFormat="1">
       <x:c r="C90" s="20"/>
       <x:c r="D90" s="8"/>
       <x:c r="E90" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F90" s="8"/>
       <x:c r="G90" s="8"/>
+      <x:c r="V90" s="45"/>
+      <x:c r="W90" s="45"/>
+      <x:c r="X90" s="44"/>
+      <x:c r="Y90" s="44"/>
+      <x:c r="Z90" s="44"/>
+      <x:c r="AA90" s="44"/>
+      <x:c r="AB90" s="45"/>
     </x:row>
     <x:row r="91" s="1" customFormat="1" ht="51">
       <x:c r="C91" s="20"/>
-      <x:c r="D91" s="23" t="s">
-        <x:v>158</x:v>
+      <x:c r="D91" s="23" t="str">
+        <x:v>拐杖糖</x:v>
       </x:c>
       <x:c r="E91" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F91" s="8">
         <x:v>40</x:v>
       </x:c>
       <x:c r="G91" s="15" t="s">
-        <x:v>433</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="I91" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="V91" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W91" s="45" t="str"/>
+      <x:c r="X91" s="44" t="str">
+        <x:v>拐杖糖</x:v>
+      </x:c>
+      <x:c r="Y91" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%8B%90%E6%9D%96%E7%B3%96%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z91" s="44" t="str">
+        <x:v>2×3单体糖果或巧克力；包装走势服从格子比例，保持强轮廓</x:v>
+      </x:c>
+      <x:c r="AA91" s="44" t="str">
+        <x:v>无餐盘；使用糖纸、锡纸或纸托；糖晶高光与巧克力哑光形成材质差</x:v>
+      </x:c>
+      <x:c r="AB91" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="92" s="1" customFormat="1">
       <x:c r="C92" s="20"/>
       <x:c r="D92" s="8"/>
       <x:c r="E92" s="8" t="s">
-        <x:v>434</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="F92" s="8"/>
       <x:c r="G92" s="8"/>
+      <x:c r="V92" s="45"/>
+      <x:c r="W92" s="45"/>
+      <x:c r="X92" s="44"/>
+      <x:c r="Y92" s="44"/>
+      <x:c r="Z92" s="44"/>
+      <x:c r="AA92" s="44"/>
+      <x:c r="AB92" s="45"/>
     </x:row>
     <x:row r="93" s="1" customFormat="1">
       <x:c r="C93" s="20"/>
       <x:c r="D93" s="8"/>
       <x:c r="E93" s="8" t="s">
-        <x:v>434</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="F93" s="8"/>
       <x:c r="G93" s="8"/>
+      <x:c r="V93" s="45"/>
+      <x:c r="W93" s="45"/>
+      <x:c r="X93" s="44"/>
+      <x:c r="Y93" s="44"/>
+      <x:c r="Z93" s="44"/>
+      <x:c r="AA93" s="44"/>
+      <x:c r="AB93" s="45"/>
     </x:row>
     <x:row r="94" s="1" customFormat="1" ht="34">
       <x:c r="C94" s="20"/>
-      <x:c r="D94" s="8" t="s">
-        <x:v>435</x:v>
+      <x:c r="D94" s="8" t="str">
+        <x:v>水果刨冰</x:v>
       </x:c>
       <x:c r="E94" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F94" s="8">
         <x:v>40</x:v>
       </x:c>
       <x:c r="G94" s="15" t="s">
-        <x:v>436</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="I94" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="V94" s="45" t="str">
+        <x:v>通用</x:v>
+      </x:c>
+      <x:c r="W94" s="45" t="str"/>
+      <x:c r="X94" s="44" t="str">
+        <x:v>水果刨冰</x:v>
+      </x:c>
+      <x:c r="Y94" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%B0%B4%E6%9E%9C%E5%88%A8%E5%86%B0+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z94" s="44" t="str">
+        <x:v>2×2单份水果刨冰；保持现实比例，用器皿或自然长形适配格子</x:v>
+      </x:c>
+      <x:c r="AA94" s="44" t="str">
+        <x:v>白瓷、透明但不半透明的风格化杯碗或烘焙纸托；不使用流派专属纹样</x:v>
+      </x:c>
+      <x:c r="AB94" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
       </x:c>
     </x:row>
     <x:row r="95" s="1" customFormat="1">
       <x:c r="C95" s="20"/>
       <x:c r="D95" s="8"/>
       <x:c r="E95" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F95" s="8"/>
       <x:c r="G95" s="8"/>
+      <x:c r="V95" s="45"/>
+      <x:c r="W95" s="45"/>
+      <x:c r="X95" s="44"/>
+      <x:c r="Y95" s="44"/>
+      <x:c r="Z95" s="44"/>
+      <x:c r="AA95" s="44"/>
+      <x:c r="AB95" s="45"/>
     </x:row>
     <x:row r="96" s="1" customFormat="1" ht="34">
       <x:c r="C96" s="20"/>
-      <x:c r="D96" s="8" t="s">
-        <x:v>437</x:v>
+      <x:c r="D96" s="8" t="str">
+        <x:v>椰奶冻</x:v>
       </x:c>
       <x:c r="E96" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F96" s="8">
         <x:v>40</x:v>
       </x:c>
       <x:c r="G96" s="15" t="s">
-        <x:v>438</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="I96" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="V96" s="45" t="str">
+        <x:v>通用</x:v>
+      </x:c>
+      <x:c r="W96" s="45" t="str"/>
+      <x:c r="X96" s="44" t="str">
+        <x:v>椰奶冻</x:v>
+      </x:c>
+      <x:c r="Y96" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%A4%B0%E5%A5%B6%E5%86%BB+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z96" s="44" t="str">
+        <x:v>2×2单份椰奶冻；保持现实比例，用器皿或自然长形适配格子</x:v>
+      </x:c>
+      <x:c r="AA96" s="44" t="str">
+        <x:v>白瓷、透明但不半透明的风格化杯碗或烘焙纸托；不使用流派专属纹样</x:v>
+      </x:c>
+      <x:c r="AB96" s="45" t="str">
+        <x:v>待选风格后制作</x:v>
       </x:c>
     </x:row>
     <x:row r="97" s="1" customFormat="1">
       <x:c r="C97" s="20"/>
       <x:c r="D97" s="8"/>
       <x:c r="E97" s="8" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F97" s="8"/>
       <x:c r="G97" s="8"/>
+      <x:c r="V97" s="45"/>
+      <x:c r="W97" s="45"/>
+      <x:c r="X97" s="44"/>
+      <x:c r="Y97" s="44"/>
+      <x:c r="Z97" s="44"/>
+      <x:c r="AA97" s="44"/>
+      <x:c r="AB97" s="45"/>
     </x:row>
     <x:row r="98" s="1" customFormat="1" ht="51">
       <x:c r="C98" s="24" t="s">
-        <x:v>439</x:v>
-      </x:c>
-      <x:c r="D98" s="9" t="s">
-        <x:v>162</x:v>
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="D98" s="9" t="str">
+        <x:v>黑森林蛋糕</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F98" s="8">
         <x:v>60</x:v>
       </x:c>
       <x:c r="G98" s="18" t="s">
-        <x:v>440</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="I98" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K98" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="O98" s="1">
         <x:v>4</x:v>
@@ -18739,282 +19668,565 @@
       </x:c>
       <x:c r="R98" s="1">
         <x:v>15</x:v>
+      </x:c>
+      <x:c r="V98" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W98" s="45" t="str"/>
+      <x:c r="X98" s="44" t="str">
+        <x:v>黑森林蛋糕</x:v>
+      </x:c>
+      <x:c r="Y98" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E9%BB%91%E6%A3%AE%E6%9E%97%E8%9B%8B%E7%B3%95%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z98" s="44" t="str">
+        <x:v>横向双层黑森林蛋糕；樱桃错落，避免整齐重复</x:v>
+      </x:c>
+      <x:c r="AA98" s="44" t="str">
+        <x:v>深色蛋糕底托；可可棕、奶油白、樱桃红</x:v>
+      </x:c>
+      <x:c r="AB98" s="45" t="str">
+        <x:v>四套画风打样</x:v>
       </x:c>
     </x:row>
     <x:row r="99" s="1" customFormat="1">
       <x:c r="C99" s="24"/>
       <x:c r="D99" s="8"/>
       <x:c r="E99" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F99" s="8"/>
       <x:c r="G99" s="8"/>
+      <x:c r="V99" s="45"/>
+      <x:c r="W99" s="45"/>
+      <x:c r="X99" s="44"/>
+      <x:c r="Y99" s="44"/>
+      <x:c r="Z99" s="44"/>
+      <x:c r="AA99" s="44"/>
+      <x:c r="AB99" s="45"/>
     </x:row>
     <x:row r="100" s="1" customFormat="1" ht="51">
       <x:c r="C100" s="24"/>
-      <x:c r="D100" s="23" t="s">
-        <x:v>166</x:v>
+      <x:c r="D100" s="23" t="str">
+        <x:v>生巧克力</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F100" s="8">
         <x:v>60</x:v>
       </x:c>
       <x:c r="G100" s="15" t="s">
-        <x:v>441</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="I100" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K100" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="V100" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W100" s="45" t="str"/>
+      <x:c r="X100" s="44" t="str">
+        <x:v>生巧克力</x:v>
+      </x:c>
+      <x:c r="Y100" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E7%94%9F%E5%B7%A7%E5%85%8B%E5%8A%9B+%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z100" s="44" t="str">
+        <x:v>3×2单体糖果或巧克力；包装走势服从格子比例，保持强轮廓</x:v>
+      </x:c>
+      <x:c r="AA100" s="44" t="str">
+        <x:v>无餐盘；使用糖纸、锡纸或纸托；糖晶高光与巧克力哑光形成材质差</x:v>
+      </x:c>
+      <x:c r="AB100" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="101" s="1" customFormat="1">
       <x:c r="C101" s="24"/>
       <x:c r="D101" s="8"/>
       <x:c r="E101" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F101" s="8"/>
       <x:c r="G101" s="8"/>
+      <x:c r="V101" s="45"/>
+      <x:c r="W101" s="45"/>
+      <x:c r="X101" s="44"/>
+      <x:c r="Y101" s="44"/>
+      <x:c r="Z101" s="44"/>
+      <x:c r="AA101" s="44"/>
+      <x:c r="AB101" s="45"/>
     </x:row>
     <x:row r="102" s="1" customFormat="1" ht="34">
       <x:c r="C102" s="24"/>
-      <x:c r="D102" s="21" t="s">
-        <x:v>169</x:v>
+      <x:c r="D102" s="21" t="str">
+        <x:v>杨枝甘露</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F102" s="8"/>
       <x:c r="G102" s="19" t="s">
-        <x:v>442</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="I102" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K102" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V102" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W102" s="45" t="str"/>
+      <x:c r="X102" s="44" t="str">
+        <x:v>杨枝甘露</x:v>
+      </x:c>
+      <x:c r="Y102" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%9D%A8%E6%9E%9D%E7%94%98%E9%9C%B2%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z102" s="44" t="str">
+        <x:v>3×2单份东方甜点；用糕、酥、糯米或甜品碗形成完整单体</x:v>
+      </x:c>
+      <x:c r="AA102" s="44" t="str">
+        <x:v>青瓷、竹托或中式纸托三选一；暖金、豆沙红、芝麻黑与米白为主</x:v>
+      </x:c>
+      <x:c r="AB102" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="103" s="1" customFormat="1">
       <x:c r="C103" s="24"/>
       <x:c r="D103" s="8"/>
       <x:c r="E103" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F103" s="15"/>
       <x:c r="M103" s="1" t="s">
-        <x:v>443</x:v>
-      </x:c>
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="V103" s="45"/>
+      <x:c r="W103" s="45"/>
+      <x:c r="X103" s="44"/>
+      <x:c r="Y103" s="44"/>
+      <x:c r="Z103" s="44"/>
+      <x:c r="AA103" s="44"/>
+      <x:c r="AB103" s="45"/>
     </x:row>
     <x:row r="104" s="1" customFormat="1" ht="51">
       <x:c r="C104" s="24"/>
-      <x:c r="D104" s="21" t="s">
-        <x:v>173</x:v>
+      <x:c r="D104" s="21" t="str">
+        <x:v>水果蛋糕</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F104" s="8"/>
       <x:c r="G104" s="18" t="s">
-        <x:v>444</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="I104" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K104" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V104" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W104" s="45" t="str"/>
+      <x:c r="X104" s="44" t="str">
+        <x:v>水果蛋糕</x:v>
+      </x:c>
+      <x:c r="Y104" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%B0%B4%E6%9E%9C%E8%9B%8B%E7%B3%95%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z104" s="44" t="str">
+        <x:v>2×3蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA104" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB104" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="105" s="1" customFormat="1">
       <x:c r="C105" s="24"/>
       <x:c r="D105" s="8"/>
       <x:c r="E105" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F105" s="8"/>
       <x:c r="K105" s="18"/>
+      <x:c r="V105" s="45"/>
+      <x:c r="W105" s="45"/>
+      <x:c r="X105" s="44"/>
+      <x:c r="Y105" s="44"/>
+      <x:c r="Z105" s="44"/>
+      <x:c r="AA105" s="44"/>
+      <x:c r="AB105" s="45"/>
     </x:row>
     <x:row r="106" s="1" customFormat="1">
       <x:c r="C106" s="24"/>
       <x:c r="D106" s="8"/>
       <x:c r="E106" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F106" s="15"/>
+      <x:c r="V106" s="45"/>
+      <x:c r="W106" s="45"/>
+      <x:c r="X106" s="44"/>
+      <x:c r="Y106" s="44"/>
+      <x:c r="Z106" s="44"/>
+      <x:c r="AA106" s="44"/>
+      <x:c r="AB106" s="45"/>
     </x:row>
     <x:row r="107" s="1" customFormat="1" ht="34">
       <x:c r="C107" s="24"/>
-      <x:c r="D107" s="21" t="s">
-        <x:v>176</x:v>
+      <x:c r="D107" s="21" t="str">
+        <x:v>酒酿圆子</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F107" s="8"/>
       <x:c r="G107" s="19" t="s">
-        <x:v>445</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="I107" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="K107" s="18"/>
+      <x:c r="V107" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W107" s="45" t="str"/>
+      <x:c r="X107" s="44" t="str">
+        <x:v>酒酿圆子</x:v>
+      </x:c>
+      <x:c r="Y107" s="44" t="str">
+        <x:v>https://en.wikipedia.org/wiki/List_of_Chinese_desserts</x:v>
+      </x:c>
+      <x:c r="Z107" s="44" t="str">
+        <x:v>2×3单份东方甜点；用糕、酥、糯米或甜品碗形成完整单体</x:v>
+      </x:c>
+      <x:c r="AA107" s="44" t="str">
+        <x:v>青瓷、竹托或中式纸托三选一；暖金、豆沙红、芝麻黑与米白为主</x:v>
+      </x:c>
+      <x:c r="AB107" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
+      </x:c>
     </x:row>
     <x:row r="108" s="1" customFormat="1">
       <x:c r="C108" s="24"/>
       <x:c r="E108" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F108" s="8"/>
+      <x:c r="V108" s="45"/>
+      <x:c r="W108" s="45"/>
+      <x:c r="X108" s="44"/>
+      <x:c r="Y108" s="44"/>
+      <x:c r="Z108" s="44"/>
+      <x:c r="AA108" s="44"/>
+      <x:c r="AB108" s="45"/>
     </x:row>
     <x:row r="109" s="1" customFormat="1">
       <x:c r="C109" s="24"/>
       <x:c r="E109" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F109" s="15"/>
       <x:c r="G109" s="18"/>
+      <x:c r="V109" s="45"/>
+      <x:c r="W109" s="45"/>
+      <x:c r="X109" s="44"/>
+      <x:c r="Y109" s="44"/>
+      <x:c r="Z109" s="44"/>
+      <x:c r="AA109" s="44"/>
+      <x:c r="AB109" s="45"/>
     </x:row>
     <x:row r="110" s="1" customFormat="1" ht="51">
       <x:c r="C110" s="24"/>
-      <x:c r="D110" s="8" t="s">
-        <x:v>179</x:v>
+      <x:c r="D110" s="8" t="str">
+        <x:v>棉花糖</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F110" s="8"/>
       <x:c r="G110" s="19" t="s">
-        <x:v>446</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="I110" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="V110" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W110" s="45" t="str"/>
+      <x:c r="X110" s="44" t="str">
+        <x:v>棉花糖</x:v>
+      </x:c>
+      <x:c r="Y110" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E6%A3%89%E8%8A%B1%E7%B3%96%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z110" s="44" t="str">
+        <x:v>2×3单体糖果或巧克力；包装走势服从格子比例，保持强轮廓</x:v>
+      </x:c>
+      <x:c r="AA110" s="44" t="str">
+        <x:v>无餐盘；使用糖纸、锡纸或纸托；糖晶高光与巧克力哑光形成材质差</x:v>
+      </x:c>
+      <x:c r="AB110" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="111" s="1" customFormat="1">
       <x:c r="C111" s="24"/>
       <x:c r="E111" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F111" s="15"/>
       <x:c r="G111" s="18"/>
+      <x:c r="V111" s="45"/>
+      <x:c r="W111" s="45"/>
+      <x:c r="X111" s="44"/>
+      <x:c r="Y111" s="44"/>
+      <x:c r="Z111" s="44"/>
+      <x:c r="AA111" s="44"/>
+      <x:c r="AB111" s="45"/>
     </x:row>
     <x:row r="112" s="1" customFormat="1">
       <x:c r="C112" s="24"/>
       <x:c r="D112" s="8"/>
       <x:c r="E112" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F112" s="8"/>
+      <x:c r="V112" s="45"/>
+      <x:c r="W112" s="45"/>
+      <x:c r="X112" s="44"/>
+      <x:c r="Y112" s="44"/>
+      <x:c r="Z112" s="44"/>
+      <x:c r="AA112" s="44"/>
+      <x:c r="AB112" s="45"/>
     </x:row>
     <x:row r="113" s="1" customFormat="1" ht="34">
       <x:c r="C113" s="15" t="s">
-        <x:v>447</x:v>
-      </x:c>
-      <x:c r="D113" s="21" t="s">
-        <x:v>183</x:v>
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="D113" s="21" t="str">
+        <x:v>大棒棒糖</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F113" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="G113" s="18" t="s">
-        <x:v>448</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="K113" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V113" s="45" t="str">
+        <x:v>甜蜜传递流</x:v>
+      </x:c>
+      <x:c r="W113" s="45" t="str"/>
+      <x:c r="X113" s="44" t="str">
+        <x:v>大棒棒糖</x:v>
+      </x:c>
+      <x:c r="Y113" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E5%A4%A7%E6%A3%92%E6%A3%92%E7%B3%96%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z113" s="44" t="str">
+        <x:v>3×3单体糖果或巧克力；包装走势服从格子比例，保持强轮廓</x:v>
+      </x:c>
+      <x:c r="AA113" s="44" t="str">
+        <x:v>无餐盘；使用糖纸、锡纸或纸托；糖晶高光与巧克力哑光形成材质差</x:v>
+      </x:c>
+      <x:c r="AB113" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="114" s="1" customFormat="1">
       <x:c r="C114" s="15"/>
       <x:c r="D114" s="8"/>
       <x:c r="E114" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G114" s="18"/>
+      <x:c r="V114" s="45"/>
+      <x:c r="W114" s="45"/>
+      <x:c r="X114" s="44"/>
+      <x:c r="Y114" s="44"/>
+      <x:c r="Z114" s="44"/>
+      <x:c r="AA114" s="44"/>
+      <x:c r="AB114" s="45"/>
     </x:row>
     <x:row r="115" s="1" customFormat="1">
       <x:c r="C115" s="15"/>
       <x:c r="D115" s="8"/>
       <x:c r="E115" s="1" t="s">
-        <x:v>357</x:v>
-      </x:c>
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="V115" s="45"/>
+      <x:c r="W115" s="45"/>
+      <x:c r="X115" s="44"/>
+      <x:c r="Y115" s="44"/>
+      <x:c r="Z115" s="44"/>
+      <x:c r="AA115" s="44"/>
+      <x:c r="AB115" s="45"/>
     </x:row>
     <x:row r="116" s="1" customFormat="1" ht="34">
       <x:c r="C116" s="15"/>
-      <x:c r="D116" s="21" t="s">
-        <x:v>186</x:v>
+      <x:c r="D116" s="21" t="str">
+        <x:v>双皮奶</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F116" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="G116" s="15" t="s">
-        <x:v>450</x:v>
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="V116" s="45" t="str">
+        <x:v>东方点心流</x:v>
+      </x:c>
+      <x:c r="W116" s="45" t="str"/>
+      <x:c r="X116" s="44" t="str">
+        <x:v>双皮奶</x:v>
+      </x:c>
+      <x:c r="Y116" s="44" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/%E9%9B%99%E7%9A%AE%E5%A5%B6</x:v>
+      </x:c>
+      <x:c r="Z116" s="44" t="str">
+        <x:v>宽口圆碗中的单份双皮奶；完整奶皮与少量红豆点缀</x:v>
+      </x:c>
+      <x:c r="AA116" s="44" t="str">
+        <x:v>青瓷宽口碗；奶白主体、焦糖色奶皮、少量红豆色</x:v>
+      </x:c>
+      <x:c r="AB116" s="45" t="str">
+        <x:v>四套画风打样</x:v>
       </x:c>
     </x:row>
     <x:row r="117" s="1" customFormat="1">
       <x:c r="C117" s="15"/>
       <x:c r="D117" s="8"/>
       <x:c r="E117" s="1" t="s">
-        <x:v>357</x:v>
-      </x:c>
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="V117" s="45"/>
+      <x:c r="W117" s="45"/>
+      <x:c r="X117" s="44"/>
+      <x:c r="Y117" s="44"/>
+      <x:c r="Z117" s="44"/>
+      <x:c r="AA117" s="44"/>
+      <x:c r="AB117" s="45"/>
     </x:row>
     <x:row r="118" s="1" customFormat="1">
       <x:c r="C118" s="15"/>
       <x:c r="D118" s="8"/>
       <x:c r="E118" s="1" t="s">
-        <x:v>357</x:v>
-      </x:c>
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="V118" s="45"/>
+      <x:c r="W118" s="45"/>
+      <x:c r="X118" s="44"/>
+      <x:c r="Y118" s="44"/>
+      <x:c r="Z118" s="44"/>
+      <x:c r="AA118" s="44"/>
+      <x:c r="AB118" s="45"/>
     </x:row>
     <x:row r="119" s="1" customFormat="1" ht="17.600000381469727">
       <x:c r="C119" s="15"/>
-      <x:c r="D119" s="21" t="s">
-        <x:v>189</x:v>
+      <x:c r="D119" s="21" t="str">
+        <x:v>双层蛋糕</x:v>
       </x:c>
       <x:c r="E119" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F119" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="G119" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="V119" s="45" t="str">
+        <x:v>蛋糕流</x:v>
+      </x:c>
+      <x:c r="W119" s="45" t="str"/>
+      <x:c r="X119" s="44" t="str">
+        <x:v>双层蛋糕</x:v>
+      </x:c>
+      <x:c r="Y119" s="44" t="str">
+        <x:v>https://www.bing.com/search?q=%E5%8F%8C%E5%B1%82%E8%9B%8B%E7%B3%95%20%E7%94%9C%E5%93%81</x:v>
+      </x:c>
+      <x:c r="Z119" s="44" t="str">
+        <x:v>3×4蛋糕主体；以真实切面、层次或烘焙轮廓区分，不堆叠复制</x:v>
+      </x:c>
+      <x:c r="AA119" s="44" t="str">
+        <x:v>象牙色或金色蛋糕托；奶油、蛋糕胚与少量真实装饰；柔和奶油色系</x:v>
+      </x:c>
+      <x:c r="AB119" s="45" t="str">
+        <x:v>待选风格后重绘</x:v>
       </x:c>
     </x:row>
     <x:row r="120" s="1" customFormat="1">
       <x:c r="C120" s="8"/>
       <x:c r="E120" s="1" t="s">
-        <x:v>357</x:v>
-      </x:c>
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="V120" s="45"/>
+      <x:c r="W120" s="45"/>
+      <x:c r="X120" s="44"/>
+      <x:c r="Y120" s="44"/>
+      <x:c r="Z120" s="44"/>
+      <x:c r="AA120" s="44"/>
+      <x:c r="AB120" s="45"/>
     </x:row>
     <x:row r="121" s="1" customFormat="1">
       <x:c r="C121" s="15"/>
       <x:c r="E121" s="1" t="s">
-        <x:v>357</x:v>
-      </x:c>
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="V121" s="45"/>
+      <x:c r="W121" s="45"/>
+      <x:c r="X121" s="44"/>
+      <x:c r="Y121" s="44"/>
+      <x:c r="Z121" s="44"/>
+      <x:c r="AA121" s="44"/>
+      <x:c r="AB121" s="45"/>
     </x:row>
     <x:row r="122" s="1" customFormat="1">
       <x:c r="C122" s="8"/>
       <x:c r="E122" s="1" t="s">
-        <x:v>357</x:v>
-      </x:c>
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="V122" s="45"/>
+      <x:c r="W122" s="45"/>
+      <x:c r="X122" s="44"/>
+      <x:c r="Y122" s="44"/>
+      <x:c r="Z122" s="44"/>
+      <x:c r="AA122" s="44"/>
+      <x:c r="AB122" s="45"/>
     </x:row>
     <x:row r="123" s="1" customFormat="1">
       <x:c r="C123" s="8"/>
@@ -19022,6 +20234,13 @@
       <x:c r="E123" s="8"/>
       <x:c r="F123" s="8"/>
       <x:c r="G123" s="8"/>
+      <x:c r="V123" s="45"/>
+      <x:c r="W123" s="45"/>
+      <x:c r="X123" s="44"/>
+      <x:c r="Y123" s="44"/>
+      <x:c r="Z123" s="44"/>
+      <x:c r="AA123" s="44"/>
+      <x:c r="AB123" s="45"/>
     </x:row>
     <x:row r="124" s="1" customFormat="1">
       <x:c r="C124" s="8"/>
@@ -19029,6 +20248,13 @@
       <x:c r="E124" s="8"/>
       <x:c r="F124" s="8"/>
       <x:c r="G124" s="8"/>
+      <x:c r="V124" s="45"/>
+      <x:c r="W124" s="45"/>
+      <x:c r="X124" s="44"/>
+      <x:c r="Y124" s="44"/>
+      <x:c r="Z124" s="44"/>
+      <x:c r="AA124" s="44"/>
+      <x:c r="AB124" s="45"/>
     </x:row>
     <x:row r="125" s="1" customFormat="1">
       <x:c r="C125" s="8"/>
@@ -19036,6 +20262,13 @@
       <x:c r="E125" s="8"/>
       <x:c r="F125" s="8"/>
       <x:c r="G125" s="8"/>
+      <x:c r="V125" s="45"/>
+      <x:c r="W125" s="45"/>
+      <x:c r="X125" s="44"/>
+      <x:c r="Y125" s="44"/>
+      <x:c r="Z125" s="44"/>
+      <x:c r="AA125" s="44"/>
+      <x:c r="AB125" s="45"/>
     </x:row>
     <x:row r="126" s="1" customFormat="1">
       <x:c r="C126" s="8"/>
@@ -19043,6 +20276,13 @@
       <x:c r="E126" s="8"/>
       <x:c r="F126" s="8"/>
       <x:c r="G126" s="8"/>
+      <x:c r="V126" s="45"/>
+      <x:c r="W126" s="45"/>
+      <x:c r="X126" s="44"/>
+      <x:c r="Y126" s="44"/>
+      <x:c r="Z126" s="44"/>
+      <x:c r="AA126" s="44"/>
+      <x:c r="AB126" s="45"/>
     </x:row>
     <x:row r="127" s="1" customFormat="1" ht="51">
       <x:c r="C127" s="8"/>
@@ -19050,8 +20290,15 @@
       <x:c r="E127" s="8"/>
       <x:c r="F127" s="8"/>
       <x:c r="G127" s="18" t="s">
-        <x:v>452</x:v>
-      </x:c>
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="V127" s="45"/>
+      <x:c r="W127" s="45"/>
+      <x:c r="X127" s="44"/>
+      <x:c r="Y127" s="44"/>
+      <x:c r="Z127" s="44"/>
+      <x:c r="AA127" s="44"/>
+      <x:c r="AB127" s="45"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -19062,6 +20309,11 @@
     <x:mergeCell ref="C98:C112"/>
     <x:mergeCell ref="C113:C119"/>
   </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="AB5:AB127">
+      <x:formula1>"四套画风打样,待选风格后制作,待选风格后重绘,已完成"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -19080,16 +20332,16 @@
       <x:c r="K4" s="3"/>
       <x:c r="L4" s="3"/>
       <x:c r="M4" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="N4" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="O4" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="P4" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="Q4" s="3"/>
       <x:c r="R4" s="3"/>
@@ -19099,16 +20351,16 @@
       <x:c r="Y4" s="3"/>
       <x:c r="Z4" s="3"/>
       <x:c r="AA4" s="3" t="s">
-        <x:v>454</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="AB4" s="3" t="s">
-        <x:v>454</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="AC4" s="3" t="s">
-        <x:v>454</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="AD4" s="3" t="s">
-        <x:v>454</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="AE4" s="3"/>
       <x:c r="AF4" s="3"/>
@@ -19129,16 +20381,16 @@
       <x:c r="K5" s="3"/>
       <x:c r="L5" s="3"/>
       <x:c r="M5" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="N5" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="O5" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
-        <x:v>455</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="Q5" s="3"/>
       <x:c r="R5" s="3"/>
@@ -19148,16 +20400,16 @@
       <x:c r="Y5" s="3"/>
       <x:c r="Z5" s="3"/>
       <x:c r="AA5" s="3" t="s">
-        <x:v>454</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="AB5" s="3" t="s">
-        <x:v>454</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="AC5" s="3" t="s">
-        <x:v>454</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="AD5" s="3" t="s">
-        <x:v>454</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="AE5" s="3"/>
       <x:c r="AF5" s="3"/>
@@ -19175,52 +20427,52 @@
       <x:c r="H6" s="2"/>
       <x:c r="I6" s="2"/>
       <x:c r="J6" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="K6" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="L6" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="M6" s="4" t="s">
-        <x:v>457</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="N6" s="5"/>
       <x:c r="O6" s="5"/>
       <x:c r="P6" s="5"/>
       <x:c r="Q6" s="3" t="s">
-        <x:v>458</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="V6" s="2"/>
       <x:c r="W6" s="2"/>
       <x:c r="X6" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="Y6" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="Z6" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="AA6" s="3" t="s">
-        <x:v>460</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="AB6" s="3" t="s">
-        <x:v>460</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="AC6" s="3" t="s">
-        <x:v>460</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="AD6" s="5"/>
       <x:c r="AE6" s="3" t="s">
-        <x:v>461</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="AF6" s="3" t="s">
-        <x:v>461</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="AG6" s="6"/>
       <x:c r="AH6" s="6"/>
@@ -19236,52 +20488,52 @@
       <x:c r="H7" s="2"/>
       <x:c r="I7" s="2"/>
       <x:c r="J7" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="K7" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="L7" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="M7" s="4" t="s">
-        <x:v>462</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="N7" s="5"/>
       <x:c r="O7" s="4" t="s">
-        <x:v>462</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="P7" s="5"/>
       <x:c r="Q7" s="3" t="s">
-        <x:v>458</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="V7" s="2"/>
       <x:c r="W7" s="2"/>
       <x:c r="X7" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="Y7" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="Z7" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="AA7" s="3" t="s">
-        <x:v>460</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="AB7" s="5"/>
       <x:c r="AC7" s="3" t="s">
-        <x:v>454</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="AD7" s="5"/>
       <x:c r="AE7" s="3" t="s">
-        <x:v>461</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="AF7" s="3" t="s">
-        <x:v>461</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="AG7" s="6"/>
       <x:c r="AH7" s="6"/>
@@ -19295,54 +20547,54 @@
     </x:row>
     <x:row r="8" ht="45" customHeight="1">
       <x:c r="H8" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="K8" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>458</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="M8" s="5"/>
       <x:c r="N8" s="5"/>
       <x:c r="O8" s="5"/>
       <x:c r="P8" s="5"/>
       <x:c r="Q8" s="3" t="s">
-        <x:v>458</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="V8" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="W8" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="X8" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="Y8" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="Z8" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="AA8" s="5"/>
       <x:c r="AB8" s="5"/>
       <x:c r="AC8" s="5"/>
       <x:c r="AD8" s="5"/>
       <x:c r="AE8" s="3" t="s">
-        <x:v>461</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="AF8" s="3" t="s">
-        <x:v>461</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="AG8" s="6"/>
       <x:c r="AH8" s="6"/>
@@ -19361,16 +20613,16 @@
       <x:c r="K9" s="3"/>
       <x:c r="L9" s="3"/>
       <x:c r="M9" s="3" t="s">
-        <x:v>455</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="N9" s="3" t="s">
-        <x:v>455</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="O9" s="3" t="s">
-        <x:v>455</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="P9" s="3" t="s">
-        <x:v>455</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="Q9" s="3"/>
       <x:c r="R9" s="3"/>
@@ -19380,16 +20632,16 @@
       <x:c r="Y9" s="3"/>
       <x:c r="Z9" s="3"/>
       <x:c r="AA9" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="AB9" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="AC9" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="AD9" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="AE9" s="3"/>
       <x:c r="AF9" s="3"/>
@@ -19397,13 +20649,13 @@
       <x:c r="AH9" s="6"/>
       <x:c r="AI9" s="6"/>
       <x:c r="AJ9" s="2" t="s">
-        <x:v>464</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="AK9" s="2" t="s">
-        <x:v>464</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="AL9" s="2" t="s">
-        <x:v>464</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="AM9" s="6"/>
       <x:c r="AN9" s="6"/>
@@ -19416,16 +20668,16 @@
       <x:c r="K10" s="3"/>
       <x:c r="L10" s="3"/>
       <x:c r="M10" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="N10" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="O10" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="Q10" s="3"/>
       <x:c r="R10" s="3"/>
@@ -19435,16 +20687,16 @@
       <x:c r="Y10" s="3"/>
       <x:c r="Z10" s="3"/>
       <x:c r="AA10" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="AB10" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="AC10" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="AD10" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="AE10" s="3"/>
       <x:c r="AF10" s="3"/>
@@ -19452,13 +20704,13 @@
       <x:c r="AH10" s="6"/>
       <x:c r="AI10" s="6"/>
       <x:c r="AJ10" s="2" t="s">
-        <x:v>465</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="AK10" s="2" t="s">
-        <x:v>465</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="AL10" s="2" t="s">
-        <x:v>465</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="AM10" s="6"/>
       <x:c r="AN10" s="6"/>
@@ -19471,10 +20723,10 @@
       <x:c r="K11" s="2"/>
       <x:c r="L11" s="2"/>
       <x:c r="M11" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="N11" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="O11" s="2"/>
       <x:c r="P11" s="2"/>
@@ -19486,10 +20738,10 @@
       <x:c r="Y11" s="2"/>
       <x:c r="Z11" s="2"/>
       <x:c r="AA11" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="AB11" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="AC11" s="2"/>
       <x:c r="AD11" s="2"/>
@@ -19499,13 +20751,13 @@
       <x:c r="AH11" s="6"/>
       <x:c r="AI11" s="6"/>
       <x:c r="AJ11" s="2" t="s">
-        <x:v>465</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="AK11" s="2" t="s">
-        <x:v>465</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="AL11" s="2" t="s">
-        <x:v>465</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="AM11" s="6"/>
       <x:c r="AN11" s="6"/>
@@ -19518,10 +20770,10 @@
       <x:c r="K12" s="2"/>
       <x:c r="L12" s="2"/>
       <x:c r="M12" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="N12" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="O12" s="2"/>
       <x:c r="P12" s="2"/>
@@ -19533,10 +20785,10 @@
       <x:c r="Y12" s="2"/>
       <x:c r="Z12" s="2"/>
       <x:c r="AA12" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="AB12" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="AC12" s="2"/>
       <x:c r="AD12" s="2"/>
@@ -19545,7 +20797,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="M14" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
